--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -10,9 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总表" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$8</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -20,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,13 +29,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="10"/>
-      <sz val="12"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b val="1"/>
@@ -81,25 +72,19 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -171,31 +156,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P8" headerRowCount="1">
-  <autoFilter ref="A1:P8"/>
-  <tableColumns count="16">
-    <tableColumn id="1" name="项目名称"/>
-    <tableColumn id="2" name="判断类别"/>
-    <tableColumn id="3" name="具体采购内容"/>
-    <tableColumn id="4" name="纳入理由"/>
-    <tableColumn id="5" name="关键信息摘要"/>
-    <tableColumn id="6" name="采购方/招标人"/>
-    <tableColumn id="7" name="中标人/候选人"/>
-    <tableColumn id="8" name="发布时间"/>
-    <tableColumn id="9" name="报名/截止/开标时间"/>
-    <tableColumn id="10" name="来源网站"/>
-    <tableColumn id="11" name="公告类型"/>
-    <tableColumn id="12" name="项目状态"/>
-    <tableColumn id="13" name="预算/最高限价"/>
-    <tableColumn id="14" name="中标/成交金额"/>
-    <tableColumn id="15" name="原文链接"/>
-    <tableColumn id="16" name="采集时间"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -487,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -590,459 +550,8 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="58" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>AOI 晶圆 缺陷 检测台评标结果公示公告</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>光学检测设备</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>AOI</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>项目：AOI 晶圆 缺陷 检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>采招网</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>中标结果</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>已出结果</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-424516652</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16T14:17:19</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="58" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>光学检测设备</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>检测设备</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>采招网</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>招标公告</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>进行中/未知</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-423735716</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16T14:17:19</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="58" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>SiC衬底 晶圆 位错缺陷光学无损 检测 设备中标结果公告(1)-0664-2640SUMECA96/01</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>光学检测设备</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>检测设备</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测 设备中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 2026-06-09；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>采招网</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>中标结果</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>已出结果</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-423847224</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16T14:17:19</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>晶圆 表面缺陷 检测 设备采购项目中标（成交）结果公告</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>光学检测设备</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>晶圆表面缺陷检测</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>项目：晶圆 表面缺陷 检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>采招网</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>中标结果</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>已出结果</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16T14:17:19</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>缺陷检测仪【重新招标】-公开招标公告</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>半导体检测/量测设备</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>缺陷检测仪</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>检测仪，且公告具有半导体产业链语境</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>无锡中微掩模电子有限公司</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>中招联合</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>公开招标公告</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>进行中/未知</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16T14:14:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>光学检测设备</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>检测仪</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>采招网</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>招标公告</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>进行中/未知</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-423147557</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16T14:17:19</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>光学检测设备</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>外观检测</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>采招网</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>中标结果</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>已出结果</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16T14:17:19</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P8"/>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId7"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -1052,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1060,7 +569,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>招标信息总表</t>
         </is>
@@ -1074,7 +583,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-16T14:23:54</t>
+          <t>2026-06-16T18:18:43</t>
         </is>
       </c>
     </row>
@@ -1085,39 +594,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>来源网站</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>条数</t>
         </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>采招网</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>中招联合</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-16T18:18:43</t>
+          <t>2026-06-16T18:19:41</t>
         </is>
       </c>
     </row>

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -10,7 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总表" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$15</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,6 +31,13 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b val="1"/>
@@ -72,19 +81,25 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -156,6 +171,31 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P15" headerRowCount="1">
+  <autoFilter ref="A1:P15"/>
+  <tableColumns count="16">
+    <tableColumn id="1" name="项目名称"/>
+    <tableColumn id="2" name="判断类别"/>
+    <tableColumn id="3" name="具体采购内容"/>
+    <tableColumn id="4" name="纳入理由"/>
+    <tableColumn id="5" name="关键信息摘要"/>
+    <tableColumn id="6" name="采购方/招标人"/>
+    <tableColumn id="7" name="中标人/候选人"/>
+    <tableColumn id="8" name="发布时间"/>
+    <tableColumn id="9" name="报名/截止/开标时间"/>
+    <tableColumn id="10" name="来源网站"/>
+    <tableColumn id="11" name="公告类型"/>
+    <tableColumn id="12" name="项目状态"/>
+    <tableColumn id="13" name="预算/最高限价"/>
+    <tableColumn id="14" name="中标/成交金额"/>
+    <tableColumn id="15" name="原文链接"/>
+    <tableColumn id="16" name="采集时间"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -447,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -550,8 +590,896 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16T09:24:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="58" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>光学量测设备</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>膜厚仪</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>招标预告</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>进行中/未知</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16T09:24:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="58" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>AOI</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16T09:24:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>检测设备</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16T09:24:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>检测设备</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>招标公告</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>进行中/未知</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16T09:24:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>自动光学检查机</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16T09:24:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>晶圆表面缺陷检测</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16T09:24:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>检测仪</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>招标公告</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>进行中/未知</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16T09:24:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>光学量测设备</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>CD-SEM</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16T09:24:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>颗粒检测系统</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16T09:24:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>检测仪</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>招标变更</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>变更/澄清</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16T09:24:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 国际招标公告(2)-0664-2640SUMECA96/09</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>检测仪</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 国际招标公告(2)-0664-2640SUMECA96/09；可见摘要：收藏 招标公告 北京 2026-05-27；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>招标公告</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>进行中/未知</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421420520</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16T09:24:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>招标变更</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>变更/澄清</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16T09:24:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>检测设备</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-421062373</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16T09:24:39</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:P15"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -561,7 +1489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -569,7 +1497,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>招标信息总表</t>
         </is>
@@ -583,7 +1511,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-16T18:19:41</t>
+          <t>2026-06-16T18:20:49</t>
         </is>
       </c>
     </row>
@@ -594,19 +1522,29 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>来源网站</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>条数</t>
         </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-16T18:20:49</t>
+          <t>2026-06-16T18:24:43</t>
         </is>
       </c>
     </row>

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P15" headerRowCount="1">
-  <autoFilter ref="A1:P15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P19" headerRowCount="1">
+  <autoFilter ref="A1:P19"/>
   <tableColumns count="16">
     <tableColumn id="1" name="项目名称"/>
     <tableColumn id="2" name="判断类别"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -593,7 +593,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目评标结果公示公告(1)-1069-264Z20261762</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -603,24 +603,24 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目评标结果公示公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -643,46 +643,46 @@
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425558679</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16T09:24:39</t>
+          <t>2026-06-18T12:08:48</t>
         </is>
       </c>
     </row>
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
+          <t>上海易启芯程 半导体 有限公司颗粒检测设备评标结果公示公告(1)-0613-264025122218</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备评标结果公示公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 20小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -693,31 +693,31 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425491184</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16T09:24:39</t>
+          <t>2026-06-18T12:08:48</t>
         </is>
       </c>
     </row>
     <row r="4" ht="58" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -727,24 +727,24 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -755,31 +755,31 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16T09:24:39</t>
+          <t>2026-06-18T12:08:48</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -789,24 +789,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>外观检查机</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -829,46 +829,46 @@
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16T09:24:39</t>
+          <t>2026-06-18T12:08:48</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
+          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>膜厚仪</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -879,7 +879,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -891,19 +891,19 @@
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16T09:24:39</t>
+          <t>2026-06-18T12:08:48</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
+          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -913,24 +913,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -953,19 +953,19 @@
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16T09:24:39</t>
+          <t>2026-06-18T12:08:48</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
+          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -975,24 +975,24 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
+          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -1015,19 +1015,19 @@
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16T09:24:39</t>
+          <t>2026-06-18T12:08:48</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1037,24 +1037,24 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -1077,46 +1077,46 @@
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16T09:24:39</t>
+          <t>2026-06-18T12:08:48</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
+          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM</t>
+          <t>自动光学检查机</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -1139,19 +1139,19 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16T09:24:39</t>
+          <t>2026-06-18T12:08:48</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
+          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统</t>
+          <t>晶圆表面缺陷检测</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1201,19 +1201,19 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16T09:24:39</t>
+          <t>2026-06-18T12:08:48</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1233,14 +1233,14 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1251,58 +1251,58 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16T09:24:39</t>
+          <t>2026-06-18T12:08:48</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 国际招标公告(2)-0664-2640SUMECA96/09</t>
+          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>CD-SEM</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 国际招标公告(2)-0664-2640SUMECA96/09；可见摘要：收藏 招标公告 北京 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1313,31 +1313,31 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421420520</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16T09:24:39</t>
+          <t>2026-06-18T12:08:48</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1347,24 +1347,24 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>外观检测</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1375,31 +1375,31 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16T09:24:39</t>
+          <t>2026-06-18T12:08:48</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1409,24 +1409,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>颗粒检测系统</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1449,17 +1449,265 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18T12:08:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>检测仪</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>招标变更</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>变更/澄清</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18T12:08:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 国际招标公告(2)-0664-2640SUMECA96/09</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>检测仪</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 国际招标公告(2)-0664-2640SUMECA96/09；可见摘要：收藏 招标公告 北京 2026-05-27；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>招标公告</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>进行中/未知</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421420520</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18T12:08:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>招标变更</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>变更/澄清</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18T12:08:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>检测设备</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
           <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-421062373</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16T09:24:39</t>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18T12:08:48</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P15"/>
+  <autoFilter ref="A1:P19"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -1475,10 +1723,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1511,7 +1763,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-16T18:24:43</t>
+          <t>2026-06-18T12:08:49</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1774,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
@@ -1544,7 +1796,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P19" headerRowCount="1">
-  <autoFilter ref="A1:P19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P22" headerRowCount="1">
+  <autoFilter ref="A1:P22"/>
   <tableColumns count="16">
     <tableColumn id="1" name="项目名称"/>
     <tableColumn id="2" name="判断类别"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -593,7 +593,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目评标结果公示公告(1)-1069-264Z20261762</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -603,17 +603,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目评标结果公示公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 18小时前；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
@@ -631,31 +631,31 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425558679</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425830318</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18T12:08:48</t>
+          <t>2026-06-22T09:27:59</t>
         </is>
       </c>
     </row>
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司颗粒检测设备评标结果公示公告(1)-0613-264025122218</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -665,17 +665,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备评标结果公示公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 20小时前；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
@@ -693,31 +693,31 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425491184</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18T12:08:48</t>
+          <t>2026-06-22T09:27:59</t>
         </is>
       </c>
     </row>
     <row r="4" ht="58" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
+          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -727,24 +727,24 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -767,19 +767,19 @@
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18T12:08:48</t>
+          <t>2026-06-22T09:27:59</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目评标结果公示公告(1)-1069-264Z20261762</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -789,24 +789,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目评标结果公示公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -829,46 +829,46 @@
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425558679</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18T12:08:48</t>
+          <t>2026-06-22T09:27:59</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
+          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -879,31 +879,31 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18T12:08:48</t>
+          <t>2026-06-22T09:27:59</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
+          <t>上海易启芯程 半导体 有限公司颗粒检测设备评标结果公示公告(1)-0613-264025122218</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -913,24 +913,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备评标结果公示公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 20小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -953,19 +953,19 @@
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425491184</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18T12:08:48</t>
+          <t>2026-06-22T09:27:59</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -975,24 +975,24 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -1003,31 +1003,31 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18T12:08:48</t>
+          <t>2026-06-22T09:27:59</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1037,24 +1037,24 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>外观检查机</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -1065,58 +1065,58 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18T12:08:48</t>
+          <t>2026-06-22T09:27:59</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
+          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机</t>
+          <t>膜厚仪</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -1127,31 +1127,31 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18T12:08:48</t>
+          <t>2026-06-22T09:27:59</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
+          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
+          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1201,19 +1201,19 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18T12:08:48</t>
+          <t>2026-06-22T09:27:59</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
+          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1223,24 +1223,24 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
+          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1251,58 +1251,58 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18T12:08:48</t>
+          <t>2026-06-22T09:27:59</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1313,31 +1313,31 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18T12:08:48</t>
+          <t>2026-06-22T09:27:59</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
+          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1347,24 +1347,24 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>外观检测</t>
+          <t>自动光学检查机</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1387,19 +1387,19 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18T12:08:48</t>
+          <t>2026-06-22T09:27:59</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
+          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1409,24 +1409,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统</t>
+          <t>晶圆表面缺陷检测</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1449,19 +1449,19 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18T12:08:48</t>
+          <t>2026-06-22T09:27:59</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1481,14 +1481,14 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1499,58 +1499,58 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18T12:08:48</t>
+          <t>2026-06-22T09:27:59</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 国际招标公告(2)-0664-2640SUMECA96/09</t>
+          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>CD-SEM</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 国际招标公告(2)-0664-2640SUMECA96/09；可见摘要：收藏 招标公告 北京 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1561,31 +1561,31 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421420520</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18T12:08:48</t>
+          <t>2026-06-22T09:27:59</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1595,24 +1595,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>外观检测</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1623,31 +1623,31 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18T12:08:48</t>
+          <t>2026-06-22T09:27:59</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1657,24 +1657,24 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>颗粒检测系统</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1697,17 +1697,203 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22T09:27:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>检测仪</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>招标变更</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>变更/澄清</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22T09:27:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>招标变更</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>变更/澄清</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22T09:27:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>检测设备</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
           <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-421062373</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18T12:08:48</t>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22T09:27:59</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P19"/>
+  <autoFilter ref="A1:P22"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -1727,10 +1913,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId22"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1763,7 +1952,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-18T12:08:49</t>
+          <t>2026-06-22T09:27:59</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1963,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -1796,7 +1985,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -1952,7 +1952,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-22T09:27:59</t>
+          <t>2026-06-22T09:31:13</t>
         </is>
       </c>
     </row>

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P22" headerRowCount="1">
-  <autoFilter ref="A1:P22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P24" headerRowCount="1">
+  <autoFilter ref="A1:P24"/>
   <tableColumns count="16">
     <tableColumn id="1" name="项目名称"/>
     <tableColumn id="2" name="判断类别"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -593,7 +593,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202</t>
+          <t>心脏自主神经功能多参数检测系统、体外冲击波治疗仪（立式）、射频治疗仪、808 半导体 激光治疗仪市场调研公告</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -603,24 +603,24 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：心脏自主神经功能多参数检测系统、体外冲击波治疗仪（立式）、射频治疗仪、808 半导体 激光治疗仪市场调研公告；可见摘要：收藏 招标公告 江苏 22小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -643,19 +643,19 @@
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425830318</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426004539</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T09:27:59</t>
+          <t>2026-06-23T09:57:50</t>
         </is>
       </c>
     </row>
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
+          <t>采购 芯片 检测 AOI没备</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -665,24 +665,24 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：采购 芯片 检测 AOI没备；可见摘要：收藏 采购信息 广东 2026-06-22；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -693,31 +693,31 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>采购信息</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-426218961</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T09:27:59</t>
+          <t>2026-06-23T09:57:50</t>
         </is>
       </c>
     </row>
     <row r="4" ht="58" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -727,17 +727,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -767,19 +767,19 @@
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425830318</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T09:27:59</t>
+          <t>2026-06-23T09:57:50</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目评标结果公示公告(1)-1069-264Z20261762</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -789,17 +789,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目评标结果公示公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 18小时前；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
@@ -817,31 +817,31 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425558679</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T09:27:59</t>
+          <t>2026-06-23T09:57:50</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
+          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
@@ -884,26 +884,26 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T09:27:59</t>
+          <t>2026-06-23T09:57:50</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司颗粒检测设备评标结果公示公告(1)-0613-264025122218</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目评标结果公示公告(1)-1069-264Z20261762</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -913,17 +913,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备评标结果公示公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 20小时前；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目评标结果公示公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
@@ -953,19 +953,19 @@
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425491184</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425558679</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T09:27:59</t>
+          <t>2026-06-23T09:57:50</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
+          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -975,24 +975,24 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -1003,31 +1003,31 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T09:27:59</t>
+          <t>2026-06-23T09:57:50</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
+          <t>上海易启芯程 半导体 有限公司颗粒检测设备评标结果公示公告(1)-0613-264025122218</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1037,24 +1037,24 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备评标结果公示公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 20小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -1077,46 +1077,46 @@
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425491184</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T09:27:59</t>
+          <t>2026-06-23T09:57:50</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1139,19 +1139,19 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T09:27:59</t>
+          <t>2026-06-23T09:57:50</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>外观检查机</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1201,46 +1201,46 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T09:27:59</t>
+          <t>2026-06-23T09:57:50</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
+          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>膜厚仪</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1251,31 +1251,31 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T09:27:59</t>
+          <t>2026-06-23T09:57:50</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
+          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1285,24 +1285,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
+          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1313,31 +1313,31 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T09:27:59</t>
+          <t>2026-06-23T09:57:50</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
+          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1347,24 +1347,24 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1387,19 +1387,19 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T09:27:59</t>
+          <t>2026-06-23T09:57:50</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1409,24 +1409,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1437,31 +1437,31 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T09:27:59</t>
+          <t>2026-06-23T09:57:50</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
+          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1471,24 +1471,24 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>自动光学检查机</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1499,58 +1499,58 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T09:27:59</t>
+          <t>2026-06-23T09:57:50</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
+          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM</t>
+          <t>晶圆表面缺陷检测</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
+          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1573,19 +1573,19 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T09:27:59</t>
+          <t>2026-06-23T09:57:50</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1595,24 +1595,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>外观检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1623,58 +1623,58 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T09:27:59</t>
+          <t>2026-06-23T09:57:50</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
+          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统</t>
+          <t>CD-SEM</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1697,19 +1697,19 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T09:27:59</t>
+          <t>2026-06-23T09:57:50</t>
         </is>
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1719,24 +1719,24 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>外观检测</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1747,31 +1747,31 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T09:27:59</t>
+          <t>2026-06-23T09:57:50</t>
         </is>
       </c>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1781,24 +1781,24 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>颗粒检测系统</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1809,31 +1809,31 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T09:27:59</t>
+          <t>2026-06-23T09:57:50</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1843,24 +1843,24 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1871,29 +1871,153 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T09:57:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>招标变更</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>变更/澄清</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T09:57:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>检测设备</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
           <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-421062373</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T09:27:59</t>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T09:57:50</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P22"/>
+  <autoFilter ref="A1:P24"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -1916,10 +2040,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId22"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId24"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1952,7 +2078,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-22T09:31:13</t>
+          <t>2026-06-23T10:16:01</t>
         </is>
       </c>
     </row>
@@ -1963,7 +2089,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -1985,7 +2111,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P24" headerRowCount="1">
-  <autoFilter ref="A1:P24"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P23" headerRowCount="1">
+  <autoFilter ref="A1:P23"/>
   <tableColumns count="16">
     <tableColumn id="1" name="项目名称"/>
     <tableColumn id="2" name="判断类别"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -593,7 +593,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>心脏自主神经功能多参数检测系统、体外冲击波治疗仪（立式）、射频治疗仪、808 半导体 激光治疗仪市场调研公告</t>
+          <t>采购 芯片 检测 AOI没备</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -603,24 +603,24 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>项目：心脏自主神经功能多参数检测系统、体外冲击波治疗仪（立式）、射频治疗仪、808 半导体 激光治疗仪市场调研公告；可见摘要：收藏 招标公告 江苏 22小时前；详情状态：受限，需人工核验</t>
+          <t>项目：采购 芯片 检测 AOI没备；可见摘要：收藏 采购信息 广东 2026-06-22；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -631,7 +631,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>采购信息</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -643,7 +643,7 @@
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426004539</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-426218961</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>采购 芯片 检测 AOI没备</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -665,24 +665,24 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>项目：采购 芯片 检测 AOI没备；可见摘要：收藏 采购信息 广东 2026-06-22；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -693,7 +693,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>采购信息</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -705,7 +705,7 @@
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-426218961</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425830318</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
     <row r="4" ht="58" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
@@ -755,19 +755,19 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425830318</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
+          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -789,17 +789,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
@@ -817,19 +817,19 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -841,7 +841,7 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目评标结果公示公告(1)-1069-264Z20261762</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目评标结果公示公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
@@ -884,14 +884,14 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425558679</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目评标结果公示公告(1)-1069-264Z20261762</t>
+          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目评标结果公示公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 18小时前；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
@@ -953,7 +953,7 @@
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425558679</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -965,7 +965,7 @@
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
+          <t>上海易启芯程 半导体 有限公司颗粒检测设备评标结果公示公告(1)-0613-264025122218</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -975,17 +975,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备评标结果公示公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 20小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
@@ -1015,7 +1015,7 @@
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425491184</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司颗粒检测设备评标结果公示公告(1)-0613-264025122218</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1037,24 +1037,24 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备评标结果公示公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 20小时前；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -1065,19 +1065,19 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425491184</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1099,24 +1099,24 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>外观检查机</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -1127,19 +1127,19 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1151,27 +1151,27 @@
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
+          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>膜厚仪</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
@@ -1189,19 +1189,19 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1213,34 +1213,34 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
+          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1251,19 +1251,19 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
+          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1285,24 +1285,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
+          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1325,7 +1325,7 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1337,7 +1337,7 @@
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1357,14 +1357,14 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1375,19 +1375,19 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1399,7 +1399,7 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
+          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1409,17 +1409,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>自动光学检查机</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
@@ -1437,19 +1437,19 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
+          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1471,24 +1471,24 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机</t>
+          <t>晶圆表面缺陷检测</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1511,7 +1511,7 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1533,24 +1533,24 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1561,19 +1561,19 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -1585,34 +1585,34 @@
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
+          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>CD-SEM</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1623,19 +1623,19 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -1647,34 +1647,34 @@
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
+          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM</t>
+          <t>外观检测</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1697,7 +1697,7 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -1709,7 +1709,7 @@
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
+          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1719,24 +1719,24 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>外观检测</t>
+          <t>颗粒检测系统</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1759,7 +1759,7 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
+          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
@@ -1809,19 +1809,19 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1843,24 +1843,24 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>外观检查机</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1883,7 +1883,7 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -1895,7 +1895,7 @@
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1905,17 +1905,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
@@ -1933,19 +1933,19 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-421062373</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -1954,70 +1954,8 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>光学检测设备</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>检测设备</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>采招网</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>中标结果</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>已出结果</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-421062373</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-23T09:57:50</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P24"/>
+  <autoFilter ref="A1:P23"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -2041,11 +1979,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId24"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId23"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2078,7 +2015,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-23T10:16:01</t>
+          <t>2026-06-23T10:18:41</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2026,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -2111,7 +2048,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P23" headerRowCount="1">
-  <autoFilter ref="A1:P23"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P24" headerRowCount="1">
+  <autoFilter ref="A1:P24"/>
   <tableColumns count="16">
     <tableColumn id="1" name="项目名称"/>
     <tableColumn id="2" name="判断类别"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -648,14 +648,14 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T09:57:50</t>
+          <t>2026-06-23T10:34:09</t>
         </is>
       </c>
     </row>
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -665,24 +665,24 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -705,19 +705,19 @@
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425830318</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T09:57:50</t>
+          <t>2026-06-23T10:34:09</t>
         </is>
       </c>
     </row>
     <row r="4" ht="58" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
@@ -755,31 +755,31 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425830318</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T09:57:50</t>
+          <t>2026-06-23T10:34:09</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -789,17 +789,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
@@ -817,31 +817,31 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T09:57:50</t>
+          <t>2026-06-23T10:34:09</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目评标结果公示公告(1)-1069-264Z20261762</t>
+          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目评标结果公示公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 18小时前；详情状态：受限，需人工核验</t>
+          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
@@ -884,26 +884,26 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425558679</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T09:57:50</t>
+          <t>2026-06-23T10:34:09</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目评标结果公示公告(1)-1069-264Z20261762</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目评标结果公示公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
@@ -953,19 +953,19 @@
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425558679</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T09:57:50</t>
+          <t>2026-06-23T10:34:09</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司颗粒检测设备评标结果公示公告(1)-0613-264025122218</t>
+          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -975,17 +975,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备评标结果公示公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 20小时前；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
@@ -1015,19 +1015,19 @@
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425491184</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T09:57:50</t>
+          <t>2026-06-23T10:34:09</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
+          <t>上海易启芯程 半导体 有限公司颗粒检测设备评标结果公示公告(1)-0613-264025122218</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1037,24 +1037,24 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备评标结果公示公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 20小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -1065,31 +1065,31 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425491184</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T09:57:50</t>
+          <t>2026-06-23T10:34:09</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1099,24 +1099,24 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -1127,51 +1127,51 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T09:57:50</t>
+          <t>2026-06-23T10:34:09</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪</t>
+          <t>外观检查机</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
@@ -1189,58 +1189,58 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T09:57:50</t>
+          <t>2026-06-23T10:34:09</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
+          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>膜厚仪</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1251,31 +1251,31 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T09:57:50</t>
+          <t>2026-06-23T10:34:09</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
+          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1285,24 +1285,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
+          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1325,19 +1325,19 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T09:57:50</t>
+          <t>2026-06-23T10:34:09</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
+          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1357,14 +1357,14 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
+          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1375,31 +1375,31 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T09:57:50</t>
+          <t>2026-06-23T10:34:09</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1409,17 +1409,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
@@ -1437,31 +1437,31 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T09:57:50</t>
+          <t>2026-06-23T10:34:09</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
+          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1471,24 +1471,24 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测</t>
+          <t>自动光学检查机</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1511,19 +1511,19 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T09:57:50</t>
+          <t>2026-06-23T10:34:09</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
+          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1533,24 +1533,24 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>晶圆表面缺陷检测</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
+          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1561,58 +1561,58 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T09:57:50</t>
+          <t>2026-06-23T10:34:09</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1623,58 +1623,58 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T09:57:50</t>
+          <t>2026-06-23T10:34:09</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
+          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>外观检测</t>
+          <t>CD-SEM</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1697,19 +1697,19 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T09:57:50</t>
+          <t>2026-06-23T10:34:09</t>
         </is>
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
+          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1719,24 +1719,24 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统</t>
+          <t>外观检测</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1759,19 +1759,19 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T09:57:50</t>
+          <t>2026-06-23T10:34:09</t>
         </is>
       </c>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>颗粒检测系统</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
@@ -1809,31 +1809,31 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T09:57:50</t>
+          <t>2026-06-23T10:34:09</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1843,24 +1843,24 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1883,19 +1883,19 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T09:57:50</t>
+          <t>2026-06-23T10:34:09</t>
         </is>
       </c>
     </row>
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1905,17 +1905,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>外观检查机</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
@@ -1933,29 +1933,91 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T10:34:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>检测设备</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
           <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-421062373</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-23T09:57:50</t>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T10:34:09</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P23"/>
+  <autoFilter ref="A1:P24"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -1979,10 +2041,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId23"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId24"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2015,7 +2078,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-23T10:18:41</t>
+          <t>2026-06-23T10:35:03</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2089,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -2048,7 +2111,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P24" headerRowCount="1">
-  <autoFilter ref="A1:P24"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P23" headerRowCount="1">
+  <autoFilter ref="A1:P23"/>
   <tableColumns count="16">
     <tableColumn id="1" name="项目名称"/>
     <tableColumn id="2" name="判断类别"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -593,7 +593,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>采购 芯片 检测 AOI没备</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -603,17 +603,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>项目：采购 芯片 检测 AOI没备；可见摘要：收藏 采购信息 广东 2026-06-22；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
@@ -631,7 +631,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>采购信息</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -643,7 +643,7 @@
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-426218961</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -665,24 +665,24 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -705,7 +705,7 @@
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425830318</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
     <row r="4" ht="58" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
@@ -755,19 +755,19 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425830318</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
+          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -789,17 +789,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
@@ -817,19 +817,19 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -841,7 +841,7 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目评标结果公示公告(1)-1069-264Z20261762</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目评标结果公示公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
@@ -884,14 +884,14 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425558679</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目评标结果公示公告(1)-1069-264Z20261762</t>
+          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目评标结果公示公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 18小时前；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
@@ -953,7 +953,7 @@
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425558679</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -965,7 +965,7 @@
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
+          <t>上海易启芯程 半导体 有限公司颗粒检测设备评标结果公示公告(1)-0613-264025122218</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -975,17 +975,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备评标结果公示公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 20小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
@@ -1015,7 +1015,7 @@
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425491184</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司颗粒检测设备评标结果公示公告(1)-0613-264025122218</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1037,24 +1037,24 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备评标结果公示公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 20小时前；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -1065,19 +1065,19 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425491184</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1099,24 +1099,24 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>外观检查机</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -1127,19 +1127,19 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1151,27 +1151,27 @@
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
+          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>膜厚仪</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
@@ -1189,19 +1189,19 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1213,34 +1213,34 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
+          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1251,19 +1251,19 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
+          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1285,24 +1285,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
+          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1325,7 +1325,7 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1337,7 +1337,7 @@
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1357,14 +1357,14 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1375,19 +1375,19 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1399,7 +1399,7 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
+          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1409,17 +1409,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>自动光学检查机</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
@@ -1437,19 +1437,19 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
+          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1471,24 +1471,24 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机</t>
+          <t>晶圆表面缺陷检测</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1511,7 +1511,7 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1533,24 +1533,24 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1561,19 +1561,19 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -1585,34 +1585,34 @@
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
+          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>CD-SEM</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1623,19 +1623,19 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -1647,34 +1647,34 @@
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
+          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM</t>
+          <t>外观检测</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1697,7 +1697,7 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -1709,7 +1709,7 @@
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
+          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1719,24 +1719,24 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>外观检测</t>
+          <t>颗粒检测系统</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1759,7 +1759,7 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
+          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
@@ -1809,19 +1809,19 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1843,24 +1843,24 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>外观检查机</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1883,7 +1883,7 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -1895,7 +1895,7 @@
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1905,17 +1905,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
@@ -1933,19 +1933,19 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-421062373</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -1954,70 +1954,8 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>光学检测设备</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>检测设备</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>采招网</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>中标结果</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>已出结果</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-421062373</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-23T10:34:09</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P24"/>
+  <autoFilter ref="A1:P23"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -2041,11 +1979,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId24"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId23"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2078,7 +2015,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-23T10:35:03</t>
+          <t>2026-06-23T10:42:34</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2026,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -2111,7 +2048,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T10:34:09</t>
+          <t>2026-06-24T09:30:17</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T10:34:09</t>
+          <t>2026-06-24T09:30:17</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T10:34:09</t>
+          <t>2026-06-24T09:30:17</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T10:34:09</t>
+          <t>2026-06-24T09:30:17</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T10:34:09</t>
+          <t>2026-06-24T09:30:17</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T10:34:09</t>
+          <t>2026-06-24T09:30:17</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T10:34:09</t>
+          <t>2026-06-24T09:30:17</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T10:34:09</t>
+          <t>2026-06-24T09:30:17</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T10:34:09</t>
+          <t>2026-06-24T09:30:17</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T10:34:09</t>
+          <t>2026-06-24T09:30:17</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T10:34:09</t>
+          <t>2026-06-24T09:30:17</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T10:34:09</t>
+          <t>2026-06-24T09:30:17</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T10:34:09</t>
+          <t>2026-06-24T09:30:17</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T10:34:09</t>
+          <t>2026-06-24T09:30:17</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T10:34:09</t>
+          <t>2026-06-24T09:30:17</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T10:34:09</t>
+          <t>2026-06-24T09:30:17</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T10:34:09</t>
+          <t>2026-06-24T09:30:17</t>
         </is>
       </c>
     </row>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T10:34:09</t>
+          <t>2026-06-24T09:30:17</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T10:34:09</t>
+          <t>2026-06-24T09:30:17</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T10:34:09</t>
+          <t>2026-06-24T09:30:17</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T10:34:09</t>
+          <t>2026-06-24T09:30:17</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T10:34:09</t>
+          <t>2026-06-24T09:30:17</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-23T10:42:34</t>
+          <t>2026-06-24T11:10:56</t>
         </is>
       </c>
     </row>

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -2015,7 +2015,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-24T11:10:56</t>
+          <t>2026-06-24T11:15:52</t>
         </is>
       </c>
     </row>

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P23" headerRowCount="1">
-  <autoFilter ref="A1:P23"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P24" headerRowCount="1">
+  <autoFilter ref="A1:P24"/>
   <tableColumns count="16">
     <tableColumn id="1" name="项目名称"/>
     <tableColumn id="2" name="判断类别"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -593,7 +593,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -603,24 +603,24 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告；可见摘要：附件 收藏 中标结果 上海 2026-06-24；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -631,31 +631,31 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426498852</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T09:30:17</t>
+          <t>2026-06-25T09:38:40</t>
         </is>
       </c>
     </row>
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -665,24 +665,24 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -693,31 +693,31 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425830318</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426408417</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T09:30:17</t>
+          <t>2026-06-25T09:38:40</t>
         </is>
       </c>
     </row>
     <row r="4" ht="58" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
+          <t>上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -727,24 +727,24 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -755,31 +755,31 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426280043</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T09:30:17</t>
+          <t>2026-06-25T09:38:40</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -789,24 +789,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -817,7 +817,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -829,19 +829,19 @@
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T09:30:17</t>
+          <t>2026-06-25T09:38:40</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目评标结果公示公告(1)-1069-264Z20261762</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -851,17 +851,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目评标结果公示公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 18小时前；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
@@ -879,31 +879,31 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425558679</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425830318</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T09:30:17</t>
+          <t>2026-06-25T09:38:40</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -913,17 +913,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
@@ -941,31 +941,31 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T09:30:17</t>
+          <t>2026-06-25T09:38:40</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司颗粒检测设备评标结果公示公告(1)-0613-264025122218</t>
+          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -975,17 +975,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备评标结果公示公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 20小时前；详情状态：受限，需人工核验</t>
+          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
@@ -1008,26 +1008,26 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425491184</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T09:30:17</t>
+          <t>2026-06-25T09:38:40</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
+          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1037,24 +1037,24 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -1065,31 +1065,31 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T09:30:17</t>
+          <t>2026-06-25T09:38:40</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1099,24 +1099,24 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -1127,51 +1127,51 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T09:30:17</t>
+          <t>2026-06-25T09:38:40</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪</t>
+          <t>外观检查机</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
@@ -1189,58 +1189,58 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T09:30:17</t>
+          <t>2026-06-25T09:38:40</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
+          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>膜厚仪</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1251,31 +1251,31 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T09:30:17</t>
+          <t>2026-06-25T09:38:40</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
+          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1285,24 +1285,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
+          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1325,19 +1325,19 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T09:30:17</t>
+          <t>2026-06-25T09:38:40</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
+          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1357,14 +1357,14 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
+          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1375,31 +1375,31 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T09:30:17</t>
+          <t>2026-06-25T09:38:40</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1409,17 +1409,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
@@ -1437,31 +1437,31 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T09:30:17</t>
+          <t>2026-06-25T09:38:40</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
+          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1471,24 +1471,24 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测</t>
+          <t>自动光学检查机</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1511,19 +1511,19 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T09:30:17</t>
+          <t>2026-06-25T09:38:40</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
+          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1533,24 +1533,24 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>晶圆表面缺陷检测</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
+          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1561,58 +1561,58 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T09:30:17</t>
+          <t>2026-06-25T09:38:40</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1623,58 +1623,58 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T09:30:17</t>
+          <t>2026-06-25T09:38:40</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
+          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>外观检测</t>
+          <t>CD-SEM</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1697,19 +1697,19 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T09:30:17</t>
+          <t>2026-06-25T09:38:40</t>
         </is>
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
+          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1719,24 +1719,24 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统</t>
+          <t>外观检测</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1759,19 +1759,19 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T09:30:17</t>
+          <t>2026-06-25T09:38:40</t>
         </is>
       </c>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>颗粒检测系统</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
@@ -1809,31 +1809,31 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T09:30:17</t>
+          <t>2026-06-25T09:38:40</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1843,24 +1843,24 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1883,19 +1883,19 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T09:30:17</t>
+          <t>2026-06-25T09:38:40</t>
         </is>
       </c>
     </row>
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1905,17 +1905,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>外观检查机</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
@@ -1933,29 +1933,91 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T09:38:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>检测设备</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
           <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-421062373</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-24T09:30:17</t>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T09:38:40</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P23"/>
+  <autoFilter ref="A1:P24"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -1979,10 +2041,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId23"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId24"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2015,7 +2078,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-24T11:15:52</t>
+          <t>2026-06-25T11:10:07</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2089,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -2048,7 +2111,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P24" headerRowCount="1">
-  <autoFilter ref="A1:P24"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P25" headerRowCount="1">
+  <autoFilter ref="A1:P25"/>
   <tableColumns count="16">
     <tableColumn id="1" name="项目名称"/>
     <tableColumn id="2" name="判断类别"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -1585,45 +1585,49 @@
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
+          <t>缺陷检测仪【重新招标】-公开招标公告</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr"/>
+          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>无锡中微掩模电子有限公司</t>
+        </is>
+      </c>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>公开招标公告</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -1635,46 +1639,46 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
+          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T09:38:40</t>
+          <t>2026-06-10T14:16:35</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1685,19 +1689,19 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -1709,34 +1713,34 @@
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
+          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>外观检测</t>
+          <t>CD-SEM</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1759,7 +1763,7 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -1771,7 +1775,7 @@
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
+          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1781,24 +1785,24 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统</t>
+          <t>外观检测</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1821,7 +1825,7 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -1833,7 +1837,7 @@
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1843,17 +1847,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>颗粒检测系统</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
@@ -1871,19 +1875,19 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -1895,7 +1899,7 @@
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1905,24 +1909,24 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1945,7 +1949,7 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -1957,7 +1961,7 @@
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1967,17 +1971,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>外观检查机</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
@@ -1995,29 +1999,91 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T09:38:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>检测设备</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
           <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-421062373</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>2026-06-25T09:38:40</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P24"/>
+  <autoFilter ref="A1:P25"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -2042,10 +2108,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId24"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId25"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2056,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2078,7 +2145,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-25T11:10:07</t>
+          <t>2026-06-25T14:54:21</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2156,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -2112,6 +2179,16 @@
       </c>
       <c r="B7" t="n">
         <v>23</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>中招联合</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P25" headerRowCount="1">
-  <autoFilter ref="A1:P25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P28" headerRowCount="1">
+  <autoFilter ref="A1:P28"/>
   <tableColumns count="16">
     <tableColumn id="1" name="项目名称"/>
     <tableColumn id="2" name="判断类别"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -593,34 +593,34 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告</t>
+          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告；可见摘要：附件 收藏 中标结果 上海 2026-06-24；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -631,58 +631,58 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426498852</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426951671</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T09:38:40</t>
+          <t>2026-06-26T10:48:10</t>
         </is>
       </c>
     </row>
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762</t>
+          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396；可见摘要：收藏 招标公告 上海 12小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -693,93 +693,97 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426408417</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426983145</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T09:38:40</t>
+          <t>2026-06-26T10:48:10</t>
         </is>
       </c>
     </row>
     <row r="4" ht="58" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218</t>
+          <t>谈判采购公告</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测</t>
+          <t>CIM系统</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>RMS，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
+          <t>采购内容：CIM系统；数量：一家；范围：CIM系统设备采购及有关技术服务、培训等，具体要求详见第五章采购需求；采购方：成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采；公告类型：采购公告；发布时间：2026-06-25</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>采购公告</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426280043</t>
+          <t>https://www.365trade.com.cn/zhwzb/837713.jhtml</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T09:38:40</t>
+          <t>2026-06-26T10:51:21</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -789,24 +793,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告；可见摘要：附件 收藏 中标结果 上海 2026-06-24；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -817,31 +821,31 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426498852</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T09:38:40</t>
+          <t>2026-06-26T10:48:10</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -851,24 +855,24 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -879,31 +883,31 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425830318</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426408417</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T09:38:40</t>
+          <t>2026-06-26T10:48:10</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
+          <t>上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -913,24 +917,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -941,31 +945,31 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426280043</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T09:38:40</t>
+          <t>2026-06-26T10:48:10</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -975,24 +979,24 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -1003,7 +1007,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1015,19 +1019,19 @@
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T09:38:40</t>
+          <t>2026-06-26T10:48:10</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1037,17 +1041,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
@@ -1065,31 +1069,31 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425830318</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T09:38:40</t>
+          <t>2026-06-26T10:48:10</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1099,24 +1103,24 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -1127,31 +1131,31 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T09:38:40</t>
+          <t>2026-06-26T10:48:10</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
+          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1161,24 +1165,24 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1194,53 +1198,53 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T09:38:40</t>
+          <t>2026-06-26T10:48:10</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
+          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1251,31 +1255,31 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T09:38:40</t>
+          <t>2026-06-26T10:48:10</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1285,24 +1289,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1313,31 +1317,31 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T09:38:40</t>
+          <t>2026-06-26T10:48:10</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1347,24 +1351,24 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>外观检查机</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1387,46 +1391,46 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T09:38:40</t>
+          <t>2026-06-26T10:48:10</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
+          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>膜厚仪</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1437,7 +1441,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1449,19 +1453,19 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T09:38:40</t>
+          <t>2026-06-26T10:48:10</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
+          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1471,24 +1475,24 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1511,19 +1515,19 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T09:38:40</t>
+          <t>2026-06-26T10:48:10</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
+          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1533,24 +1537,24 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
+          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1573,61 +1577,57 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T09:38:40</t>
+          <t>2026-06-26T10:48:10</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪【重新招标】-公开招标公告</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>无锡中微掩模电子有限公司</t>
-        </is>
-      </c>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>公开招标公告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -1639,19 +1639,19 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10T14:16:35</t>
+          <t>2026-06-26T10:48:10</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
+          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1661,24 +1661,24 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>自动光学检查机</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1689,58 +1689,58 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T09:38:40</t>
+          <t>2026-06-26T10:48:10</t>
         </is>
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
+          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM</t>
+          <t>晶圆表面缺陷检测</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
+          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1763,81 +1763,85 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T09:38:40</t>
+          <t>2026-06-26T10:48:10</t>
         </is>
       </c>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
+          <t>缺陷检测仪【重新招标】-公开招标公告</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>外观检测</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr"/>
+          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>无锡中微掩模电子有限公司</t>
+        </is>
+      </c>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>公开招标公告</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
+          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T09:38:40</t>
+          <t>2026-06-10T14:16:35</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1847,24 +1851,24 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1875,58 +1879,58 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T09:38:40</t>
+          <t>2026-06-26T10:48:10</t>
         </is>
       </c>
     </row>
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>CD-SEM</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1937,31 +1941,31 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T09:38:40</t>
+          <t>2026-06-26T10:48:10</t>
         </is>
       </c>
     </row>
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1971,24 +1975,24 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>外观检测</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1999,31 +2003,31 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T09:38:40</t>
+          <t>2026-06-26T10:48:10</t>
         </is>
       </c>
     </row>
     <row r="25" ht="58" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -2033,24 +2037,24 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>颗粒检测系统</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -2073,17 +2077,203 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26T10:48:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>检测仪</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>招标变更</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>变更/澄清</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26T10:48:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>招标变更</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>变更/澄清</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26T10:48:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>检测设备</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
           <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-421062373</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-25T09:38:40</t>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26T10:48:10</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P25"/>
+  <autoFilter ref="A1:P28"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -2109,10 +2299,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId25"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId28"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2145,7 +2338,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-25T14:54:21</t>
+          <t>2026-06-26T10:51:22</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2349,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -2178,7 +2371,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
@@ -2188,7 +2381,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P28" headerRowCount="1">
-  <autoFilter ref="A1:P28"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P36" headerRowCount="1">
+  <autoFilter ref="A1:P36"/>
   <tableColumns count="16">
     <tableColumn id="1" name="项目名称"/>
     <tableColumn id="2" name="判断类别"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -593,34 +593,34 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告；可见摘要：收藏 招标公告 河北 22分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -643,46 +643,46 @@
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426951671</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427329545</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:48:10</t>
+          <t>2026-06-29T10:31:52</t>
         </is>
       </c>
     </row>
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396；可见摘要：收藏 招标公告 上海 12小时前；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告；可见摘要：附件 收藏 招标变更 河北 2026-06-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -693,73 +693,69 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>终止/流标</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426983145</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427255950</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:48:10</t>
+          <t>2026-06-29T10:31:52</t>
         </is>
       </c>
     </row>
     <row r="4" ht="58" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>谈判采购公告</t>
+          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>CIM系统</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>RMS，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>采购内容：CIM系统；数量：一家；范围：CIM系统设备采购及有关技术服务、培训等，具体要求详见第五章采购需求；采购方：成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采；公告类型：采购公告；发布时间：2026-06-25</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采</t>
-        </is>
-      </c>
+          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)；可见摘要：收藏 招标预告 上海 2026-06-27；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>采购公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -771,19 +767,19 @@
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/837713.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427280358</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:51:21</t>
+          <t>2026-06-29T10:31:52</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告</t>
+          <t>生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -793,24 +789,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告；可见摘要：附件 收藏 中标结果 上海 2026-06-24；详情状态：受限，需人工核验</t>
+          <t>项目：生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告；可见摘要：收藏 招标公告 江苏 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -821,31 +817,31 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426498852</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427124669</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:48:10</t>
+          <t>2026-06-29T10:31:52</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -855,24 +851,24 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>缺陷检测</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告；可见摘要：附件 收藏 招标公告 安徽 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -883,31 +879,31 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426408417</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427174343</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:48:10</t>
+          <t>2026-06-29T10:31:52</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -917,24 +913,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告；可见摘要：标书 收藏 中标结果 北京 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -957,46 +953,46 @@
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426280043</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-427191692</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:48:10</t>
+          <t>2026-06-29T10:31:52</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
+          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -1019,46 +1015,46 @@
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426951671</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:48:10</t>
+          <t>2026-06-29T10:31:52</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202</t>
+          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396；可见摘要：收藏 招标公告 上海 12小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -1081,19 +1077,19 @@
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425830318</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426983145</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:48:10</t>
+          <t>2026-06-29T10:31:52</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
+          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1103,24 +1099,24 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器；可见摘要：收藏 招标预告 上海 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -1131,31 +1127,31 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427096376</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:48:10</t>
+          <t>2026-06-29T10:31:52</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
+          <t>2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1175,14 +1171,14 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14；可见摘要：收藏 招标公告 浙江 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1193,7 +1189,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1205,81 +1201,85 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427057182</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:48:10</t>
+          <t>2026-06-29T10:31:52</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
+          <t>谈判采购公告</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>CIM系统</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>RMS，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr"/>
+          <t>采购内容：CIM系统；数量：一家；范围：CIM系统设备采购及有关技术服务、培训等，具体要求详见第五章采购需求；采购方：成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采；公告类型：采购公告；发布时间：2026-06-25</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>采购公告</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
+          <t>https://www.365trade.com.cn/zhwzb/837713.jhtml</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:48:10</t>
+          <t>2026-06-26T10:51:21</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1289,24 +1289,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告；可见摘要：附件 收藏 中标结果 上海 2026-06-24；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1317,31 +1317,31 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426498852</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:48:10</t>
+          <t>2026-06-29T10:31:52</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1391,46 +1391,46 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426408417</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:48:10</t>
+          <t>2026-06-29T10:31:52</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
+          <t>上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1441,31 +1441,31 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426280043</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:48:10</t>
+          <t>2026-06-29T10:31:52</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1475,24 +1475,24 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1503,31 +1503,31 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:48:10</t>
+          <t>2026-06-29T10:31:52</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1547,14 +1547,14 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1565,31 +1565,31 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425830318</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:48:10</t>
+          <t>2026-06-29T10:31:52</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1609,14 +1609,14 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1627,31 +1627,31 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:48:10</t>
+          <t>2026-06-29T10:31:52</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
+          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1661,24 +1661,24 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1694,26 +1694,26 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:48:10</t>
+          <t>2026-06-29T10:31:52</t>
         </is>
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
+          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1723,24 +1723,24 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1763,24 +1763,24 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:48:10</t>
+          <t>2026-06-29T10:31:52</t>
         </is>
       </c>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪【重新招标】-公开招标公告</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1790,34 +1790,30 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>无锡中微掩模电子有限公司</t>
-        </is>
-      </c>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>公开招标公告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -1829,19 +1825,19 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10T14:16:35</t>
+          <t>2026-06-29T10:31:52</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1851,24 +1847,24 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>外观检查机</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1879,31 +1875,31 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:48:10</t>
+          <t>2026-06-29T10:31:52</t>
         </is>
       </c>
     </row>
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
+          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1913,24 +1909,24 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM</t>
+          <t>膜厚仪</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1941,31 +1937,31 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:48:10</t>
+          <t>2026-06-29T10:31:52</t>
         </is>
       </c>
     </row>
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
+          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1975,24 +1971,24 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>外观检测</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
+          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -2015,19 +2011,19 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:48:10</t>
+          <t>2026-06-29T10:31:52</t>
         </is>
       </c>
     </row>
     <row r="25" ht="58" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
+          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -2037,24 +2033,24 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -2077,19 +2073,19 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:48:10</t>
+          <t>2026-06-29T10:31:52</t>
         </is>
       </c>
     </row>
     <row r="26" ht="58" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -2099,24 +2095,24 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -2127,31 +2123,31 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:48:10</t>
+          <t>2026-06-29T10:31:52</t>
         </is>
       </c>
     </row>
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -2161,24 +2157,24 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>自动光学检查机</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -2189,31 +2185,31 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:48:10</t>
+          <t>2026-06-29T10:31:52</t>
         </is>
       </c>
     </row>
     <row r="28" ht="58" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2223,24 +2219,24 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>晶圆表面缺陷检测</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -2263,17 +2259,517 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="3" t="inlineStr">
         <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T10:31:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>缺陷检测仪【重新招标】-公开招标公告</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>半导体检测/量测设备</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>缺陷检测仪</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>缺陷检测，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>无锡中微掩模电子有限公司</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>中招联合</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>公开招标公告</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>进行中/未知</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10T14:16:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>检测仪</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>招标公告</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>进行中/未知</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T10:31:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>光学量测设备</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>CD-SEM</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T10:31:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>外观检测</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T10:31:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>颗粒检测系统</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T10:31:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>检测仪</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>招标变更</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>变更/澄清</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T10:31:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>招标变更</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>变更/澄清</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T10:31:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>检测设备</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
           <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-421062373</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-26T10:48:10</t>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T10:31:52</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P28"/>
+  <autoFilter ref="A1:P36"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -2302,10 +2798,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId28"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId36"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2338,7 +2842,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-26T10:51:22</t>
+          <t>2026-06-29T10:34:53</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2853,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -2371,7 +2875,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8">

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P36" headerRowCount="1">
-  <autoFilter ref="A1:P36"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P38" headerRowCount="1">
+  <autoFilter ref="A1:P38"/>
   <tableColumns count="16">
     <tableColumn id="1" name="项目名称"/>
     <tableColumn id="2" name="判断类别"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P36"/>
+  <dimension ref="A1:P38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -593,7 +593,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -603,24 +603,24 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告；可见摘要：收藏 招标公告 河北 22分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -643,19 +643,19 @@
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427329545</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434578</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -665,24 +665,24 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告；可见摘要：附件 收藏 招标变更 河北 2026-06-27；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -693,31 +693,31 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>终止/流标</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427255950</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434575</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="4" ht="58" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -727,24 +727,24 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)；可见摘要：收藏 招标预告 上海 2026-06-27；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告；可见摘要：收藏 招标公告 河北 22分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -767,19 +767,19 @@
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427280358</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427329545</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -789,24 +789,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>项目：生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告；可见摘要：收藏 招标公告 江苏 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告；可见摘要：附件 收藏 招标变更 河北 2026-06-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -817,31 +817,31 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>终止/流标</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427124669</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427255950</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告</t>
+          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -851,24 +851,24 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告；可见摘要：附件 收藏 招标公告 安徽 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)；可见摘要：收藏 招标预告 上海 2026-06-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -879,7 +879,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -891,19 +891,19 @@
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427174343</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427280358</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告</t>
+          <t>生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -913,17 +913,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告；可见摘要：标书 收藏 中标结果 北京 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告；可见摘要：收藏 招标公告 江苏 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
@@ -941,51 +941,51 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-427191692</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427124669</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>缺陷检测</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告；可见摘要：附件 收藏 招标公告 安徽 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
@@ -1015,39 +1015,39 @@
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426951671</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427174343</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396；可见摘要：收藏 招标公告 上海 12小时前；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告；可见摘要：标书 收藏 中标结果 北京 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
@@ -1065,51 +1065,51 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426983145</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-427191692</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器</t>
+          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器；可见摘要：收藏 招标预告 上海 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1139,39 +1139,39 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427096376</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426951671</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14</t>
+          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>项目：2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14；可见摘要：收藏 招标公告 浙江 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396；可见摘要：收藏 招标公告 上海 12小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
@@ -1201,61 +1201,57 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427057182</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426983145</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>谈判采购公告</t>
+          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>CIM系统</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>RMS，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>采购内容：CIM系统；数量：一家；范围：CIM系统设备采购及有关技术服务、培训等，具体要求详见第五章采购需求；采购方：成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采；公告类型：采购公告；发布时间：2026-06-25</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采</t>
-        </is>
-      </c>
+          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器；可见摘要：收藏 招标预告 上海 2026-06-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>采购公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1267,19 +1263,19 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/837713.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427096376</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:51:21</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告</t>
+          <t>2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1299,14 +1295,14 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告；可见摘要：附件 收藏 中标结果 上海 2026-06-24；详情状态：受限，需人工核验</t>
+          <t>项目：2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14；可见摘要：收藏 招标公告 浙江 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1317,93 +1313,97 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426498852</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427057182</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762</t>
+          <t>谈判采购公告</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>CIM系统</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>RMS，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr"/>
+          <t>采购内容：CIM系统；数量：一家；范围：CIM系统设备采购及有关技术服务、培训等，具体要求详见第五章采购需求；采购方：成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采；公告类型：采购公告；发布时间：2026-06-25</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采</t>
+        </is>
+      </c>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>采购公告</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426408417</t>
+          <t>https://www.365trade.com.cn/zhwzb/837713.jhtml</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-26T10:51:21</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1413,24 +1413,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告；可见摘要：附件 收藏 中标结果 上海 2026-06-24；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1453,19 +1453,19 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426280043</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426498852</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1475,24 +1475,24 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1503,31 +1503,31 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426408417</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202</t>
+          <t>上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1537,24 +1537,24 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1565,31 +1565,31 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425830318</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426280043</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1599,24 +1599,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1627,31 +1627,31 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1701,19 +1701,19 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425830318</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1723,17 +1723,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
@@ -1751,31 +1751,31 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
+          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1785,24 +1785,24 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -1825,19 +1825,19 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
+          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1847,24 +1847,24 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1887,46 +1887,46 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -1949,19 +1949,19 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1971,24 +1971,24 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>外观检查机</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -2011,46 +2011,46 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="25" ht="58" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
+          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>膜厚仪</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -2061,31 +2061,31 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="26" ht="58" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
+          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -2095,24 +2095,24 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
+          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -2123,31 +2123,31 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
+          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -2157,24 +2157,24 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -2197,19 +2197,19 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="28" ht="58" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2219,24 +2219,24 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -2247,97 +2247,93 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="29" ht="58" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪【重新招标】-公开招标公告</t>
+          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>自动光学检查机</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测，且公告具有半导体产业链语境</t>
+          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>无锡中微掩模电子有限公司</t>
-        </is>
-      </c>
+          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>公开招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10T14:16:35</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
+          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2347,24 +2343,24 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>晶圆表面缺陷检测</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
+          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -2375,93 +2371,97 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="31" ht="58" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
+          <t>缺陷检测仪【重新招标】-公开招标公告</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr"/>
+          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>无锡中微掩模电子有限公司</t>
+        </is>
+      </c>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>公开招标公告</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
+          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-10T14:16:35</t>
         </is>
       </c>
     </row>
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2471,24 +2471,24 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>外观检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2499,58 +2499,58 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="33" ht="58" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
+          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统</t>
+          <t>CD-SEM</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2573,19 +2573,19 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="34" ht="58" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2595,24 +2595,24 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>外观检测</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2623,31 +2623,31 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="35" ht="58" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2657,24 +2657,24 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>颗粒检测系统</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2685,31 +2685,31 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29T10:31:52</t>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
     <row r="36" ht="58" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2719,24 +2719,24 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2747,29 +2747,153 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T09:20:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>招标变更</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>变更/澄清</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T09:20:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>检测设备</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
           <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-421062373</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29T10:31:52</t>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T09:20:18</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P36"/>
+  <autoFilter ref="A1:P38"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -2806,10 +2930,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId36"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId38"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2842,7 +2968,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-29T10:34:53</t>
+          <t>2026-06-30T09:24:45</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2979,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
@@ -2875,7 +3001,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:20:18</t>
+          <t>2026-07-01T09:35:44</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-30T09:24:45</t>
+          <t>2026-07-01T10:00:38</t>
         </is>
       </c>
     </row>

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T09:35:44</t>
+          <t>2026-07-02T09:52:53</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-01T10:00:38</t>
+          <t>2026-07-02T09:55:43</t>
         </is>
       </c>
     </row>

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02T09:52:53</t>
+          <t>2026-07-03T09:18:02</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-02T09:55:43</t>
+          <t>2026-07-03T09:22:01</t>
         </is>
       </c>
     </row>

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P38" headerRowCount="1">
-  <autoFilter ref="A1:P38"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P43" headerRowCount="1">
+  <autoFilter ref="A1:P43"/>
   <tableColumns count="16">
     <tableColumn id="1" name="项目名称"/>
     <tableColumn id="2" name="判断类别"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P38"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -593,7 +593,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -603,24 +603,24 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告；可见摘要：收藏 招标变更 河北 2026-07-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -631,31 +631,31 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>终止/流标</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434578</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428711615</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告</t>
+          <t>纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -665,24 +665,24 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
+          <t>项目：纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告；可见摘要：收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -705,46 +705,46 @@
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434575</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428537526</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="4" ht="58" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告</t>
+          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告；可见摘要：收藏 招标公告 河北 22分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -755,58 +755,58 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427329545</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419989</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告</t>
+          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告；可见摘要：附件 收藏 招标变更 河北 2026-06-27；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -822,26 +822,26 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>终止/流标</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427255950</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419915</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)</t>
+          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -861,14 +861,14 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)；可见摘要：收藏 招标预告 上海 2026-06-27；详情状态：受限，需人工核验</t>
+          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告；可见摘要：附件 收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -879,7 +879,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -891,19 +891,19 @@
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427280358</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428541747</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -913,24 +913,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>项目：生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告；可见摘要：收藏 招标公告 江苏 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -953,19 +953,19 @@
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427124669</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434578</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -975,24 +975,24 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告；可见摘要：附件 收藏 招标公告 安徽 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -1015,19 +1015,19 @@
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427174343</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434575</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1037,24 +1037,24 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告；可见摘要：标书 收藏 中标结果 北京 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告；可见摘要：收藏 招标公告 河北 22分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -1065,58 +1065,58 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-427191692</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427329545</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告；可见摘要：附件 收藏 招标变更 河北 2026-06-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -1127,58 +1127,58 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>终止/流标</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426951671</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427255950</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396</t>
+          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396；可见摘要：收藏 招标公告 上海 12小时前；详情状态：受限，需人工核验</t>
+          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)；可见摘要：收藏 招标预告 上海 2026-06-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1201,19 +1201,19 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426983145</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427280358</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器</t>
+          <t>生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1223,17 +1223,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器；可见摘要：收藏 招标预告 上海 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告；可见摘要：收藏 招标公告 江苏 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1263,19 +1263,19 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427096376</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427124669</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>缺陷检测</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>项目：2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14；可见摘要：收藏 招标公告 浙江 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告；可见摘要：附件 收藏 招标公告 安徽 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
@@ -1325,112 +1325,108 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427057182</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427174343</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>谈判采购公告</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>CIM系统</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>RMS，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>采购内容：CIM系统；数量：一家；范围：CIM系统设备采购及有关技术服务、培训等，具体要求详见第五章采购需求；采购方：成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采；公告类型：采购公告；发布时间：2026-06-25</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采</t>
-        </is>
-      </c>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告；可见摘要：标书 收藏 中标结果 北京 2026-06-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>采购公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/837713.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-427191692</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:51:21</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告</t>
+          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告；可见摘要：附件 收藏 中标结果 上海 2026-06-24；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1441,58 +1437,58 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426498852</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426951671</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762</t>
+          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396；可见摘要：收藏 招标公告 上海 12小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1503,31 +1499,31 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426408417</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426983145</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218</t>
+          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1537,24 +1533,24 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
+          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器；可见摘要：收藏 招标预告 上海 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1565,31 +1561,31 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426280043</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427096376</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
+          <t>2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1599,24 +1595,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
+          <t>项目：2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14；可见摘要：收藏 招标公告 浙江 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1639,57 +1635,61 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427057182</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202</t>
+          <t>谈判采购公告</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>CIM系统</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>RMS，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-18；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr"/>
+          <t>采购内容：CIM系统；数量：一家；范围：CIM系统设备采购及有关技术服务、培训等，具体要求详见第五章采购需求；采购方：成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采；公告类型：采购公告；发布时间：2026-06-25</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采</t>
+        </is>
+      </c>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>采购公告</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1701,19 +1701,19 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425830318</t>
+          <t>https://www.365trade.com.cn/zhwzb/837713.jhtml</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-06-26T10:51:21</t>
         </is>
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1723,24 +1723,24 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告；可见摘要：附件 收藏 中标结果 上海 2026-06-24；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1751,31 +1751,31 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426498852</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1795,14 +1795,14 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1818,26 +1818,26 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426408417</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
+          <t>上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1847,24 +1847,24 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1887,19 +1887,19 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426280043</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1909,24 +1909,24 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1949,19 +1949,19 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1971,24 +1971,24 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1999,58 +1999,58 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425830318</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="25" ht="58" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -2061,31 +2061,31 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="26" ht="58" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
+          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -2095,24 +2095,24 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
+          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -2128,26 +2128,26 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
+          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -2157,24 +2157,24 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -2197,19 +2197,19 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="28" ht="58" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2219,24 +2219,24 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -2259,19 +2259,19 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="29" ht="58" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机</t>
+          <t>外观检查机</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -2321,46 +2321,46 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
+          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测</t>
+          <t>膜厚仪</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -2371,97 +2371,93 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="31" ht="58" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪【重新招标】-公开招标公告</t>
+          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>无锡中微掩模电子有限公司</t>
-        </is>
-      </c>
+          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>公开招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10T14:16:35</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
+          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2471,24 +2467,24 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
+          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2499,58 +2495,58 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="33" ht="58" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2561,31 +2557,31 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="34" ht="58" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
+          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2595,24 +2591,24 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>外观检测</t>
+          <t>自动光学检查机</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2635,19 +2631,19 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="35" ht="58" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
+          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2657,24 +2653,24 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统</t>
+          <t>晶圆表面缺陷检测</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2697,81 +2693,85 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="36" ht="58" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+          <t>缺陷检测仪【重新招标】-公开招标公告</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr"/>
+          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>无锡中微掩模电子有限公司</t>
+        </is>
+      </c>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>公开招标公告</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-06-10T14:16:35</t>
         </is>
       </c>
     </row>
     <row r="37" ht="58" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2781,24 +2781,24 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2809,58 +2809,58 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T09:18:02</t>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
     <row r="38" ht="58" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>CD-SEM</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2883,17 +2883,327 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="3" t="inlineStr">
         <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06T10:03:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>外观检测</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06T10:03:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="58" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>颗粒检测系统</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06T10:03:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="58" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>检测仪</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>招标变更</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>变更/澄清</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06T10:03:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="58" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>招标变更</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>变更/澄清</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06T10:03:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="58" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>检测设备</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
           <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-421062373</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-03T09:18:02</t>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06T10:03:04</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P38"/>
+  <autoFilter ref="A1:P43"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -2932,10 +3242,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId38"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId43"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2968,7 +3283,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-03T09:22:01</t>
+          <t>2026-07-06T10:05:53</t>
         </is>
       </c>
     </row>
@@ -2979,7 +3294,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
@@ -3001,7 +3316,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -3074,7 +3074,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T10:03:04</t>
+          <t>2026-07-07T15:01:54</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-06T10:05:53</t>
+          <t>2026-07-07T15:04:58</t>
         </is>
       </c>
     </row>

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -3074,7 +3074,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T15:01:54</t>
+          <t>2026-07-08T09:54:55</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-07T15:04:58</t>
+          <t>2026-07-08T09:59:36</t>
         </is>
       </c>
     </row>

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P43" headerRowCount="1">
-  <autoFilter ref="A1:P43"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P45" headerRowCount="1">
+  <autoFilter ref="A1:P45"/>
   <tableColumns count="16">
     <tableColumn id="1" name="项目名称"/>
     <tableColumn id="2" name="判断类别"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P43"/>
+  <dimension ref="A1:P45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -593,7 +593,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告</t>
+          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -603,24 +603,24 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告；可见摘要：收藏 招标变更 河北 2026-07-05；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -631,31 +631,31 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>终止/流标</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428711615</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429404126</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告</t>
+          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -665,24 +665,24 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>项目：纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告；可见摘要：收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)；可见摘要：收藏 招标公告 上海 2026-07-08；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -705,46 +705,46 @@
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428537526</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429489269</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="4" ht="58" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告；可见摘要：收藏 招标变更 河北 2026-07-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -760,46 +760,46 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>终止/流标</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419989</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428711615</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396</t>
+          <t>纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告；可见摘要：收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
@@ -817,51 +817,51 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419915</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428537526</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告</t>
+          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告；可见摘要：附件 收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
@@ -879,58 +879,58 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428541747</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419989</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告</t>
+          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -941,31 +941,31 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434578</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419915</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告</t>
+          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -975,24 +975,24 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
+          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告；可见摘要：附件 收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -1015,19 +1015,19 @@
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434575</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428541747</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1037,24 +1037,24 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告；可见摘要：收藏 招标公告 河北 22分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -1077,19 +1077,19 @@
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427329545</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434578</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1099,24 +1099,24 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告；可见摘要：附件 收藏 招标变更 河北 2026-06-27；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -1127,31 +1127,31 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>终止/流标</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427255950</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434575</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)；可见摘要：收藏 招标预告 上海 2026-06-27；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告；可见摘要：收藏 招标公告 河北 22分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1201,19 +1201,19 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427280358</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427329545</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1223,24 +1223,24 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>项目：生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告；可见摘要：收藏 招标公告 江苏 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告；可见摘要：附件 收藏 招标变更 河北 2026-06-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1251,31 +1251,31 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>终止/流标</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427124669</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427255950</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告</t>
+          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1285,24 +1285,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告；可见摘要：附件 收藏 招标公告 安徽 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)；可见摘要：收藏 招标预告 上海 2026-06-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1325,19 +1325,19 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427174343</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427280358</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告</t>
+          <t>生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1347,17 +1347,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告；可见摘要：标书 收藏 中标结果 北京 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告；可见摘要：收藏 招标公告 江苏 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
@@ -1375,51 +1375,51 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-427191692</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427124669</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>缺陷检测</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告；可见摘要：附件 收藏 招标公告 安徽 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
@@ -1449,39 +1449,39 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426951671</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427174343</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396；可见摘要：收藏 招标公告 上海 12小时前；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告；可见摘要：标书 收藏 中标结果 北京 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
@@ -1499,51 +1499,51 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426983145</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-427191692</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器</t>
+          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器；可见摘要：收藏 招标预告 上海 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1573,39 +1573,39 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427096376</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426951671</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14</t>
+          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>项目：2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14；可见摘要：收藏 招标公告 浙江 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396；可见摘要：收藏 招标公告 上海 12小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
@@ -1635,61 +1635,57 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427057182</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426983145</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>谈判采购公告</t>
+          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>CIM系统</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>RMS，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>采购内容：CIM系统；数量：一家；范围：CIM系统设备采购及有关技术服务、培训等，具体要求详见第五章采购需求；采购方：成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采；公告类型：采购公告；发布时间：2026-06-25</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采</t>
-        </is>
-      </c>
+          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器；可见摘要：收藏 招标预告 上海 2026-06-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>采购公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1701,19 +1697,19 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/837713.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427096376</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:51:21</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告</t>
+          <t>2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1733,14 +1729,14 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告；可见摘要：附件 收藏 中标结果 上海 2026-06-24；详情状态：受限，需人工核验</t>
+          <t>项目：2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14；可见摘要：收藏 招标公告 浙江 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1751,93 +1747,97 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426498852</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427057182</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762</t>
+          <t>谈判采购公告</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>CIM系统</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>RMS，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr"/>
+          <t>采购内容：CIM系统；数量：一家；范围：CIM系统设备采购及有关技术服务、培训等，具体要求详见第五章采购需求；采购方：成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采；公告类型：采购公告；发布时间：2026-06-25</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采</t>
+        </is>
+      </c>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>采购公告</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426408417</t>
+          <t>https://www.365trade.com.cn/zhwzb/837713.jhtml</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-06-26T10:51:21</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1847,24 +1847,24 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告；可见摘要：附件 收藏 中标结果 上海 2026-06-24；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1887,19 +1887,19 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426280043</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426498852</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1909,24 +1909,24 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1937,31 +1937,31 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426408417</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202</t>
+          <t>上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1971,24 +1971,24 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1999,31 +1999,31 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425830318</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426280043</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="25" ht="58" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -2033,24 +2033,24 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -2061,31 +2061,31 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="26" ht="58" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -2095,17 +2095,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2135,19 +2135,19 @@
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425830318</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -2157,17 +2157,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
@@ -2185,31 +2185,31 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="28" ht="58" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
+          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2219,24 +2219,24 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -2259,19 +2259,19 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="29" ht="58" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
+          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -2321,46 +2321,46 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -2383,19 +2383,19 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="31" ht="58" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2405,24 +2405,24 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>外观检查机</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -2445,46 +2445,46 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
+          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>膜厚仪</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2495,31 +2495,31 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="33" ht="58" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
+          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2529,24 +2529,24 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
+          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2557,31 +2557,31 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="34" ht="58" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
+          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2591,24 +2591,24 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2631,19 +2631,19 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="35" ht="58" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2653,24 +2653,24 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2681,97 +2681,93 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="36" ht="58" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪【重新招标】-公开招标公告</t>
+          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>自动光学检查机</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测，且公告具有半导体产业链语境</t>
+          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>无锡中微掩模电子有限公司</t>
-        </is>
-      </c>
+          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>公开招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10T14:16:35</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="37" ht="58" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
+          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2781,24 +2777,24 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>晶圆表面缺陷检测</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
+          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2809,93 +2805,97 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="38" ht="58" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
+          <t>缺陷检测仪【重新招标】-公开招标公告</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr"/>
+          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>无锡中微掩模电子有限公司</t>
+        </is>
+      </c>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>公开招标公告</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
+          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-06-10T14:16:35</t>
         </is>
       </c>
     </row>
     <row r="39" ht="58" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2905,24 +2905,24 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>外观检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2933,58 +2933,58 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="40" ht="58" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
+          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统</t>
+          <t>CD-SEM</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -3007,19 +3007,19 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="41" ht="58" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -3029,24 +3029,24 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>外观检测</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -3057,31 +3057,31 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="42" ht="58" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -3091,24 +3091,24 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>颗粒检测系统</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -3119,31 +3119,31 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T09:54:55</t>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
     <row r="43" ht="58" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -3153,24 +3153,24 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -3181,29 +3181,153 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr">
         <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09T09:17:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="58" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>招标变更</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>变更/澄清</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09T09:17:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="58" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>检测设备</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
           <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-421062373</t>
         </is>
       </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-08T09:54:55</t>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09T09:17:08</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P43"/>
+  <autoFilter ref="A1:P45"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -3247,10 +3371,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId43"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId45"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3283,7 +3409,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-08T09:59:36</t>
+          <t>2026-07-09T09:29:12</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3420,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">
@@ -3316,7 +3442,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P45" headerRowCount="1">
-  <autoFilter ref="A1:P45"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P50" headerRowCount="1">
+  <autoFilter ref="A1:P50"/>
   <tableColumns count="16">
     <tableColumn id="1" name="项目名称"/>
     <tableColumn id="2" name="判断类别"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P45"/>
+  <dimension ref="A1:P50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -593,7 +593,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686</t>
+          <t>关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -603,24 +603,24 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告；可见摘要：收藏 招标变更 广东 9分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -631,7 +631,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -643,19 +643,19 @@
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429404126</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430039810</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)</t>
+          <t>陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -665,24 +665,24 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)；可见摘要：收藏 招标公告 上海 2026-07-08；详情状态：受限，需人工核验</t>
+          <t>项目：陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告；可见摘要：收藏 招标公告 陕西 2026-07-10；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -705,19 +705,19 @@
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429489269</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429867103</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="4" ht="58" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告</t>
+          <t>西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -727,24 +727,24 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告；可见摘要：收藏 招标变更 河北 2026-07-05；详情状态：受限，需人工核验</t>
+          <t>项目：西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09；可见摘要：附件 收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -755,31 +755,31 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>终止/流标</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428711615</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429704334</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告</t>
+          <t>中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -789,24 +789,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>项目：纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告；可见摘要：收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)；可见摘要：收藏 招标预告 上海 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -817,7 +817,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -829,46 +829,46 @@
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428537526</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-429701886</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397</t>
+          <t>【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告；可见摘要：收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -879,58 +879,58 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419989</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429701915</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396</t>
+          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -941,31 +941,31 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419915</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429404126</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告</t>
+          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -975,24 +975,24 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告；可见摘要：附件 收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)；可见摘要：收藏 招标公告 上海 2026-07-08；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -1015,19 +1015,19 @@
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428541747</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429489269</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1037,24 +1037,24 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告；可见摘要：收藏 招标变更 河北 2026-07-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -1065,31 +1065,31 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>终止/流标</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434578</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428711615</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告</t>
+          <t>纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1099,24 +1099,24 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
+          <t>项目：纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告；可见摘要：收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -1139,46 +1139,46 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434575</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428537526</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告</t>
+          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告；可见摘要：收藏 招标公告 河北 22分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1189,58 +1189,58 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427329545</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419989</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告</t>
+          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告；可见摘要：附件 收藏 招标变更 河北 2026-06-27；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1256,26 +1256,26 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>终止/流标</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427255950</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419915</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)</t>
+          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1295,14 +1295,14 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)；可见摘要：收藏 招标预告 上海 2026-06-27；详情状态：受限，需人工核验</t>
+          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告；可见摘要：附件 收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1325,19 +1325,19 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427280358</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428541747</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1347,24 +1347,24 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>项目：生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告；可见摘要：收藏 招标公告 江苏 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1387,19 +1387,19 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427124669</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434578</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1409,24 +1409,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告；可见摘要：附件 收藏 招标公告 安徽 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1449,19 +1449,19 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427174343</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434575</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1471,24 +1471,24 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告；可见摘要：标书 收藏 中标结果 北京 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告；可见摘要：收藏 招标公告 河北 22分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1499,58 +1499,58 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-427191692</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427329545</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告；可见摘要：附件 收藏 招标变更 河北 2026-06-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1561,58 +1561,58 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>终止/流标</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426951671</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427255950</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396</t>
+          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396；可见摘要：收藏 招标公告 上海 12小时前；详情状态：受限，需人工核验</t>
+          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)；可见摘要：收藏 招标预告 上海 2026-06-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -1635,19 +1635,19 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426983145</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427280358</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器</t>
+          <t>生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1657,17 +1657,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器；可见摘要：收藏 招标预告 上海 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告；可见摘要：收藏 招标公告 江苏 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1697,19 +1697,19 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427096376</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427124669</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1719,17 +1719,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>缺陷检测</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>项目：2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14；可见摘要：收藏 招标公告 浙江 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告；可见摘要：附件 收藏 招标公告 安徽 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
@@ -1759,112 +1759,108 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427057182</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427174343</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>谈判采购公告</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>CIM系统</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>RMS，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>采购内容：CIM系统；数量：一家；范围：CIM系统设备采购及有关技术服务、培训等，具体要求详见第五章采购需求；采购方：成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采；公告类型：采购公告；发布时间：2026-06-25</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采</t>
-        </is>
-      </c>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告；可见摘要：标书 收藏 中标结果 北京 2026-06-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>采购公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/837713.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-427191692</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:51:21</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告</t>
+          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告；可见摘要：附件 收藏 中标结果 上海 2026-06-24；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1875,58 +1871,58 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426498852</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426951671</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762</t>
+          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396；可见摘要：收藏 招标公告 上海 12小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1937,31 +1933,31 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426408417</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426983145</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218</t>
+          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1971,24 +1967,24 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
+          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器；可见摘要：收藏 招标预告 上海 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1999,31 +1995,31 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426280043</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427096376</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="25" ht="58" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
+          <t>2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -2033,24 +2029,24 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
+          <t>项目：2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14；可见摘要：收藏 招标公告 浙江 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -2073,57 +2069,61 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427057182</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="26" ht="58" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202</t>
+          <t>谈判采购公告</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>CIM系统</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>RMS，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-18；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr"/>
+          <t>采购内容：CIM系统；数量：一家；范围：CIM系统设备采购及有关技术服务、培训等，具体要求详见第五章采购需求；采购方：成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采；公告类型：采购公告；发布时间：2026-06-25</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采</t>
+        </is>
+      </c>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>采购公告</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2135,19 +2135,19 @@
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425830318</t>
+          <t>https://www.365trade.com.cn/zhwzb/837713.jhtml</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-06-26T10:51:21</t>
         </is>
       </c>
     </row>
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -2157,24 +2157,24 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告；可见摘要：附件 收藏 中标结果 上海 2026-06-24；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -2185,31 +2185,31 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426498852</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="28" ht="58" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2229,14 +2229,14 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -2252,26 +2252,26 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426408417</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="29" ht="58" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
+          <t>上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -2321,19 +2321,19 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426280043</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2343,24 +2343,24 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -2383,19 +2383,19 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="31" ht="58" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2405,24 +2405,24 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -2433,58 +2433,58 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425830318</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2495,31 +2495,31 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="33" ht="58" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
+          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2529,24 +2529,24 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
+          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2562,26 +2562,26 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="34" ht="58" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
+          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2591,24 +2591,24 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2631,19 +2631,19 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="35" ht="58" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2653,24 +2653,24 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2693,19 +2693,19 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="36" ht="58" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2715,24 +2715,24 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机</t>
+          <t>外观检查机</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2755,46 +2755,46 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="37" ht="58" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
+          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测</t>
+          <t>膜厚仪</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2805,97 +2805,93 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="38" ht="58" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪【重新招标】-公开招标公告</t>
+          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>无锡中微掩模电子有限公司</t>
-        </is>
-      </c>
+          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>公开招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10T14:16:35</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="39" ht="58" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
+          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2905,24 +2901,24 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
+          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2933,58 +2929,58 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="40" ht="58" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2995,31 +2991,31 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="41" ht="58" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
+          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -3029,24 +3025,24 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>外观检测</t>
+          <t>自动光学检查机</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -3069,19 +3065,19 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="42" ht="58" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
+          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -3091,24 +3087,24 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统</t>
+          <t>晶圆表面缺陷检测</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -3131,81 +3127,85 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="43" ht="58" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+          <t>缺陷检测仪【重新招标】-公开招标公告</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr"/>
+          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>无锡中微掩模电子有限公司</t>
+        </is>
+      </c>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>公开招标公告</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-06-10T14:16:35</t>
         </is>
       </c>
     </row>
     <row r="44" ht="58" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -3215,24 +3215,24 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -3243,58 +3243,58 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T09:17:08</t>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
     <row r="45" ht="58" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>CD-SEM</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -3317,17 +3317,327 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="3" t="inlineStr">
         <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13T09:07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="58" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>外观检测</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13T09:07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="58" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>颗粒检测系统</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13T09:07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="58" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>检测仪</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>招标变更</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>变更/澄清</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13T09:07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="58" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>招标变更</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>变更/澄清</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13T09:07:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="58" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>检测设备</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
           <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-421062373</t>
         </is>
       </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-09T09:17:08</t>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13T09:07:03</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P45"/>
+  <autoFilter ref="A1:P50"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -3373,10 +3683,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId45"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId50"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3409,7 +3724,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-09T09:29:12</t>
+          <t>2026-07-13T09:18:05</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3735,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
@@ -3442,7 +3757,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8">

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-13T09:18:05</t>
+          <t>2026-07-13T09:27:09</t>
         </is>
       </c>
     </row>

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P50" headerRowCount="1">
-  <autoFilter ref="A1:P50"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P53" headerRowCount="1">
+  <autoFilter ref="A1:P53"/>
   <tableColumns count="16">
     <tableColumn id="1" name="项目名称"/>
     <tableColumn id="2" name="判断类别"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P50"/>
+  <dimension ref="A1:P53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -593,7 +593,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告</t>
+          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -613,14 +613,14 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>项目：关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告；可见摘要：收藏 招标变更 广东 9分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告；可见摘要：收藏 招标变更 广东 23小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -643,19 +643,19 @@
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430039810</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430062786</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告</t>
+          <t>关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -665,24 +665,24 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>项目：陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告；可见摘要：收藏 招标公告 陕西 2026-07-10；详情状态：受限，需人工核验</t>
+          <t>项目：关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告；可见摘要：收藏 招标变更 广东 9分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -693,7 +693,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -705,19 +705,19 @@
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429867103</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430039810</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="4" ht="58" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09</t>
+          <t>陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -727,17 +727,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>项目：西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09；可见摘要：附件 收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告；可见摘要：收藏 招标公告 陕西 2026-07-10；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
@@ -767,19 +767,19 @@
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429704334</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429867103</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)</t>
+          <t>西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -789,17 +789,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)；可见摘要：收藏 招标预告 上海 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09；可见摘要：附件 收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
@@ -817,7 +817,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -829,19 +829,19 @@
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-429701886</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429704334</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告</t>
+          <t>中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -851,17 +851,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>项目：【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告；可见摘要：收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)；可见摘要：收藏 招标预告 上海 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
@@ -879,7 +879,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -891,19 +891,19 @@
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429701915</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-429701886</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686</t>
+          <t>【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -913,24 +913,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告；可见摘要：收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -953,52 +953,52 @@
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429404126</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429701915</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)</t>
+          <t>晶圆有机清洗机-招标公告</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>晶圆/衬底光学缺陷检测</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>晶圆有机清洗机</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)；可见摘要：收藏 招标公告 上海 2026-07-08；详情状态：受限，需人工核验</t>
+          <t>采购内容：晶圆有机清洗机；数量：1台；公告类型：招标公告；发布时间：2026-07-10</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1015,81 +1015,89 @@
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429489269</t>
+          <t>https://www.365trade.com.cn/zhwzb/843900.jhtml</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:31:20</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告</t>
+          <t>中数创和设备采购项目014结果公告</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>晶圆/衬底光学缺陷检测</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>中数创和设备采购项目014</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统，且公告明确晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告；可见摘要：收藏 招标变更 河北 2026-07-05；详情状态：受限，需人工核验</t>
+          <t>采购内容：中数创和设备采购项目014；成交/中标方：黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2；成交/中标金额：000.00元；公告类型：结果公告；发布时间：2026-07-10</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>结果公告</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>终止/流标</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>000.00元</t>
+        </is>
+      </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428711615</t>
+          <t>https://www.365trade.com.cn/jhwzb/843422.jhtml</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:31:20</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告</t>
+          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1099,24 +1107,24 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>项目：纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告；可见摘要：收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -1139,46 +1147,46 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428537526</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429404126</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397</t>
+          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)；可见摘要：收藏 招标公告 上海 2026-07-08；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1189,58 +1197,58 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419989</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429489269</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告；可见摘要：收藏 招标变更 河北 2026-07-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1256,26 +1264,26 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>终止/流标</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419915</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428711615</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告</t>
+          <t>纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1295,7 +1303,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告；可见摘要：附件 收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告；可见摘要：收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
@@ -1325,46 +1333,46 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428541747</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428537526</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告</t>
+          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1375,58 +1383,58 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434578</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419989</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告</t>
+          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1437,31 +1445,31 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434575</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419915</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告</t>
+          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1471,24 +1479,24 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告；可见摘要：收藏 招标公告 河北 22分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告；可见摘要：附件 收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1511,19 +1519,19 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427329545</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428541747</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1533,24 +1541,24 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告；可见摘要：附件 收藏 招标变更 河北 2026-06-27；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1561,31 +1569,31 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>终止/流标</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427255950</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434578</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1595,24 +1603,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)；可见摘要：收藏 招标预告 上海 2026-06-27；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1623,7 +1631,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -1635,19 +1643,19 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427280358</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434575</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1657,24 +1665,24 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>项目：生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告；可见摘要：收藏 招标公告 江苏 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告；可见摘要：收藏 招标公告 河北 22分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1697,19 +1705,19 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427124669</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427329545</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1719,24 +1727,24 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告；可见摘要：附件 收藏 招标公告 安徽 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告；可见摘要：附件 收藏 招标变更 河北 2026-06-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1747,31 +1755,31 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>终止/流标</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427174343</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427255950</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告</t>
+          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1791,14 +1799,14 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告；可见摘要：标书 收藏 中标结果 北京 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)；可见摘要：收藏 招标预告 上海 2026-06-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1809,51 +1817,51 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-427191692</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427280358</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397</t>
+          <t>生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告；可见摘要：收藏 招标公告 江苏 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
@@ -1883,39 +1891,39 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426951671</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427124669</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>缺陷检测</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396；可见摘要：收藏 招标公告 上海 12小时前；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告；可见摘要：附件 收藏 招标公告 安徽 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
@@ -1945,19 +1953,19 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426983145</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427174343</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1977,7 +1985,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器；可见摘要：收藏 招标预告 上海 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告；可见摘要：标书 收藏 中标结果 北京 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
@@ -1995,51 +2003,51 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427096376</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-427191692</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="25" ht="58" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14</t>
+          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>项目：2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14；可见摘要：收藏 招标公告 浙江 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
@@ -2069,61 +2077,57 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427057182</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426951671</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="26" ht="58" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>谈判采购公告</t>
+          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>CIM系统</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>RMS，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>采购内容：CIM系统；数量：一家；范围：CIM系统设备采购及有关技术服务、培训等，具体要求详见第五章采购需求；采购方：成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采；公告类型：采购公告；发布时间：2026-06-25</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采</t>
-        </is>
-      </c>
+          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396；可见摘要：收藏 招标公告 上海 12小时前；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>采购公告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2135,19 +2139,19 @@
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/837713.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426983145</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:51:21</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告</t>
+          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -2167,14 +2171,14 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告；可见摘要：附件 收藏 中标结果 上海 2026-06-24；详情状态：受限，需人工核验</t>
+          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器；可见摘要：收藏 招标预告 上海 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -2185,31 +2189,31 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426498852</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427096376</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="28" ht="58" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762</t>
+          <t>2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2229,14 +2233,14 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
+          <t>项目：2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14；可见摘要：收藏 招标公告 浙江 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -2247,93 +2251,97 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426408417</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427057182</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="29" ht="58" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218</t>
+          <t>谈判采购公告</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测</t>
+          <t>CIM系统</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>RMS，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr"/>
+          <t>采购内容：CIM系统；数量：一家；范围：CIM系统设备采购及有关技术服务、培训等，具体要求详见第五章采购需求；采购方：成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采；公告类型：采购公告；发布时间：2026-06-25</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采</t>
+        </is>
+      </c>
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>采购公告</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426280043</t>
+          <t>https://www.365trade.com.cn/zhwzb/837713.jhtml</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-06-26T10:51:21</t>
         </is>
       </c>
     </row>
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2343,24 +2351,24 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告；可见摘要：附件 收藏 中标结果 上海 2026-06-24；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -2371,31 +2379,31 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426498852</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="31" ht="58" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2405,24 +2413,24 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -2433,31 +2441,31 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425830318</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426408417</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
+          <t>上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2467,24 +2475,24 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2495,31 +2503,31 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426280043</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="33" ht="58" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2529,24 +2537,24 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2557,7 +2565,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -2569,19 +2577,19 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="34" ht="58" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2591,17 +2599,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
@@ -2619,31 +2627,31 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425830318</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="35" ht="58" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2653,24 +2661,24 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2681,31 +2689,31 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="36" ht="58" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
+          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2715,24 +2723,24 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2748,53 +2756,53 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="37" ht="58" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
+          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2805,31 +2813,31 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="38" ht="58" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2839,24 +2847,24 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2867,31 +2875,31 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="39" ht="58" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2901,24 +2909,24 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>外观检查机</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2941,46 +2949,46 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="40" ht="58" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
+          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>膜厚仪</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2991,7 +2999,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -3003,19 +3011,19 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="41" ht="58" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
+          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -3025,24 +3033,24 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -3065,19 +3073,19 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="42" ht="58" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
+          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -3087,24 +3095,24 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
+          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -3127,61 +3135,57 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="43" ht="58" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪【重新招标】-公开招标公告</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>无锡中微掩模电子有限公司</t>
-        </is>
-      </c>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>公开招标公告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -3193,19 +3197,19 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10T14:16:35</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="44" ht="58" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
+          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -3215,24 +3219,24 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>自动光学检查机</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -3243,58 +3247,58 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="45" ht="58" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
+          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM</t>
+          <t>晶圆表面缺陷检测</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
+          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -3317,81 +3321,85 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="46" ht="58" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
+          <t>缺陷检测仪【重新招标】-公开招标公告</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>外观检测</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr"/>
+          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>无锡中微掩模电子有限公司</t>
+        </is>
+      </c>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>公开招标公告</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
+          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-06-10T14:16:35</t>
         </is>
       </c>
     </row>
     <row r="47" ht="58" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -3401,24 +3409,24 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -3429,58 +3437,58 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="48" ht="58" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>CD-SEM</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -3491,31 +3499,31 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="49" ht="58" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -3525,24 +3533,24 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>外观检测</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
@@ -3553,31 +3561,31 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T09:07:03</t>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
     <row r="50" ht="58" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3587,24 +3595,24 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>颗粒检测系统</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -3627,17 +3635,203 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="3" t="inlineStr">
         <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14T09:29:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="58" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>检测仪</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>招标变更</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>变更/澄清</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14T09:29:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="58" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>招标变更</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>变更/澄清</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14T09:29:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="58" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>检测设备</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
           <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-421062373</t>
         </is>
       </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-13T09:07:03</t>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14T09:29:01</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P50"/>
+  <autoFilter ref="A1:P53"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -3688,10 +3882,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId50"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId53"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3724,7 +3921,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-13T09:27:09</t>
+          <t>2026-07-14T09:31:21</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3932,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
@@ -3757,7 +3954,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
@@ -3767,7 +3964,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P53" headerRowCount="1">
-  <autoFilter ref="A1:P53"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P54" headerRowCount="1">
+  <autoFilter ref="A1:P54"/>
   <tableColumns count="16">
     <tableColumn id="1" name="项目名称"/>
     <tableColumn id="2" name="判断类别"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P53"/>
+  <dimension ref="A1:P54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -593,7 +593,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）评标结果公示公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -603,24 +603,24 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告；可见摘要：收藏 招标变更 广东 23小时前；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）评标结果公示公告(1)-0821-264MSKZZ2202；可见摘要：收藏 中标结果 河南 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -631,31 +631,31 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430062786</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430471714</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告</t>
+          <t>北京大学2026年9月政府采购意向- 晶圆 检测 仪详细情况150.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -675,14 +675,14 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>项目：关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告；可见摘要：收藏 招标变更 广东 9分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：北京大学2026年9月政府采购意向- 晶圆 检测 仪详细情况150.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-07-14；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -693,7 +693,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -705,19 +705,19 @@
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430039810</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-430314307</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="4" ht="58" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告</t>
+          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -727,24 +727,24 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>项目：陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告；可见摘要：收藏 招标公告 陕西 2026-07-10；详情状态：受限，需人工核验</t>
+          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告；可见摘要：收藏 招标变更 广东 23小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -767,19 +767,19 @@
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429867103</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430062786</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09</t>
+          <t>关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -789,24 +789,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>项目：西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09；可见摘要：附件 收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告；可见摘要：收藏 招标变更 广东 9分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -817,7 +817,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -829,19 +829,19 @@
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429704334</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430039810</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)</t>
+          <t>陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -851,17 +851,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)；可见摘要：收藏 招标预告 上海 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告；可见摘要：收藏 招标公告 陕西 2026-07-10；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
@@ -879,7 +879,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -891,19 +891,19 @@
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-429701886</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429867103</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告</t>
+          <t>西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>项目：【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告；可见摘要：收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09；可见摘要：附件 收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
@@ -953,39 +953,39 @@
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429701915</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429704334</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>晶圆有机清洗机-招标公告</t>
+          <t>中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>晶圆/衬底光学缺陷检测</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>晶圆有机清洗机</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>采购内容：晶圆有机清洗机；数量：1台；公告类型：招标公告；发布时间：2026-07-10</t>
+          <t>项目：中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)；可见摘要：收藏 招标预告 上海 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
@@ -998,12 +998,12 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1015,47 +1015,43 @@
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/843900.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-429701886</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:31:20</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>中数创和设备采购项目014结果公告</t>
+          <t>【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>晶圆/衬底光学缺陷检测</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>中数创和设备采购项目014</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>检测系统，且公告明确晶圆/硅片/SiC/衬底场景</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>采购内容：中数创和设备采购项目014；成交/中标方：黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2；成交/中标金额：000.00元；公告类型：结果公告；发布时间：2026-07-10</t>
+          <t>项目：【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告；可见摘要：收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2</t>
-        </is>
-      </c>
+      <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
@@ -1064,73 +1060,69 @@
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>结果公告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>000.00元</t>
-        </is>
-      </c>
+      <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/jhwzb/843422.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429701915</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:31:20</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686</t>
+          <t>晶圆有机清洗机-招标公告</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>晶圆/衬底光学缺陷检测</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>晶圆有机清洗机</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
+          <t>采购内容：晶圆有机清洗机；数量：1台；公告类型：招标公告；发布时间：2026-07-10</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1147,81 +1139,89 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429404126</t>
+          <t>https://www.365trade.com.cn/zhwzb/843900.jhtml</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-14T09:31:20</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)</t>
+          <t>中数创和设备采购项目014结果公告</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>晶圆/衬底光学缺陷检测</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>中数创和设备采购项目014</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统，且公告明确晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)；可见摘要：收藏 招标公告 上海 2026-07-08；详情状态：受限，需人工核验</t>
+          <t>采购内容：中数创和设备采购项目014；成交/中标方：黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2；成交/中标金额：000.00元；公告类型：结果公告；发布时间：2026-07-10</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>结果公告</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>000.00元</t>
+        </is>
+      </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429489269</t>
+          <t>https://www.365trade.com.cn/jhwzb/843422.jhtml</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-14T09:31:20</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告</t>
+          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告；可见摘要：收藏 招标变更 河北 2026-07-05；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1259,31 +1259,31 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>终止/流标</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428711615</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429404126</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告</t>
+          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1293,24 +1293,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>项目：纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告；可见摘要：收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)；可见摘要：收藏 招标公告 上海 2026-07-08；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1333,46 +1333,46 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428537526</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429489269</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告；可见摘要：收藏 招标变更 河北 2026-07-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1388,46 +1388,46 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>终止/流标</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419989</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428711615</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396</t>
+          <t>纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告；可见摘要：收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
@@ -1445,51 +1445,51 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419915</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428537526</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告</t>
+          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告；可见摘要：附件 收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
@@ -1507,58 +1507,58 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428541747</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419989</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告</t>
+          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1569,31 +1569,31 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434578</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419915</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告</t>
+          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1603,24 +1603,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
+          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告；可见摘要：附件 收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1643,19 +1643,19 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434575</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428541747</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1665,24 +1665,24 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告；可见摘要：收藏 招标公告 河北 22分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1705,19 +1705,19 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427329545</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434578</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1727,24 +1727,24 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告；可见摘要：附件 收藏 招标变更 河北 2026-06-27；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1755,31 +1755,31 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>终止/流标</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427255950</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434575</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1789,24 +1789,24 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)；可见摘要：收藏 招标预告 上海 2026-06-27；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告；可见摘要：收藏 招标公告 河北 22分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -1829,19 +1829,19 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427280358</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427329545</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1851,24 +1851,24 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>项目：生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告；可见摘要：收藏 招标公告 江苏 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告；可见摘要：附件 收藏 招标变更 河北 2026-06-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1879,31 +1879,31 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>终止/流标</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427124669</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427255950</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告</t>
+          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1913,24 +1913,24 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告；可见摘要：附件 收藏 招标公告 安徽 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)；可见摘要：收藏 招标预告 上海 2026-06-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -1953,19 +1953,19 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427174343</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427280358</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告</t>
+          <t>生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1975,17 +1975,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告；可见摘要：标书 收藏 中标结果 北京 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告；可见摘要：收藏 招标公告 江苏 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
@@ -2003,51 +2003,51 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-427191692</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427124669</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="25" ht="58" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>缺陷检测</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告；可见摘要：附件 收藏 招标公告 安徽 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
@@ -2077,39 +2077,39 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426951671</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427174343</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="26" ht="58" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396；可见摘要：收藏 招标公告 上海 12小时前；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告；可见摘要：标书 收藏 中标结果 北京 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
@@ -2127,51 +2127,51 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426983145</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-427191692</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器</t>
+          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器；可见摘要：收藏 招标预告 上海 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -2201,39 +2201,39 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427096376</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426951671</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="28" ht="58" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14</t>
+          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>项目：2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14；可见摘要：收藏 招标公告 浙江 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396；可见摘要：收藏 招标公告 上海 12小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
@@ -2263,61 +2263,57 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427057182</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426983145</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="29" ht="58" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>谈判采购公告</t>
+          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>CIM系统</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>RMS，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>采购内容：CIM系统；数量：一家；范围：CIM系统设备采购及有关技术服务、培训等，具体要求详见第五章采购需求；采购方：成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采；公告类型：采购公告；发布时间：2026-06-25</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采</t>
-        </is>
-      </c>
+          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器；可见摘要：收藏 招标预告 上海 2026-06-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>采购公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -2329,19 +2325,19 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/837713.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427096376</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:51:21</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告</t>
+          <t>2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2361,14 +2357,14 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告；可见摘要：附件 收藏 中标结果 上海 2026-06-24；详情状态：受限，需人工核验</t>
+          <t>项目：2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14；可见摘要：收藏 招标公告 浙江 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -2379,93 +2375,97 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426498852</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427057182</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="31" ht="58" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762</t>
+          <t>谈判采购公告</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>CIM系统</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>RMS，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr"/>
+          <t>采购内容：CIM系统；数量：一家；范围：CIM系统设备采购及有关技术服务、培训等，具体要求详见第五章采购需求；采购方：成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采；公告类型：采购公告；发布时间：2026-06-25</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采</t>
+        </is>
+      </c>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>采购公告</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426408417</t>
+          <t>https://www.365trade.com.cn/zhwzb/837713.jhtml</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-06-26T10:51:21</t>
         </is>
       </c>
     </row>
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2475,24 +2475,24 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告；可见摘要：附件 收藏 中标结果 上海 2026-06-24；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2515,19 +2515,19 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426280043</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426498852</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="33" ht="58" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2537,24 +2537,24 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2565,31 +2565,31 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426408417</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="34" ht="58" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202</t>
+          <t>上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2599,24 +2599,24 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）国际招标公告(2)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2627,31 +2627,31 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425830318</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426280043</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="35" ht="58" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2661,24 +2661,24 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2689,31 +2689,31 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="36" ht="58" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2723,17 +2723,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
@@ -2751,31 +2751,31 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="37" ht="58" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
+          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
@@ -2818,26 +2818,26 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="38" ht="58" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
+          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2847,24 +2847,24 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2875,31 +2875,31 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="39" ht="58" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2909,24 +2909,24 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2937,51 +2937,51 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="40" ht="58" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪</t>
+          <t>外观检查机</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
@@ -2999,58 +2999,58 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="41" ht="58" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
+          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>膜厚仪</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -3061,31 +3061,31 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="42" ht="58" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
+          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -3095,24 +3095,24 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
+          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -3135,19 +3135,19 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="43" ht="58" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
+          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -3167,14 +3167,14 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
+          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -3185,31 +3185,31 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="44" ht="58" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -3219,17 +3219,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
@@ -3247,31 +3247,31 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="45" ht="58" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
+          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -3281,24 +3281,24 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测</t>
+          <t>自动光学检查机</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -3321,46 +3321,42 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="46" ht="58" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪【重新招标】-公开招标公告</t>
+          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>晶圆表面缺陷检测</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测，且公告具有半导体产业链语境</t>
+          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>无锡中微掩模电子有限公司</t>
-        </is>
-      </c>
+          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -3370,74 +3366,78 @@
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>公开招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10T14:16:35</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="47" ht="58" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
+          <t>缺陷检测仪【重新招标】-公开招标公告</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr"/>
+          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>无锡中微掩模电子有限公司</t>
+        </is>
+      </c>
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>公开招标公告</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -3449,46 +3449,46 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
+          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-06-10T14:16:35</t>
         </is>
       </c>
     </row>
     <row r="48" ht="58" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -3499,58 +3499,58 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="49" ht="58" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
+          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>外观检测</t>
+          <t>CD-SEM</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
@@ -3573,19 +3573,19 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="50" ht="58" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
+          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3595,24 +3595,24 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统</t>
+          <t>外观检测</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -3635,19 +3635,19 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="51" ht="58" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -3657,17 +3657,17 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>颗粒检测系统</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
@@ -3685,31 +3685,31 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="52" ht="58" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3719,24 +3719,24 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -3759,19 +3759,19 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:29:01</t>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="53" ht="58" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>外观检查机</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
@@ -3809,29 +3809,91 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="3" t="inlineStr">
         <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15T10:31:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="58" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>检测设备</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
           <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-421062373</t>
         </is>
       </c>
-      <c r="P53" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-14T09:29:01</t>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15T10:31:53</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P53"/>
+  <autoFilter ref="A1:P54"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -3885,10 +3947,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId53"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId53"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId54"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3921,7 +3984,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-14T09:31:21</t>
+          <t>2026-07-15T10:35:30</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3995,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
@@ -3954,7 +4017,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P54" headerRowCount="1">
-  <autoFilter ref="A1:P54"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P56" headerRowCount="1">
+  <autoFilter ref="A1:P56"/>
   <tableColumns count="16">
     <tableColumn id="1" name="项目名称"/>
     <tableColumn id="2" name="判断类别"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P54"/>
+  <dimension ref="A1:P56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -593,7 +593,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）评标结果公示公告(1)-0821-264MSKZZ2202</t>
+          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备重新招标澄清或变更公告(1)-0613-264025123686</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -603,24 +603,24 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）评标结果公示公告(1)-0821-264MSKZZ2202；可见摘要：收藏 中标结果 河南 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备重新招标澄清或变更公告(1)-0613-264025123686；可见摘要：收藏 招标变更 上海 32分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -631,31 +631,31 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430471714</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430820283</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>北京大学2026年9月政府采购意向- 晶圆 检测 仪详细情况150.000000万元(人民币)</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）评标结果公示公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -665,24 +665,24 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>项目：北京大学2026年9月政府采购意向- 晶圆 检测 仪详细情况150.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-07-14；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）评标结果公示公告(1)-0821-264MSKZZ2202；可见摘要：收藏 中标结果 河南 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -693,69 +693,69 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-430314307</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430471714</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="4" ht="58" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告</t>
+          <t>超光滑碳化硅光学元件无损清洗系统-公开招标公告</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>晶圆/衬底光学缺陷检测</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>超光滑碳化硅光学元件无损清洗系统</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告；可见摘要：收藏 招标变更 广东 23小时前；详情状态：受限，需人工核验</t>
+          <t>采购内容：超光滑碳化硅光学元件无损清洗系统；数量：1套；公告类型：公开招标公告；发布时间：2026-07-15</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>公开招标公告</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -767,19 +767,19 @@
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430062786</t>
+          <t>https://www.365trade.com.cn/zhwzb/845555.jhtml</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:35:32</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告</t>
+          <t>北京大学2026年9月政府采购意向- 晶圆 检测 仪详细情况150.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -799,14 +799,14 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>项目：关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告；可见摘要：收藏 招标变更 广东 9分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：北京大学2026年9月政府采购意向- 晶圆 检测 仪详细情况150.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-07-14；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -817,7 +817,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -829,19 +829,19 @@
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430039810</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-430314307</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告</t>
+          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -851,24 +851,24 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>项目：陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告；可见摘要：收藏 招标公告 陕西 2026-07-10；详情状态：受限，需人工核验</t>
+          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告；可见摘要：收藏 招标变更 广东 23小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -879,7 +879,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -891,19 +891,19 @@
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429867103</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430062786</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09</t>
+          <t>关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -913,24 +913,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>项目：西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09；可见摘要：附件 收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告；可见摘要：收藏 招标变更 广东 9分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -941,7 +941,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -953,19 +953,19 @@
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429704334</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430039810</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)</t>
+          <t>陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -975,17 +975,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)；可见摘要：收藏 招标预告 上海 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告；可见摘要：收藏 招标公告 陕西 2026-07-10；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1015,19 +1015,19 @@
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-429701886</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429867103</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告</t>
+          <t>西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>项目：【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告；可见摘要：收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09；可见摘要：附件 收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
@@ -1077,39 +1077,39 @@
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429701915</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429704334</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>晶圆有机清洗机-招标公告</t>
+          <t>中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>晶圆/衬底光学缺陷检测</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>晶圆有机清洗机</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>采购内容：晶圆有机清洗机；数量：1台；公告类型：招标公告；发布时间：2026-07-10</t>
+          <t>项目：中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)；可见摘要：收藏 招标预告 上海 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
@@ -1122,12 +1122,12 @@
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1139,47 +1139,43 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/843900.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-429701886</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:31:20</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>中数创和设备采购项目014结果公告</t>
+          <t>【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>晶圆/衬底光学缺陷检测</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>中数创和设备采购项目014</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>检测系统，且公告明确晶圆/硅片/SiC/衬底场景</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>采购内容：中数创和设备采购项目014；成交/中标方：黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2；成交/中标金额：000.00元；公告类型：结果公告；发布时间：2026-07-10</t>
+          <t>项目：【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告；可见摘要：收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2</t>
-        </is>
-      </c>
+      <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
@@ -1188,73 +1184,69 @@
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>结果公告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>000.00元</t>
-        </is>
-      </c>
+      <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/jhwzb/843422.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429701915</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:31:20</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686</t>
+          <t>晶圆有机清洗机-招标公告</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>晶圆/衬底光学缺陷检测</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>晶圆有机清洗机</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
+          <t>采购内容：晶圆有机清洗机；数量：1台；公告类型：招标公告；发布时间：2026-07-10</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1271,81 +1263,89 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429404126</t>
+          <t>https://www.365trade.com.cn/zhwzb/843900.jhtml</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-14T09:31:20</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)</t>
+          <t>中数创和设备采购项目014结果公告</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>晶圆/衬底光学缺陷检测</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>中数创和设备采购项目014</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统，且公告明确晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)；可见摘要：收藏 招标公告 上海 2026-07-08；详情状态：受限，需人工核验</t>
+          <t>采购内容：中数创和设备采购项目014；成交/中标方：黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2；成交/中标金额：000.00元；公告类型：结果公告；发布时间：2026-07-10</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2</t>
+        </is>
+      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>结果公告</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>000.00元</t>
+        </is>
+      </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429489269</t>
+          <t>https://www.365trade.com.cn/jhwzb/843422.jhtml</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-14T09:31:20</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告</t>
+          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1355,24 +1355,24 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告；可见摘要：收藏 招标变更 河北 2026-07-05；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1383,31 +1383,31 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>终止/流标</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428711615</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429404126</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告</t>
+          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1417,24 +1417,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>项目：纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告；可见摘要：收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)；可见摘要：收藏 招标公告 上海 2026-07-08；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1457,46 +1457,46 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428537526</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429489269</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告；可见摘要：收藏 招标变更 河北 2026-07-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1512,46 +1512,46 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>终止/流标</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419989</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428711615</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396</t>
+          <t>纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告；可见摘要：收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
@@ -1569,51 +1569,51 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419915</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428537526</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告</t>
+          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告；可见摘要：附件 收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
@@ -1631,58 +1631,58 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428541747</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419989</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告</t>
+          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1693,31 +1693,31 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434578</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419915</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告</t>
+          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1727,24 +1727,24 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
+          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告；可见摘要：附件 收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1767,19 +1767,19 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434575</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428541747</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1789,24 +1789,24 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告；可见摘要：收藏 招标公告 河北 22分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1829,19 +1829,19 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427329545</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434578</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1851,24 +1851,24 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告；可见摘要：附件 收藏 招标变更 河北 2026-06-27；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1879,31 +1879,31 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>终止/流标</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427255950</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434575</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1913,24 +1913,24 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)；可见摘要：收藏 招标预告 上海 2026-06-27；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告；可见摘要：收藏 招标公告 河北 22分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -1953,19 +1953,19 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427280358</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427329545</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1975,24 +1975,24 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>项目：生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告；可见摘要：收藏 招标公告 江苏 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告；可见摘要：附件 收藏 招标变更 河北 2026-06-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -2003,31 +2003,31 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>终止/流标</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427124669</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427255950</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="25" ht="58" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告</t>
+          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -2037,24 +2037,24 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告；可见摘要：附件 收藏 招标公告 安徽 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)；可见摘要：收藏 招标预告 上海 2026-06-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -2077,19 +2077,19 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427174343</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427280358</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="26" ht="58" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告</t>
+          <t>生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -2099,17 +2099,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告；可见摘要：标书 收藏 中标结果 北京 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告；可见摘要：收藏 招标公告 江苏 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
@@ -2127,51 +2127,51 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-427191692</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427124669</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>缺陷检测</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告；可见摘要：附件 收藏 招标公告 安徽 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
@@ -2201,39 +2201,39 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426951671</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427174343</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="28" ht="58" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396；可见摘要：收藏 招标公告 上海 12小时前；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告；可见摘要：标书 收藏 中标结果 北京 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
@@ -2251,51 +2251,51 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426983145</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-427191692</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="29" ht="58" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器</t>
+          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器；可见摘要：收藏 招标预告 上海 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -2325,39 +2325,39 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427096376</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426951671</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14</t>
+          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>项目：2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14；可见摘要：收藏 招标公告 浙江 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396；可见摘要：收藏 招标公告 上海 12小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
@@ -2387,61 +2387,57 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427057182</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426983145</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="31" ht="58" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>谈判采购公告</t>
+          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>CIM系统</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>RMS，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>采购内容：CIM系统；数量：一家；范围：CIM系统设备采购及有关技术服务、培训等，具体要求详见第五章采购需求；采购方：成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采；公告类型：采购公告；发布时间：2026-06-25</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采</t>
-        </is>
-      </c>
+          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器；可见摘要：收藏 招标预告 上海 2026-06-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>采购公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -2453,19 +2449,19 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/837713.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427096376</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:51:21</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告</t>
+          <t>2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2485,14 +2481,14 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告；可见摘要：附件 收藏 中标结果 上海 2026-06-24；详情状态：受限，需人工核验</t>
+          <t>项目：2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14；可见摘要：收藏 招标公告 浙江 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2503,93 +2499,97 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426498852</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427057182</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="33" ht="58" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762</t>
+          <t>谈判采购公告</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>CIM系统</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>RMS，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr"/>
+          <t>采购内容：CIM系统；数量：一家；范围：CIM系统设备采购及有关技术服务、培训等，具体要求详见第五章采购需求；采购方：成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采；公告类型：采购公告；发布时间：2026-06-25</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采</t>
+        </is>
+      </c>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>采购公告</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426408417</t>
+          <t>https://www.365trade.com.cn/zhwzb/837713.jhtml</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-06-26T10:51:21</t>
         </is>
       </c>
     </row>
     <row r="34" ht="58" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2599,24 +2599,24 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告；可见摘要：附件 收藏 中标结果 上海 2026-06-24；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2639,19 +2639,19 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426280043</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426498852</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="35" ht="58" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2661,24 +2661,24 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2689,31 +2689,31 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426408417</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="36" ht="58" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
+          <t>上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2723,24 +2723,24 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2751,31 +2751,31 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426280043</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="37" ht="58" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2785,24 +2785,24 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -2825,19 +2825,19 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="38" ht="58" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2847,17 +2847,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
@@ -2875,31 +2875,31 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="39" ht="58" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
+          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2909,24 +2909,24 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -2949,19 +2949,19 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="40" ht="58" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
+          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -3011,46 +3011,46 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="41" ht="58" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -3073,19 +3073,19 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="42" ht="58" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -3095,24 +3095,24 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>外观检查机</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -3135,46 +3135,46 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="43" ht="58" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
+          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>膜厚仪</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -3185,31 +3185,31 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="44" ht="58" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
+          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -3219,24 +3219,24 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
+          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -3247,31 +3247,31 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="45" ht="58" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
+          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -3281,24 +3281,24 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -3321,19 +3321,19 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="46" ht="58" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -3343,24 +3343,24 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -3371,97 +3371,93 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="47" ht="58" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪【重新招标】-公开招标公告</t>
+          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>自动光学检查机</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测，且公告具有半导体产业链语境</t>
+          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>无锡中微掩模电子有限公司</t>
-        </is>
-      </c>
+          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>公开招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10T14:16:35</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="48" ht="58" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
+          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3471,24 +3467,24 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>晶圆表面缺陷检测</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
+          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -3499,93 +3495,97 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="49" ht="58" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
+          <t>缺陷检测仪【重新招标】-公开招标公告</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr"/>
+          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>无锡中微掩模电子有限公司</t>
+        </is>
+      </c>
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>公开招标公告</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
+          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-06-10T14:16:35</t>
         </is>
       </c>
     </row>
     <row r="50" ht="58" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3595,24 +3595,24 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>外观检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -3623,58 +3623,58 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="51" ht="58" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
+          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统</t>
+          <t>CD-SEM</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -3697,19 +3697,19 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="52" ht="58" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3719,24 +3719,24 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>外观检测</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -3747,31 +3747,31 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="53" ht="58" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3781,24 +3781,24 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>颗粒检测系统</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3809,31 +3809,31 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:31:53</t>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
     <row r="54" ht="58" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3843,24 +3843,24 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3871,29 +3871,153 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="3" t="inlineStr">
         <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16T10:31:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="58" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>招标变更</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>变更/澄清</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16T10:31:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="58" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>检测设备</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
           <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-421062373</t>
         </is>
       </c>
-      <c r="P54" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:31:53</t>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16T10:31:53</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P54"/>
+  <autoFilter ref="A1:P56"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -3948,10 +4072,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId55"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId54"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId56"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3984,7 +4110,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-15T10:35:30</t>
+          <t>2026-07-16T10:35:33</t>
         </is>
       </c>
     </row>
@@ -3995,7 +4121,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
@@ -4017,7 +4143,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -4027,7 +4153,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$63</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P56" headerRowCount="1">
-  <autoFilter ref="A1:P56"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P63" headerRowCount="1">
+  <autoFilter ref="A1:P63"/>
   <tableColumns count="16">
     <tableColumn id="1" name="项目名称"/>
     <tableColumn id="2" name="判断类别"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P56"/>
+  <dimension ref="A1:P63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -593,7 +593,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备重新招标澄清或变更公告(1)-0613-264025123686</t>
+          <t>陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目-2026-07-16</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -603,24 +603,24 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备重新招标澄清或变更公告(1)-0613-264025123686；可见摘要：收藏 招标变更 上海 32分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目-2026-07-16；可见摘要：附件 收藏 招标公告 陕西 11小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -631,31 +631,31 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430820283</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%9B%86%E6%88%90%E7%94%B5%E8%B7%AF%20%E6%A3%80%E6%B5%8B#bidcenter-431023609</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）评标结果公示公告(1)-0821-264MSKZZ2202</t>
+          <t>陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -665,24 +665,24 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）评标结果公示公告(1)-0821-264MSKZZ2202；可见摘要：收藏 中标结果 河南 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目；可见摘要：附件 收藏 招标公告 陕西 12小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -693,93 +693,93 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430471714</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%9B%86%E6%88%90%E7%94%B5%E8%B7%AF%20%E6%A3%80%E6%B5%8B#bidcenter-431017188</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="4" ht="58" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>超光滑碳化硅光学元件无损清洗系统-公开招标公告</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第4包中标结果公告</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>晶圆/衬底光学缺陷检测</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>超光滑碳化硅光学元件无损清洗系统</t>
+          <t>缺陷检测</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>采购内容：超光滑碳化硅光学元件无损清洗系统；数量：1套；公告类型：公开招标公告；发布时间：2026-07-15</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第4包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>公开招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/845555.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361360</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:35:32</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>北京大学2026年9月政府采购意向- 晶圆 检测 仪详细情况150.000000万元(人民币)</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第3包中标结果公告</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -789,24 +789,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>缺陷检测</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>项目：北京大学2026年9月政府采购意向- 晶圆 检测 仪详细情况150.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-07-14；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第3包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -817,31 +817,31 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-430314307</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361355</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第2包中标结果公告</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -851,24 +851,24 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>缺陷检测</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告；可见摘要：收藏 招标变更 广东 23小时前；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第2包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -879,31 +879,31 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430062786</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361358</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第1包中标结果公告</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -913,24 +913,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>缺陷检测</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>项目：关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告；可见摘要：收藏 招标变更 广东 9分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第1包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -941,31 +941,31 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430039810</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361353</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告</t>
+          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备重新招标澄清或变更公告</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -975,24 +975,24 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>项目：陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告；可见摘要：收藏 招标公告 陕西 2026-07-10；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备重新招标澄清或变更公告；可见摘要：收藏 招标变更 上海 22小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -1003,31 +1003,31 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429867103</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430852656</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09</t>
+          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备重新招标澄清或变更公告(1)-0613-264025123686</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1037,24 +1037,24 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>项目：西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09；可见摘要：附件 收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备重新招标澄清或变更公告(1)-0613-264025123686；可见摘要：收藏 招标变更 上海 32分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -1065,31 +1065,31 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429704334</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430820283</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）评标结果公示公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1109,14 +1109,14 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)；可见摘要：收藏 招标预告 上海 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）评标结果公示公告(1)-0821-264MSKZZ2202；可见摘要：收藏 中标结果 河南 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -1127,69 +1127,69 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-429701886</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430471714</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告</t>
+          <t>超光滑碳化硅光学元件无损清洗系统-公开招标公告</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>晶圆/衬底光学缺陷检测</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>超光滑碳化硅光学元件无损清洗系统</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>项目：【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告；可见摘要：收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
+          <t>采购内容：超光滑碳化硅光学元件无损清洗系统；数量：1套；公告类型：公开招标公告；发布时间：2026-07-15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>公开招标公告</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1201,57 +1201,57 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429701915</t>
+          <t>https://www.365trade.com.cn/zhwzb/845555.jhtml</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-16T10:35:32</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>晶圆有机清洗机-招标公告</t>
+          <t>北京大学2026年9月政府采购意向- 晶圆 检测 仪详细情况150.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>晶圆/衬底光学缺陷检测</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>晶圆有机清洗机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>采购内容：晶圆有机清洗机；数量：1台；公告类型：招标公告；发布时间：2026-07-10</t>
+          <t>项目：北京大学2026年9月政府采购意向- 晶圆 检测 仪详细情况150.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-07-14；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1263,89 +1263,81 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/843900.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-430314307</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:31:20</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>中数创和设备采购项目014结果公告</t>
+          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>晶圆/衬底光学缺陷检测</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>中数创和设备采购项目014</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>检测系统，且公告明确晶圆/硅片/SiC/衬底场景</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>采购内容：中数创和设备采购项目014；成交/中标方：黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2；成交/中标金额：000.00元；公告类型：结果公告；发布时间：2026-07-10</t>
+          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告；可见摘要：收藏 招标变更 广东 23小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2</t>
-        </is>
-      </c>
+      <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>结果公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>000.00元</t>
-        </is>
-      </c>
+      <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/jhwzb/843422.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430062786</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:31:20</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686</t>
+          <t>关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1355,24 +1347,24 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告；可见摘要：收藏 招标变更 广东 9分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1383,7 +1375,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1395,19 +1387,19 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429404126</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430039810</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)</t>
+          <t>陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1417,24 +1409,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)；可见摘要：收藏 招标公告 上海 2026-07-08；详情状态：受限，需人工核验</t>
+          <t>项目：陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告；可见摘要：收藏 招标公告 陕西 2026-07-10；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1457,19 +1449,19 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429489269</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429867103</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告</t>
+          <t>西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1479,24 +1471,24 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告；可见摘要：收藏 招标变更 河北 2026-07-05；详情状态：受限，需人工核验</t>
+          <t>项目：西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09；可见摘要：附件 收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1507,31 +1499,31 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>终止/流标</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428711615</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429704334</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告</t>
+          <t>中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1541,24 +1533,24 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>项目：纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告；可见摘要：收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)；可见摘要：收藏 招标预告 上海 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1569,7 +1561,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1581,46 +1573,46 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428537526</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-429701886</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397</t>
+          <t>【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告；可见摘要：收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1631,155 +1623,163 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419989</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429701915</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396</t>
+          <t>晶圆有机清洗机-招标公告</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>晶圆/衬底光学缺陷检测</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>晶圆有机清洗机</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>采购内容：晶圆有机清洗机；数量：1台；公告类型：招标公告；发布时间：2026-07-10</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419915</t>
+          <t>https://www.365trade.com.cn/zhwzb/843900.jhtml</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-14T09:31:20</t>
         </is>
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告</t>
+          <t>中数创和设备采购项目014结果公告</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>晶圆/衬底光学缺陷检测</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>中数创和设备采购项目014</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统，且公告明确晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告；可见摘要：附件 收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>采购内容：中数创和设备采购项目014；成交/中标方：黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2；成交/中标金额：000.00元；公告类型：结果公告；发布时间：2026-07-10</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>结果公告</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>000.00元</t>
+        </is>
+      </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428541747</t>
+          <t>https://www.365trade.com.cn/jhwzb/843422.jhtml</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-14T09:31:20</t>
         </is>
       </c>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告</t>
+          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1789,24 +1789,24 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1829,19 +1829,19 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434578</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429404126</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告</t>
+          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1851,24 +1851,24 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)；可见摘要：收藏 招标公告 上海 2026-07-08；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1891,19 +1891,19 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434575</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429489269</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1923,14 +1923,14 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告；可见摘要：收藏 招标公告 河北 22分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告；可见摘要：收藏 招标变更 河北 2026-07-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1941,31 +1941,31 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>终止/流标</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427329545</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428711615</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告</t>
+          <t>纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1975,24 +1975,24 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告；可见摘要：附件 收藏 招标变更 河北 2026-06-27；详情状态：受限，需人工核验</t>
+          <t>项目：纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告；可见摘要：收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -2003,58 +2003,58 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>终止/流标</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427255950</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428537526</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="25" ht="58" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)</t>
+          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)；可见摘要：收藏 招标预告 上海 2026-06-27；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -2065,58 +2065,58 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427280358</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419989</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="26" ht="58" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告</t>
+          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>项目：生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告；可见摘要：收藏 招标公告 江苏 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -2127,31 +2127,31 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427124669</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419915</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告</t>
+          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -2161,24 +2161,24 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告；可见摘要：附件 收藏 招标公告 安徽 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告；可见摘要：附件 收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -2201,19 +2201,19 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427174343</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428541747</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="28" ht="58" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2223,24 +2223,24 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告；可见摘要：标书 收藏 中标结果 北京 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -2251,58 +2251,58 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-427191692</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434578</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="29" ht="58" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -2325,46 +2325,46 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426951671</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434575</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396；可见摘要：收藏 招标公告 上海 12小时前；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告；可见摘要：收藏 招标公告 河北 22分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -2387,19 +2387,19 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426983145</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427329545</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="31" ht="58" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2409,24 +2409,24 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器；可见摘要：收藏 招标预告 上海 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告；可见摘要：附件 收藏 招标变更 河北 2026-06-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -2437,31 +2437,31 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>终止/流标</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427096376</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427255950</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14</t>
+          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2481,14 +2481,14 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>项目：2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14；可见摘要：收藏 招标公告 浙江 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)；可见摘要：收藏 招标预告 上海 2026-06-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -2511,61 +2511,57 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427057182</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427280358</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="33" ht="58" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>谈判采购公告</t>
+          <t>生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>CIM系统</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>RMS，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>采购内容：CIM系统；数量：一家；范围：CIM系统设备采购及有关技术服务、培训等，具体要求详见第五章采购需求；采购方：成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采；公告类型：采购公告；发布时间：2026-06-25</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采</t>
-        </is>
-      </c>
+          <t>项目：生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告；可见摘要：收藏 招标公告 江苏 2026-06-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>采购公告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -2577,19 +2573,19 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/837713.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427124669</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:51:21</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="34" ht="58" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2599,24 +2595,24 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>缺陷检测</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告；可见摘要：附件 收藏 中标结果 上海 2026-06-24；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告；可见摘要：附件 收藏 招标公告 安徽 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2627,31 +2623,31 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426498852</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427174343</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="35" ht="58" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2671,14 +2667,14 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告；可见摘要：标书 收藏 中标结果 北京 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2701,46 +2697,46 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426408417</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-427191692</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="36" ht="58" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218</t>
+          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2751,58 +2747,58 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426280043</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426951671</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="37" ht="58" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
+          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396；可见摘要：收藏 招标公告 上海 12小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2825,19 +2821,19 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426983145</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="38" ht="58" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
+          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2847,24 +2843,24 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器；可见摘要：收藏 招标预告 上海 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2875,31 +2871,31 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427096376</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="39" ht="58" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
+          <t>2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2919,14 +2915,14 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14；可见摘要：收藏 招标公告 浙江 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2937,7 +2933,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -2949,81 +2945,85 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427057182</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="40" ht="58" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
+          <t>谈判采购公告</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>CIM系统</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>RMS，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr"/>
+          <t>采购内容：CIM系统；数量：一家；范围：CIM系统设备采购及有关技术服务、培训等，具体要求详见第五章采购需求；采购方：成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采；公告类型：采购公告；发布时间：2026-06-25</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采</t>
+        </is>
+      </c>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>采购公告</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
+          <t>https://www.365trade.com.cn/zhwzb/837713.jhtml</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-06-26T10:51:21</t>
         </is>
       </c>
     </row>
     <row r="41" ht="58" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -3033,24 +3033,24 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告；可见摘要：附件 收藏 中标结果 上海 2026-06-24；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -3061,31 +3061,31 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426498852</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="42" ht="58" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -3095,24 +3095,24 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -3135,46 +3135,46 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426408417</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="43" ht="58" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
+          <t>上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -3185,31 +3185,31 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426280043</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="44" ht="58" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -3219,24 +3219,24 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -3247,31 +3247,31 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="45" ht="58" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -3291,14 +3291,14 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -3309,31 +3309,31 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="46" ht="58" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
+          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -3343,24 +3343,24 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
+          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -3383,19 +3383,19 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="47" ht="58" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
+          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -3405,24 +3405,24 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -3445,19 +3445,19 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="48" ht="58" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3467,24 +3467,24 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -3495,124 +3495,120 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="49" ht="58" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪【重新招标】-公开招标公告</t>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>外观检查机</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测，且公告具有半导体产业链语境</t>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>无锡中微掩模电子有限公司</t>
-        </is>
-      </c>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>公开招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10T14:16:35</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="50" ht="58" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
+          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>膜厚仪</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -3623,7 +3619,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -3635,46 +3631,46 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="51" ht="58" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
+          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
+          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -3697,19 +3693,19 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="52" ht="58" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
+          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3719,24 +3715,24 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>外观检测</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
+          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -3759,19 +3755,19 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="53" ht="58" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3781,24 +3777,24 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3809,31 +3805,31 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="54" ht="58" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3843,24 +3839,24 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>自动光学检查机</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3871,31 +3867,31 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="55" ht="58" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3905,24 +3901,24 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>晶圆表面缺陷检测</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -3933,91 +3929,529 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:31:53</t>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
     <row r="56" ht="58" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+          <t>缺陷检测仪【重新招标】-公开招标公告</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr"/>
+          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>无锡中微掩模电子有限公司</t>
+        </is>
+      </c>
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>公开招标公告</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="3" t="inlineStr">
         <is>
+          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10T14:16:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="58" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>检测仪</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>招标公告</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>进行中/未知</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20T10:31:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="58" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>光学量测设备</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>CD-SEM</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20T10:31:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="58" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>外观检测</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20T10:31:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="58" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>颗粒检测系统</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20T10:31:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="58" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>检测仪</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>招标变更</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>变更/澄清</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20T10:31:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="58" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>招标变更</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>变更/澄清</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20T10:31:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="58" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>检测设备</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="3" t="inlineStr">
+        <is>
           <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-421062373</t>
         </is>
       </c>
-      <c r="P56" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-16T10:31:53</t>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20T10:31:54</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P56"/>
+  <autoFilter ref="A1:P63"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -4074,10 +4508,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId62"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId56"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId63"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4110,7 +4551,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-16T10:35:33</t>
+          <t>2026-07-20T10:35:23</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4562,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
@@ -4143,7 +4584,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8">

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P63" headerRowCount="1">
-  <autoFilter ref="A1:P63"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P64" headerRowCount="1">
+  <autoFilter ref="A1:P64"/>
   <tableColumns count="16">
     <tableColumn id="1" name="项目名称"/>
     <tableColumn id="2" name="判断类别"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P63"/>
+  <dimension ref="A1:P64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -593,7 +593,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目-2026-07-16</t>
+          <t>麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目GDMS检测设备采购项目国际招标公告(1)-2435-264JT2026002</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -603,24 +603,24 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>项目：陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目-2026-07-16；可见摘要：附件 收藏 招标公告 陕西 11小时前；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目GDMS检测设备采购项目国际招标公告(1)-2435-264JT2026002；可见摘要：收藏 招标公告 河南 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -643,19 +643,19 @@
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%9B%86%E6%88%90%E7%94%B5%E8%B7%AF%20%E6%A3%80%E6%B5%8B#bidcenter-431023609</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-431545561</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目</t>
+          <t>陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目-2026-07-16</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>项目：陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目；可见摘要：附件 收藏 招标公告 陕西 12小时前；详情状态：受限，需人工核验</t>
+          <t>项目：陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目-2026-07-16；可见摘要：附件 收藏 招标公告 陕西 11小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
@@ -705,19 +705,19 @@
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%9B%86%E6%88%90%E7%94%B5%E8%B7%AF%20%E6%A3%80%E6%B5%8B#bidcenter-431017188</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%9B%86%E6%88%90%E7%94%B5%E8%B7%AF%20%E6%A3%80%E6%B5%8B#bidcenter-431023609</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="4" ht="58" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第4包中标结果公告</t>
+          <t>陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -727,17 +727,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第4包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
+          <t>项目：陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目；可见摘要：附件 收藏 招标公告 陕西 12小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
@@ -755,31 +755,31 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361360</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%9B%86%E6%88%90%E7%94%B5%E8%B7%AF%20%E6%A3%80%E6%B5%8B#bidcenter-431017188</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第3包中标结果公告</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第4包中标结果公告</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第3包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第4包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
@@ -829,19 +829,19 @@
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361355</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361360</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第2包中标结果公告</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第3包中标结果公告</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第2包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第3包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
@@ -891,19 +891,19 @@
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361358</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361355</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第1包中标结果公告</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第2包中标结果公告</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第1包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第2包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
@@ -953,19 +953,19 @@
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361353</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361358</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备重新招标澄清或变更公告</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第1包中标结果公告</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -975,17 +975,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>缺陷检测</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备重新招标澄清或变更公告；可见摘要：收藏 招标变更 上海 22小时前；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第1包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
@@ -1003,31 +1003,31 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430852656</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361353</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备重新招标澄清或变更公告(1)-0613-264025123686</t>
+          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备重新招标澄清或变更公告</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1047,14 +1047,14 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备重新招标澄清或变更公告(1)-0613-264025123686；可见摘要：收藏 招标变更 上海 32分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备重新招标澄清或变更公告；可见摘要：收藏 招标变更 上海 22小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -1077,19 +1077,19 @@
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430820283</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430852656</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）评标结果公示公告(1)-0821-264MSKZZ2202</t>
+          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备重新招标澄清或变更公告(1)-0613-264025123686</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1099,24 +1099,24 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）评标结果公示公告(1)-0821-264MSKZZ2202；可见摘要：收藏 中标结果 河南 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备重新招标澄清或变更公告(1)-0613-264025123686；可见摘要：收藏 招标变更 上海 32分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -1127,51 +1127,51 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430471714</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430820283</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>超光滑碳化硅光学元件无损清洗系统-公开招标公告</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）评标结果公示公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>晶圆/衬底光学缺陷检测</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>超光滑碳化硅光学元件无损清洗系统</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>采购内容：超光滑碳化硅光学元件无损清洗系统；数量：1套；公告类型：公开招标公告；发布时间：2026-07-15</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）评标结果公示公告(1)-0821-264MSKZZ2202；可见摘要：收藏 中标结果 河南 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
@@ -1184,74 +1184,74 @@
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>公开招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/845555.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430471714</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:35:32</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>北京大学2026年9月政府采购意向- 晶圆 检测 仪详细情况150.000000万元(人民币)</t>
+          <t>超光滑碳化硅光学元件无损清洗系统-公开招标公告</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>晶圆/衬底光学缺陷检测</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>超光滑碳化硅光学元件无损清洗系统</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>项目：北京大学2026年9月政府采购意向- 晶圆 检测 仪详细情况150.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-07-14；详情状态：受限，需人工核验</t>
+          <t>采购内容：超光滑碳化硅光学元件无损清洗系统；数量：1套；公告类型：公开招标公告；发布时间：2026-07-15</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>公开招标公告</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1263,19 +1263,19 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-430314307</t>
+          <t>https://www.365trade.com.cn/zhwzb/845555.jhtml</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-16T10:35:32</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告</t>
+          <t>北京大学2026年9月政府采购意向- 晶圆 检测 仪详细情况150.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告；可见摘要：收藏 招标变更 广东 23小时前；详情状态：受限，需人工核验</t>
+          <t>项目：北京大学2026年9月政府采购意向- 晶圆 检测 仪详细情况150.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-07-14；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1325,19 +1325,19 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430062786</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-430314307</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告</t>
+          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1357,14 +1357,14 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>项目：关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告；可见摘要：收藏 招标变更 广东 9分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告；可见摘要：收藏 招标变更 广东 23小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1387,19 +1387,19 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430039810</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430062786</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告</t>
+          <t>关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1409,24 +1409,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>项目：陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告；可见摘要：收藏 招标公告 陕西 2026-07-10；详情状态：受限，需人工核验</t>
+          <t>项目：关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告；可见摘要：收藏 招标变更 广东 9分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1449,19 +1449,19 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429867103</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430039810</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09</t>
+          <t>陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1471,17 +1471,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>项目：西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09；可见摘要：附件 收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告；可见摘要：收藏 招标公告 陕西 2026-07-10；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
@@ -1511,19 +1511,19 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429704334</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429867103</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)</t>
+          <t>西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1533,17 +1533,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)；可见摘要：收藏 招标预告 上海 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09；可见摘要：附件 收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1573,19 +1573,19 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-429701886</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429704334</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告</t>
+          <t>中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>项目：【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告；可见摘要：收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)；可见摘要：收藏 招标预告 上海 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -1635,39 +1635,39 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429701915</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-429701886</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>晶圆有机清洗机-招标公告</t>
+          <t>【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>晶圆/衬底光学缺陷检测</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>晶圆有机清洗机</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>采购内容：晶圆有机清洗机；数量：1台；公告类型：招标公告；发布时间：2026-07-10</t>
+          <t>项目：【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告；可见摘要：收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
@@ -1680,7 +1680,7 @@
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1697,19 +1697,19 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/843900.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429701915</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:31:20</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>中数创和设备采购项目014结果公告</t>
+          <t>晶圆有机清洗机-招标公告</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1719,25 +1719,21 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>中数创和设备采购项目014</t>
+          <t>晶圆有机清洗机</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>检测系统，且公告明确晶圆/硅片/SiC/衬底场景</t>
+          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>采购内容：中数创和设备采购项目014；成交/中标方：黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2；成交/中标金额：000.00元；公告类型：结果公告；发布时间：2026-07-10</t>
+          <t>采购内容：晶圆有机清洗机；数量：1台；公告类型：招标公告；发布时间：2026-07-10</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2</t>
-        </is>
-      </c>
+      <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
@@ -1751,23 +1747,19 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>结果公告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>000.00元</t>
-        </is>
-      </c>
+      <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/jhwzb/843422.jhtml</t>
+          <t>https://www.365trade.com.cn/zhwzb/843900.jhtml</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -1779,69 +1771,77 @@
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686</t>
+          <t>中数创和设备采购项目014结果公告</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>晶圆/衬底光学缺陷检测</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>中数创和设备采购项目014</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统，且公告明确晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
+          <t>采购内容：中数创和设备采购项目014；成交/中标方：黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2；成交/中标金额：000.00元；公告类型：结果公告；发布时间：2026-07-10</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>结果公告</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>000.00元</t>
+        </is>
+      </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429404126</t>
+          <t>https://www.365trade.com.cn/jhwzb/843422.jhtml</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-14T09:31:20</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)</t>
+          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1861,14 +1861,14 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)；可见摘要：收藏 招标公告 上海 2026-07-08；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1891,19 +1891,19 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429489269</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429404126</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告</t>
+          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1913,24 +1913,24 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告；可见摘要：收藏 招标变更 河北 2026-07-05；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)；可见摘要：收藏 招标公告 上海 2026-07-08；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1941,31 +1941,31 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>终止/流标</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428711615</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429489269</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1975,24 +1975,24 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>项目：纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告；可见摘要：收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告；可见摘要：收藏 招标变更 河北 2026-07-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -2003,51 +2003,51 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>终止/流标</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428537526</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428711615</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="25" ht="58" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397</t>
+          <t>纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告；可见摘要：收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
@@ -2065,31 +2065,31 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419989</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428537526</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="26" ht="58" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396</t>
+          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
@@ -2139,39 +2139,39 @@
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419915</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419989</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告</t>
+          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告；可见摘要：附件 收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
@@ -2189,31 +2189,31 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428541747</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419915</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="28" ht="58" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告</t>
+          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2223,24 +2223,24 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
+          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告；可见摘要：附件 收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -2263,19 +2263,19 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434578</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428541747</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="29" ht="58" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
@@ -2325,19 +2325,19 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434575</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434578</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2347,24 +2347,24 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告；可见摘要：收藏 招标公告 河北 22分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -2387,19 +2387,19 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427329545</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434575</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="31" ht="58" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2419,14 +2419,14 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告；可见摘要：附件 收藏 招标变更 河北 2026-06-27；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告；可见摘要：收藏 招标公告 河北 22分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -2437,31 +2437,31 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>终止/流标</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427255950</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427329545</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2471,17 +2471,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)；可见摘要：收藏 招标预告 上海 2026-06-27；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告；可见摘要：附件 收藏 招标变更 河北 2026-06-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
@@ -2499,31 +2499,31 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>终止/流标</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427280358</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427255950</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="33" ht="58" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告</t>
+          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2533,24 +2533,24 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>项目：生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告；可见摘要：收藏 招标公告 江苏 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)；可见摘要：收藏 招标预告 上海 2026-06-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -2573,19 +2573,19 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427124669</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427280358</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="34" ht="58" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告</t>
+          <t>生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2595,17 +2595,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告；可见摘要：附件 收藏 招标公告 安徽 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告；可见摘要：收藏 招标公告 江苏 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
@@ -2635,19 +2635,19 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427174343</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427124669</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="35" ht="58" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2657,17 +2657,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>缺陷检测</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告；可见摘要：标书 收藏 中标结果 北京 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告；可见摘要：附件 收藏 招标公告 安徽 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
@@ -2685,51 +2685,51 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-427191692</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427174343</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="36" ht="58" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告；可见摘要：标书 收藏 中标结果 北京 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
@@ -2747,31 +2747,31 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426951671</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-427191692</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="37" ht="58" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396</t>
+          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396；可见摘要：收藏 招标公告 上海 12小时前；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
@@ -2821,39 +2821,39 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426983145</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426951671</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="38" ht="58" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器</t>
+          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器；可见摘要：收藏 招标预告 上海 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396；可见摘要：收藏 招标公告 上海 12小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -2883,19 +2883,19 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427096376</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426983145</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="39" ht="58" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14</t>
+          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>项目：2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14；可见摘要：收藏 招标公告 浙江 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器；可见摘要：收藏 招标预告 上海 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -2945,61 +2945,57 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427057182</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427096376</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="40" ht="58" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>谈判采购公告</t>
+          <t>2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>CIM系统</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>RMS，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>采购内容：CIM系统；数量：一家；范围：CIM系统设备采购及有关技术服务、培训等，具体要求详见第五章采购需求；采购方：成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采；公告类型：采购公告；发布时间：2026-06-25</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采</t>
-        </is>
-      </c>
+          <t>项目：2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14；可见摘要：收藏 招标公告 浙江 2026-06-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>采购公告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -3011,81 +3007,85 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/837713.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427057182</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:51:21</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="41" ht="58" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告</t>
+          <t>谈判采购公告</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>CIM系统</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>RMS，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告；可见摘要：附件 收藏 中标结果 上海 2026-06-24；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr"/>
+          <t>采购内容：CIM系统；数量：一家；范围：CIM系统设备采购及有关技术服务、培训等，具体要求详见第五章采购需求；采购方：成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采；公告类型：采购公告；发布时间：2026-06-25</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采</t>
+        </is>
+      </c>
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>采购公告</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426498852</t>
+          <t>https://www.365trade.com.cn/zhwzb/837713.jhtml</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-06-26T10:51:21</t>
         </is>
       </c>
     </row>
     <row r="42" ht="58" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -3105,14 +3105,14 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告；可见摘要：附件 收藏 中标结果 上海 2026-06-24；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -3135,19 +3135,19 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426408417</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426498852</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="43" ht="58" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -3157,17 +3157,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
@@ -3197,19 +3197,19 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426280043</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426408417</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="44" ht="58" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
+          <t>上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -3219,24 +3219,24 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -3247,31 +3247,31 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426280043</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="45" ht="58" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -3281,24 +3281,24 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -3309,31 +3309,31 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="46" ht="58" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -3343,17 +3343,17 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
@@ -3371,31 +3371,31 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="47" ht="58" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
+          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
@@ -3438,26 +3438,26 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="48" ht="58" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
+          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3467,24 +3467,24 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -3495,31 +3495,31 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="49" ht="58" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -3529,24 +3529,24 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
@@ -3557,51 +3557,51 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="50" ht="58" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪</t>
+          <t>外观检查机</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
@@ -3619,58 +3619,58 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="51" ht="58" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
+          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>膜厚仪</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -3681,31 +3681,31 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="52" ht="58" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
+          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3715,24 +3715,24 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
+          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -3755,19 +3755,19 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="53" ht="58" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
+          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3787,14 +3787,14 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
+          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3805,31 +3805,31 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="54" ht="58" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3839,17 +3839,17 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
@@ -3867,31 +3867,31 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="55" ht="58" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
+          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3901,24 +3901,24 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测</t>
+          <t>自动光学检查机</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -3941,46 +3941,42 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="56" ht="58" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪【重新招标】-公开招标公告</t>
+          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>晶圆表面缺陷检测</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测，且公告具有半导体产业链语境</t>
+          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>无锡中微掩模电子有限公司</t>
-        </is>
-      </c>
+          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3990,74 +3986,78 @@
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>公开招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10T14:16:35</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="57" ht="58" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
+          <t>缺陷检测仪【重新招标】-公开招标公告</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr"/>
+          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>无锡中微掩模电子有限公司</t>
+        </is>
+      </c>
       <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>公开招标公告</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
@@ -4069,46 +4069,46 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
+          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-06-10T14:16:35</t>
         </is>
       </c>
     </row>
     <row r="58" ht="58" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -4119,58 +4119,58 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="59" ht="58" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
+          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>外观检测</t>
+          <t>CD-SEM</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
@@ -4193,19 +4193,19 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="60" ht="58" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
+          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -4215,24 +4215,24 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统</t>
+          <t>外观检测</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -4255,19 +4255,19 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="61" ht="58" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -4277,17 +4277,17 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>颗粒检测系统</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
@@ -4305,31 +4305,31 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="62" ht="58" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -4339,24 +4339,24 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -4379,19 +4379,19 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T10:31:54</t>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
     <row r="63" ht="58" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -4401,17 +4401,17 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>外观检查机</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr"/>
@@ -4429,29 +4429,91 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="3" t="inlineStr">
         <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21T12:01:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="58" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>检测设备</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="3" t="inlineStr">
+        <is>
           <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-421062373</t>
         </is>
       </c>
-      <c r="P63" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-20T10:31:54</t>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21T12:01:58</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P63"/>
+  <autoFilter ref="A1:P64"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -4515,10 +4577,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId63"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId63"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId64"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4551,7 +4614,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-20T10:35:23</t>
+          <t>2026-07-21T12:05:26</t>
         </is>
       </c>
     </row>
@@ -4562,7 +4625,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6">
@@ -4584,7 +4647,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8">

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$68</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P64" headerRowCount="1">
-  <autoFilter ref="A1:P64"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P68" headerRowCount="1">
+  <autoFilter ref="A1:P68"/>
   <tableColumns count="16">
     <tableColumn id="1" name="项目名称"/>
     <tableColumn id="2" name="判断类别"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P64"/>
+  <dimension ref="A1:P68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -593,7 +593,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目GDMS检测设备采购项目国际招标公告(1)-2435-264JT2026002</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）开标信息</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -603,24 +603,24 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目GDMS检测设备采购项目国际招标公告(1)-2435-264JT2026002；可见摘要：收藏 招标公告 河南 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）开标信息；可见摘要：收藏 中标结果 安徽 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -631,7 +631,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -643,19 +643,19 @@
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-431545561</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431784773</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目-2026-07-16</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）开标信息</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -665,24 +665,24 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>项目：陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目-2026-07-16；可见摘要：附件 收藏 招标公告 陕西 11小时前；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）开标信息；可见摘要：收藏 中标结果 安徽 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -693,7 +693,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -705,19 +705,19 @@
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%9B%86%E6%88%90%E7%94%B5%E8%B7%AF%20%E6%A3%80%E6%B5%8B#bidcenter-431023609</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431784789</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="4" ht="58" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目</t>
+          <t>合肥丰创光罩有限公司光 掩模 缺陷 检测 仪报废处置项目招标公告</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -727,24 +727,24 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>掩模缺陷检测仪</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>掩模缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>项目：陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目；可见摘要：附件 收藏 招标公告 陕西 12小时前；详情状态：受限，需人工核验</t>
+          <t>项目：合肥丰创光罩有限公司光 掩模 缺陷 检测 仪报废处置项目招标公告；可见摘要：收藏 招标公告 安徽 15小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -767,19 +767,19 @@
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%9B%86%E6%88%90%E7%94%B5%E8%B7%AF%20%E6%A3%80%E6%B5%8B#bidcenter-431017188</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E6%A3%80%E6%B5%8B#bidcenter-431811305</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第4包中标结果公告</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购项目单一来源采购邀请书</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -789,24 +789,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第4包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购项目单一来源采购邀请书；可见摘要：收藏 招标公告 河北 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -817,31 +817,31 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361360</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-431794027</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第3包中标结果公告</t>
+          <t>麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目GDMS检测设备采购项目国际招标公告(1)-2435-264JT2026002</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -851,24 +851,24 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第3包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目GDMS检测设备采购项目国际招标公告(1)-2435-264JT2026002；可见摘要：收藏 招标公告 河南 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -879,31 +879,31 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361355</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-431545561</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第2包中标结果公告</t>
+          <t>陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目-2026-07-16</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -913,17 +913,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第2包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
+          <t>项目：陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目-2026-07-16；可见摘要：附件 收藏 招标公告 陕西 11小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
@@ -941,31 +941,31 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361358</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%9B%86%E6%88%90%E7%94%B5%E8%B7%AF%20%E6%A3%80%E6%B5%8B#bidcenter-431023609</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第1包中标结果公告</t>
+          <t>陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -975,17 +975,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第1包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
+          <t>项目：陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目；可见摘要：附件 收藏 招标公告 陕西 12小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
@@ -1003,31 +1003,31 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361353</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%9B%86%E6%88%90%E7%94%B5%E8%B7%AF%20%E6%A3%80%E6%B5%8B#bidcenter-431017188</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备重新招标澄清或变更公告</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第4包中标结果公告</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1037,17 +1037,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>缺陷检测</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备重新招标澄清或变更公告；可见摘要：收藏 招标变更 上海 22小时前；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第4包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
@@ -1065,31 +1065,31 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430852656</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361360</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备重新招标澄清或变更公告(1)-0613-264025123686</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第3包中标结果公告</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1099,24 +1099,24 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>缺陷检测</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备重新招标澄清或变更公告(1)-0613-264025123686；可见摘要：收藏 招标变更 上海 32分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第3包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -1127,31 +1127,31 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430820283</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361355</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）评标结果公示公告(1)-0821-264MSKZZ2202</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第2包中标结果公告</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>缺陷检测</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）评标结果公示公告(1)-0821-264MSKZZ2202；可见摘要：收藏 中标结果 河南 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第2包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1201,81 +1201,81 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430471714</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361358</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>超光滑碳化硅光学元件无损清洗系统-公开招标公告</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第1包中标结果公告</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>晶圆/衬底光学缺陷检测</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>超光滑碳化硅光学元件无损清洗系统</t>
+          <t>缺陷检测</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>采购内容：超光滑碳化硅光学元件无损清洗系统；数量：1套；公告类型：公开招标公告；发布时间：2026-07-15</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第1包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>公开招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/845555.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361353</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:35:32</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>北京大学2026年9月政府采购意向- 晶圆 检测 仪详细情况150.000000万元(人民币)</t>
+          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备重新招标澄清或变更公告</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1285,24 +1285,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>项目：北京大学2026年9月政府采购意向- 晶圆 检测 仪详细情况150.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-07-14；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备重新招标澄清或变更公告；可见摘要：收藏 招标变更 上海 22小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1313,31 +1313,31 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-430314307</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430852656</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告</t>
+          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备重新招标澄清或变更公告(1)-0613-264025123686</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1347,24 +1347,24 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告；可见摘要：收藏 招标变更 广东 23小时前；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备重新招标澄清或变更公告(1)-0613-264025123686；可见摘要：收藏 招标变更 上海 32分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1380,26 +1380,26 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430062786</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430820283</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）评标结果公示公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1409,24 +1409,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>项目：关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告；可见摘要：收藏 招标变更 广东 9分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）评标结果公示公告(1)-0821-264MSKZZ2202；可见摘要：收藏 中标结果 河南 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1437,69 +1437,69 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430039810</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430471714</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告</t>
+          <t>超光滑碳化硅光学元件无损清洗系统-公开招标公告</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>晶圆/衬底光学缺陷检测</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测</t>
+          <t>超光滑碳化硅光学元件无损清洗系统</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>项目：陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告；可见摘要：收藏 招标公告 陕西 2026-07-10；详情状态：受限，需人工核验</t>
+          <t>采购内容：超光滑碳化硅光学元件无损清洗系统；数量：1套；公告类型：公开招标公告；发布时间：2026-07-15</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>公开招标公告</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1511,19 +1511,19 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429867103</t>
+          <t>https://www.365trade.com.cn/zhwzb/845555.jhtml</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-16T10:35:32</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09</t>
+          <t>北京大学2026年9月政府采购意向- 晶圆 检测 仪详细情况150.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1533,24 +1533,24 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>项目：西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09；可见摘要：附件 收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：北京大学2026年9月政府采购意向- 晶圆 检测 仪详细情况150.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-07-14；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1573,19 +1573,19 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429704334</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-430314307</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)</t>
+          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1595,24 +1595,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)；可见摘要：收藏 招标预告 上海 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告；可见摘要：收藏 招标变更 广东 23小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -1635,19 +1635,19 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-429701886</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430062786</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告</t>
+          <t>关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1657,24 +1657,24 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>项目：【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告；可见摘要：收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告；可见摘要：收藏 招标变更 广东 9分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1697,39 +1697,39 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429701915</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430039810</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>晶圆有机清洗机-招标公告</t>
+          <t>陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>晶圆/衬底光学缺陷检测</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>晶圆有机清洗机</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>采购内容：晶圆有机清洗机；数量：1台；公告类型：招标公告；发布时间：2026-07-10</t>
+          <t>项目：陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告；可见摘要：收藏 招标公告 陕西 2026-07-10；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
@@ -1742,7 +1742,7 @@
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1759,47 +1759,43 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/843900.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429867103</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:31:20</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>中数创和设备采购项目014结果公告</t>
+          <t>西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>晶圆/衬底光学缺陷检测</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>中数创和设备采购项目014</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>检测系统，且公告明确晶圆/硅片/SiC/衬底场景</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>采购内容：中数创和设备采购项目014；成交/中标方：黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2；成交/中标金额：000.00元；公告类型：结果公告；发布时间：2026-07-10</t>
+          <t>项目：西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09；可见摘要：附件 收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2</t>
-        </is>
-      </c>
+      <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
@@ -1808,40 +1804,36 @@
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>结果公告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>000.00元</t>
-        </is>
-      </c>
+      <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/jhwzb/843422.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429704334</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:31:20</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686</t>
+          <t>中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1851,24 +1843,24 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)；可见摘要：收藏 招标预告 上海 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1879,7 +1871,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -1891,19 +1883,19 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429404126</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-429701886</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)</t>
+          <t>【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1913,24 +1905,24 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)；可见摘要：收藏 招标公告 上海 2026-07-08；详情状态：受限，需人工核验</t>
+          <t>项目：【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告；可见摘要：收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1953,170 +1945,178 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429489269</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429701915</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告</t>
+          <t>晶圆有机清洗机-招标公告</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>晶圆/衬底光学缺陷检测</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>晶圆有机清洗机</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告；可见摘要：收藏 招标变更 河北 2026-07-05；详情状态：受限，需人工核验</t>
+          <t>采购内容：晶圆有机清洗机；数量：1台；公告类型：招标公告；发布时间：2026-07-10</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>终止/流标</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428711615</t>
+          <t>https://www.365trade.com.cn/zhwzb/843900.jhtml</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-14T09:31:20</t>
         </is>
       </c>
     </row>
     <row r="25" ht="58" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告</t>
+          <t>中数创和设备采购项目014结果公告</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>晶圆/衬底光学缺陷检测</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>中数创和设备采购项目014</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统，且公告明确晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>项目：纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告；可见摘要：收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>采购内容：中数创和设备采购项目014；成交/中标方：黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2；成交/中标金额：000.00元；公告类型：结果公告；发布时间：2026-07-10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>结果公告</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>000.00元</t>
+        </is>
+      </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428537526</t>
+          <t>https://www.365trade.com.cn/jhwzb/843422.jhtml</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-14T09:31:20</t>
         </is>
       </c>
     </row>
     <row r="26" ht="58" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397</t>
+          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -2127,58 +2127,58 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419989</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429404126</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396</t>
+          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)；可见摘要：收藏 招标公告 上海 2026-07-08；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -2189,31 +2189,31 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419915</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429489269</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="28" ht="58" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2223,24 +2223,24 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告；可见摘要：附件 收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告；可见摘要：收藏 招标变更 河北 2026-07-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -2251,31 +2251,31 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>终止/流标</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428541747</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428711615</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="29" ht="58" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告</t>
+          <t>纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -2285,24 +2285,24 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
+          <t>项目：纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告；可见摘要：收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -2325,46 +2325,46 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434578</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428537526</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告</t>
+          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -2375,58 +2375,58 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434575</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419989</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="31" ht="58" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告</t>
+          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告；可见摘要：收藏 招标公告 河北 22分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -2437,31 +2437,31 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427329545</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419915</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告</t>
+          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2471,24 +2471,24 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告；可见摘要：附件 收藏 招标变更 河北 2026-06-27；详情状态：受限，需人工核验</t>
+          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告；可见摘要：附件 收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2499,31 +2499,31 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>终止/流标</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427255950</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428541747</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="33" ht="58" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2533,24 +2533,24 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)；可见摘要：收藏 招标预告 上海 2026-06-27；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -2573,19 +2573,19 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427280358</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434578</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="34" ht="58" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2595,24 +2595,24 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>项目：生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告；可见摘要：收藏 招标公告 江苏 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2635,19 +2635,19 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427124669</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434575</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="35" ht="58" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2657,24 +2657,24 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告；可见摘要：附件 收藏 招标公告 安徽 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告；可见摘要：收藏 招标公告 河北 22分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2697,19 +2697,19 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427174343</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427329545</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="36" ht="58" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2719,24 +2719,24 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告；可见摘要：标书 收藏 中标结果 北京 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告；可见摘要：附件 收藏 招标变更 河北 2026-06-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2747,58 +2747,58 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>终止/流标</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-427191692</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427255950</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="37" ht="58" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397</t>
+          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)；可见摘要：收藏 招标预告 上海 2026-06-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -2821,39 +2821,39 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426951671</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427280358</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="38" ht="58" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396</t>
+          <t>生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396；可见摘要：收藏 招标公告 上海 12小时前；详情状态：受限，需人工核验</t>
+          <t>项目：生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告；可见摘要：收藏 招标公告 江苏 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
@@ -2883,19 +2883,19 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426983145</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427124669</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="39" ht="58" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2905,17 +2905,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>缺陷检测</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器；可见摘要：收藏 招标预告 上海 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告；可见摘要：附件 收藏 招标公告 安徽 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -2945,19 +2945,19 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427096376</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427174343</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="40" ht="58" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>项目：2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14；可见摘要：收藏 招标公告 浙江 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告；可见摘要：标书 收藏 中标结果 北京 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
@@ -2995,73 +2995,69 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427057182</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-427191692</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="41" ht="58" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>谈判采购公告</t>
+          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>CIM系统</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>RMS，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>采购内容：CIM系统；数量：一家；范围：CIM系统设备采购及有关技术服务、培训等，具体要求详见第五章采购需求；采购方：成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采；公告类型：采购公告；发布时间：2026-06-25</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采</t>
-        </is>
-      </c>
+          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>采购公告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -3073,46 +3069,46 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/837713.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426951671</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:51:21</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="42" ht="58" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告</t>
+          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告；可见摘要：附件 收藏 中标结果 上海 2026-06-24；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396；可见摘要：收藏 招标公告 上海 12小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -3123,31 +3119,31 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426498852</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426983145</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="43" ht="58" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762</t>
+          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -3167,14 +3163,14 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
+          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器；可见摘要：收藏 招标预告 上海 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -3185,31 +3181,31 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426408417</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427096376</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="44" ht="58" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218</t>
+          <t>2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -3219,24 +3215,24 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
+          <t>项目：2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14；可见摘要：收藏 招标公告 浙江 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -3247,69 +3243,73 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426280043</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427057182</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="45" ht="58" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
+          <t>谈判采购公告</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>CIM系统</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>RMS，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr"/>
+          <t>采购内容：CIM系统；数量：一家；范围：CIM系统设备采购及有关技术服务、培训等，具体要求详见第五章采购需求；采购方：成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采；公告类型：采购公告；发布时间：2026-06-25</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采</t>
+        </is>
+      </c>
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>采购公告</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -3321,19 +3321,19 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
+          <t>https://www.365trade.com.cn/zhwzb/837713.jhtml</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-06-26T10:51:21</t>
         </is>
       </c>
     </row>
     <row r="46" ht="58" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -3343,24 +3343,24 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告；可见摘要：附件 收藏 中标结果 上海 2026-06-24；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -3371,31 +3371,31 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426498852</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="47" ht="58" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -3415,14 +3415,14 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -3438,26 +3438,26 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426408417</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="48" ht="58" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
+          <t>上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3467,24 +3467,24 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -3507,19 +3507,19 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426280043</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="49" ht="58" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -3529,24 +3529,24 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
@@ -3569,19 +3569,19 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="50" ht="58" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3591,24 +3591,24 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -3619,58 +3619,58 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="51" ht="58" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
+          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
@@ -3693,19 +3693,19 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="52" ht="58" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
+          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3715,24 +3715,24 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -3755,19 +3755,19 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="53" ht="58" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3777,24 +3777,24 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3805,31 +3805,31 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="54" ht="58" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3839,24 +3839,24 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>外观检查机</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3867,58 +3867,58 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="55" ht="58" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
+          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机</t>
+          <t>膜厚仪</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -3929,31 +3929,31 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="56" ht="58" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
+          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3963,24 +3963,24 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
+          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -4003,85 +4003,81 @@
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="57" ht="58" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪【重新招标】-公开招标公告</t>
+          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>无锡中微掩模电子有限公司</t>
-        </is>
-      </c>
+          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>公开招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10T14:16:35</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="58" ht="58" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -4091,24 +4087,24 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -4131,46 +4127,46 @@
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="59" ht="58" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
+          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM</t>
+          <t>自动光学检查机</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
@@ -4193,19 +4189,19 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="60" ht="58" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
+          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -4215,24 +4211,24 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>外观检测</t>
+          <t>晶圆表面缺陷检测</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
+          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -4255,81 +4251,85 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="61" ht="58" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
+          <t>缺陷检测仪【重新招标】-公开招标公告</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr"/>
+          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>无锡中微掩模电子有限公司</t>
+        </is>
+      </c>
       <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>公开招标公告</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-06-10T14:16:35</t>
         </is>
       </c>
     </row>
     <row r="62" ht="58" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -4349,14 +4349,14 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -4367,58 +4367,58 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="63" ht="58" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>CD-SEM</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
@@ -4429,31 +4429,31 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:01:58</t>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
     <row r="64" ht="58" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4463,24 +4463,24 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>外观检测</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
@@ -4503,17 +4503,265 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="3" t="inlineStr">
         <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22T10:32:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="58" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>颗粒检测系统</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22T10:32:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="58" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>检测仪</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>招标变更</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>变更/澄清</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22T10:32:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="58" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>招标变更</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>变更/澄清</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22T10:32:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="58" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>检测设备</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="3" t="inlineStr">
+        <is>
           <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-421062373</t>
         </is>
       </c>
-      <c r="P64" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-21T12:01:58</t>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22T10:32:05</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P64"/>
+  <autoFilter ref="A1:P68"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -4578,10 +4826,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O68" r:id="rId67"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId64"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId68"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4614,7 +4866,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-21T12:05:26</t>
+          <t>2026-07-22T10:35:43</t>
         </is>
       </c>
     </row>
@@ -4625,7 +4877,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -4647,7 +4899,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8">

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P68" headerRowCount="1">
-  <autoFilter ref="A1:P68"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P69" headerRowCount="1">
+  <autoFilter ref="A1:P69"/>
   <tableColumns count="16">
     <tableColumn id="1" name="项目名称"/>
     <tableColumn id="2" name="判断类别"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P68"/>
+  <dimension ref="A1:P69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -593,7 +593,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）开标信息</t>
+          <t>2026第三季度 检测 仪器生产物料采购及成品备货专项 芯片</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -603,24 +603,24 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）开标信息；可见摘要：收藏 中标结果 安徽 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：2026第三季度 检测 仪器生产物料采购及成品备货专项 芯片；可见摘要：收藏 招标公告 浙江 14分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -631,7 +631,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -643,19 +643,19 @@
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431784773</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-432133611</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）开标信息</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）开标信息</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）开标信息；可见摘要：收藏 中标结果 安徽 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）开标信息；可见摘要：收藏 中标结果 安徽 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
@@ -705,19 +705,19 @@
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431784789</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431784773</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="4" ht="58" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>合肥丰创光罩有限公司光 掩模 缺陷 检测 仪报废处置项目招标公告</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）开标信息</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -727,17 +727,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>掩模缺陷检测仪</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>掩模缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥丰创光罩有限公司光 掩模 缺陷 检测 仪报废处置项目招标公告；可见摘要：收藏 招标公告 安徽 15小时前；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）开标信息；可见摘要：收藏 中标结果 安徽 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -767,19 +767,19 @@
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E6%A3%80%E6%B5%8B#bidcenter-431811305</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431784789</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购项目单一来源采购邀请书</t>
+          <t>合肥丰创光罩有限公司光 掩模 缺陷 检测 仪报废处置项目招标公告</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -789,17 +789,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>掩模缺陷检测仪</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>掩模缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购项目单一来源采购邀请书；可见摘要：收藏 招标公告 河北 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：合肥丰创光罩有限公司光 掩模 缺陷 检测 仪报废处置项目招标公告；可见摘要：收藏 招标公告 安徽 15小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
@@ -829,19 +829,19 @@
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-431794027</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E6%A3%80%E6%B5%8B#bidcenter-431811305</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目GDMS检测设备采购项目国际招标公告(1)-2435-264JT2026002</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购项目单一来源采购邀请书</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -851,24 +851,24 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目GDMS检测设备采购项目国际招标公告(1)-2435-264JT2026002；可见摘要：收藏 招标公告 河南 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购项目单一来源采购邀请书；可见摘要：收藏 招标公告 河北 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -891,19 +891,19 @@
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-431545561</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-431794027</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目-2026-07-16</t>
+          <t>麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目GDMS检测设备采购项目国际招标公告(1)-2435-264JT2026002</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -913,24 +913,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>项目：陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目-2026-07-16；可见摘要：附件 收藏 招标公告 陕西 11小时前；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目GDMS检测设备采购项目国际招标公告(1)-2435-264JT2026002；可见摘要：收藏 招标公告 河南 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -953,19 +953,19 @@
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%9B%86%E6%88%90%E7%94%B5%E8%B7%AF%20%E6%A3%80%E6%B5%8B#bidcenter-431023609</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-431545561</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目</t>
+          <t>陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目-2026-07-16</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>项目：陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目；可见摘要：附件 收藏 招标公告 陕西 12小时前；详情状态：受限，需人工核验</t>
+          <t>项目：陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目-2026-07-16；可见摘要：附件 收藏 招标公告 陕西 11小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
@@ -1015,19 +1015,19 @@
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%9B%86%E6%88%90%E7%94%B5%E8%B7%AF%20%E6%A3%80%E6%B5%8B#bidcenter-431017188</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%9B%86%E6%88%90%E7%94%B5%E8%B7%AF%20%E6%A3%80%E6%B5%8B#bidcenter-431023609</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第4包中标结果公告</t>
+          <t>陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1037,17 +1037,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第4包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
+          <t>项目：陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目；可见摘要：附件 收藏 招标公告 陕西 12小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
@@ -1065,31 +1065,31 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361360</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%9B%86%E6%88%90%E7%94%B5%E8%B7%AF%20%E6%A3%80%E6%B5%8B#bidcenter-431017188</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第3包中标结果公告</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第4包中标结果公告</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第3包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第4包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
@@ -1139,19 +1139,19 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361355</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361360</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第2包中标结果公告</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第3包中标结果公告</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第2包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第3包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
@@ -1201,19 +1201,19 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361358</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361355</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第1包中标结果公告</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第2包中标结果公告</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第1包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第2包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
@@ -1263,19 +1263,19 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361353</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361358</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备重新招标澄清或变更公告</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第1包中标结果公告</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>缺陷检测</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备重新招标澄清或变更公告；可见摘要：收藏 招标变更 上海 22小时前；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第1包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
@@ -1313,31 +1313,31 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430852656</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361353</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备重新招标澄清或变更公告(1)-0613-264025123686</t>
+          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备重新招标澄清或变更公告</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1357,14 +1357,14 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备重新招标澄清或变更公告(1)-0613-264025123686；可见摘要：收藏 招标变更 上海 32分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备重新招标澄清或变更公告；可见摘要：收藏 招标变更 上海 22小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1387,19 +1387,19 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430820283</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430852656</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）评标结果公示公告(1)-0821-264MSKZZ2202</t>
+          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备重新招标澄清或变更公告(1)-0613-264025123686</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1409,24 +1409,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）评标结果公示公告(1)-0821-264MSKZZ2202；可见摘要：收藏 中标结果 河南 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备重新招标澄清或变更公告(1)-0613-264025123686；可见摘要：收藏 招标变更 上海 32分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1437,51 +1437,51 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430471714</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430820283</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>超光滑碳化硅光学元件无损清洗系统-公开招标公告</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）评标结果公示公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>晶圆/衬底光学缺陷检测</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>超光滑碳化硅光学元件无损清洗系统</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>采购内容：超光滑碳化硅光学元件无损清洗系统；数量：1套；公告类型：公开招标公告；发布时间：2026-07-15</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）评标结果公示公告(1)-0821-264MSKZZ2202；可见摘要：收藏 中标结果 河南 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
@@ -1494,74 +1494,74 @@
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>公开招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/845555.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430471714</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:35:32</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>北京大学2026年9月政府采购意向- 晶圆 检测 仪详细情况150.000000万元(人民币)</t>
+          <t>超光滑碳化硅光学元件无损清洗系统-公开招标公告</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>晶圆/衬底光学缺陷检测</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>超光滑碳化硅光学元件无损清洗系统</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>项目：北京大学2026年9月政府采购意向- 晶圆 检测 仪详细情况150.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-07-14；详情状态：受限，需人工核验</t>
+          <t>采购内容：超光滑碳化硅光学元件无损清洗系统；数量：1套；公告类型：公开招标公告；发布时间：2026-07-15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>公开招标公告</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1573,19 +1573,19 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-430314307</t>
+          <t>https://www.365trade.com.cn/zhwzb/845555.jhtml</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-16T10:35:32</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告</t>
+          <t>北京大学2026年9月政府采购意向- 晶圆 检测 仪详细情况150.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告；可见摘要：收藏 招标变更 广东 23小时前；详情状态：受限，需人工核验</t>
+          <t>项目：北京大学2026年9月政府采购意向- 晶圆 检测 仪详细情况150.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-07-14；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -1635,19 +1635,19 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430062786</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-430314307</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告</t>
+          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1667,14 +1667,14 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>项目：关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告；可见摘要：收藏 招标变更 广东 9分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告；可见摘要：收藏 招标变更 广东 23小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1697,19 +1697,19 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430039810</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430062786</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告</t>
+          <t>关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1719,24 +1719,24 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>项目：陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告；可见摘要：收藏 招标公告 陕西 2026-07-10；详情状态：受限，需人工核验</t>
+          <t>项目：关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告；可见摘要：收藏 招标变更 广东 9分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -1759,19 +1759,19 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429867103</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430039810</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09</t>
+          <t>陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>项目：西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09；可见摘要：附件 收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告；可见摘要：收藏 招标公告 陕西 2026-07-10；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
@@ -1821,19 +1821,19 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429704334</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429867103</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)</t>
+          <t>西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1843,17 +1843,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)；可见摘要：收藏 招标预告 上海 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09；可见摘要：附件 收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -1883,19 +1883,19 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-429701886</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429704334</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告</t>
+          <t>中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1905,17 +1905,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>项目：【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告；可见摘要：收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)；可见摘要：收藏 招标预告 上海 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -1945,39 +1945,39 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429701915</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-429701886</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>晶圆有机清洗机-招标公告</t>
+          <t>【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>晶圆/衬底光学缺陷检测</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>晶圆有机清洗机</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>采购内容：晶圆有机清洗机；数量：1台；公告类型：招标公告；发布时间：2026-07-10</t>
+          <t>项目：【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告；可见摘要：收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
@@ -1990,7 +1990,7 @@
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2007,19 +2007,19 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/843900.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429701915</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:31:20</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="25" ht="58" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>中数创和设备采购项目014结果公告</t>
+          <t>晶圆有机清洗机-招标公告</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -2029,25 +2029,21 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>中数创和设备采购项目014</t>
+          <t>晶圆有机清洗机</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>检测系统，且公告明确晶圆/硅片/SiC/衬底场景</t>
+          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>采购内容：中数创和设备采购项目014；成交/中标方：黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2；成交/中标金额：000.00元；公告类型：结果公告；发布时间：2026-07-10</t>
+          <t>采购内容：晶圆有机清洗机；数量：1台；公告类型：招标公告；发布时间：2026-07-10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2</t>
-        </is>
-      </c>
+      <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
@@ -2061,23 +2057,19 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>结果公告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>000.00元</t>
-        </is>
-      </c>
+      <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/jhwzb/843422.jhtml</t>
+          <t>https://www.365trade.com.cn/zhwzb/843900.jhtml</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -2089,69 +2081,77 @@
     <row r="26" ht="58" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686</t>
+          <t>中数创和设备采购项目014结果公告</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>晶圆/衬底光学缺陷检测</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>中数创和设备采购项目014</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统，且公告明确晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
+          <t>采购内容：中数创和设备采购项目014；成交/中标方：黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2；成交/中标金额：000.00元；公告类型：结果公告；发布时间：2026-07-10</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>结果公告</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>000.00元</t>
+        </is>
+      </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429404126</t>
+          <t>https://www.365trade.com.cn/jhwzb/843422.jhtml</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-14T09:31:20</t>
         </is>
       </c>
     </row>
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)</t>
+          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -2171,14 +2171,14 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)；可见摘要：收藏 招标公告 上海 2026-07-08；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -2201,19 +2201,19 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429489269</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429404126</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="28" ht="58" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告</t>
+          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2223,24 +2223,24 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告；可见摘要：收藏 招标变更 河北 2026-07-05；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)；可见摘要：收藏 招标公告 上海 2026-07-08；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -2251,31 +2251,31 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>终止/流标</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428711615</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429489269</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="29" ht="58" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -2285,24 +2285,24 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>项目：纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告；可见摘要：收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告；可见摘要：收藏 招标变更 河北 2026-07-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -2313,51 +2313,51 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>终止/流标</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428537526</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428711615</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397</t>
+          <t>纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告；可见摘要：收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
@@ -2375,31 +2375,31 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419989</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428537526</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="31" ht="58" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396</t>
+          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
@@ -2449,39 +2449,39 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419915</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419989</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告</t>
+          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告；可见摘要：附件 收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
@@ -2499,31 +2499,31 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428541747</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419915</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="33" ht="58" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告</t>
+          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2533,24 +2533,24 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
+          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告；可见摘要：附件 收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2573,19 +2573,19 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434578</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428541747</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="34" ht="58" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
@@ -2635,19 +2635,19 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434575</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434578</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="35" ht="58" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2657,24 +2657,24 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告；可见摘要：收藏 招标公告 河北 22分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2697,19 +2697,19 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427329545</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434575</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="36" ht="58" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2729,14 +2729,14 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告；可见摘要：附件 收藏 招标变更 河北 2026-06-27；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告；可见摘要：收藏 招标公告 河北 22分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2747,31 +2747,31 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>终止/流标</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427255950</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427329545</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="37" ht="58" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2781,17 +2781,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)；可见摘要：收藏 招标预告 上海 2026-06-27；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告；可见摘要：附件 收藏 招标变更 河北 2026-06-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
@@ -2809,31 +2809,31 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>终止/流标</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427280358</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427255950</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="38" ht="58" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告</t>
+          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2843,24 +2843,24 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>项目：生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告；可见摘要：收藏 招标公告 江苏 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)；可见摘要：收藏 招标预告 上海 2026-06-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -2883,19 +2883,19 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427124669</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427280358</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="39" ht="58" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告</t>
+          <t>生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2905,17 +2905,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告；可见摘要：附件 收藏 招标公告 安徽 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告；可见摘要：收藏 招标公告 江苏 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
@@ -2945,19 +2945,19 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427174343</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427124669</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="40" ht="58" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2967,17 +2967,17 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>缺陷检测</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告；可见摘要：标书 收藏 中标结果 北京 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告；可见摘要：附件 收藏 招标公告 安徽 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
@@ -2995,51 +2995,51 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-427191692</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427174343</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="41" ht="58" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告；可见摘要：标书 收藏 中标结果 北京 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
@@ -3057,31 +3057,31 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426951671</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-427191692</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="42" ht="58" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396</t>
+          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396；可见摘要：收藏 招标公告 上海 12小时前；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
@@ -3131,39 +3131,39 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426983145</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426951671</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="43" ht="58" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器</t>
+          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器；可见摘要：收藏 招标预告 上海 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396；可见摘要：收藏 招标公告 上海 12小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -3193,19 +3193,19 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427096376</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426983145</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="44" ht="58" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14</t>
+          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>项目：2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14；可见摘要：收藏 招标公告 浙江 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器；可见摘要：收藏 招标预告 上海 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -3255,61 +3255,57 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427057182</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427096376</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="45" ht="58" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>谈判采购公告</t>
+          <t>2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>CIM系统</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>RMS，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>采购内容：CIM系统；数量：一家；范围：CIM系统设备采购及有关技术服务、培训等，具体要求详见第五章采购需求；采购方：成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采；公告类型：采购公告；发布时间：2026-06-25</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采</t>
-        </is>
-      </c>
+          <t>项目：2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14；可见摘要：收藏 招标公告 浙江 2026-06-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>采购公告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -3321,81 +3317,85 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/837713.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427057182</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:51:21</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="46" ht="58" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告</t>
+          <t>谈判采购公告</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>CIM系统</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>RMS，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告；可见摘要：附件 收藏 中标结果 上海 2026-06-24；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr"/>
+          <t>采购内容：CIM系统；数量：一家；范围：CIM系统设备采购及有关技术服务、培训等，具体要求详见第五章采购需求；采购方：成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采；公告类型：采购公告；发布时间：2026-06-25</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采</t>
+        </is>
+      </c>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>采购公告</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426498852</t>
+          <t>https://www.365trade.com.cn/zhwzb/837713.jhtml</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-06-26T10:51:21</t>
         </is>
       </c>
     </row>
     <row r="47" ht="58" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -3415,14 +3415,14 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告；可见摘要：附件 收藏 中标结果 上海 2026-06-24；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -3445,19 +3445,19 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426408417</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426498852</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="48" ht="58" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3467,17 +3467,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
@@ -3507,19 +3507,19 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426280043</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426408417</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="49" ht="58" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
+          <t>上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -3529,24 +3529,24 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
@@ -3557,31 +3557,31 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426280043</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="50" ht="58" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3591,24 +3591,24 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -3619,31 +3619,31 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="51" ht="58" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -3653,17 +3653,17 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
@@ -3681,31 +3681,31 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="52" ht="58" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
+          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
@@ -3748,26 +3748,26 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="53" ht="58" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
+          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3777,24 +3777,24 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3805,31 +3805,31 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="54" ht="58" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3839,24 +3839,24 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3867,51 +3867,51 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="55" ht="58" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪</t>
+          <t>外观检查机</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
@@ -3929,58 +3929,58 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="56" ht="58" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
+          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>膜厚仪</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -3991,31 +3991,31 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="57" ht="58" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
+          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -4025,24 +4025,24 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
+          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
@@ -4065,19 +4065,19 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="58" ht="58" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
+          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -4097,14 +4097,14 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
+          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -4115,31 +4115,31 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="59" ht="58" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -4149,17 +4149,17 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
@@ -4177,31 +4177,31 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr"/>
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="60" ht="58" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
+          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -4211,24 +4211,24 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测</t>
+          <t>自动光学检查机</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -4251,46 +4251,42 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="61" ht="58" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪【重新招标】-公开招标公告</t>
+          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>晶圆表面缺陷检测</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测，且公告具有半导体产业链语境</t>
+          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>无锡中微掩模电子有限公司</t>
-        </is>
-      </c>
+          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -4300,74 +4296,78 @@
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>公开招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10T14:16:35</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="62" ht="58" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
+          <t>缺陷检测仪【重新招标】-公开招标公告</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr"/>
+          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>无锡中微掩模电子有限公司</t>
+        </is>
+      </c>
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>公开招标公告</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -4379,46 +4379,46 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
+          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-06-10T14:16:35</t>
         </is>
       </c>
     </row>
     <row r="63" ht="58" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
@@ -4429,58 +4429,58 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="64" ht="58" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
+          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>外观检测</t>
+          <t>CD-SEM</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
@@ -4503,19 +4503,19 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="65" ht="58" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
+          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -4525,24 +4525,24 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统</t>
+          <t>外观检测</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
@@ -4565,19 +4565,19 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="66" ht="58" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4587,17 +4587,17 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>颗粒检测系统</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
@@ -4615,31 +4615,31 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="67" ht="58" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -4649,24 +4649,24 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
@@ -4689,19 +4689,19 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22T10:32:05</t>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
     <row r="68" ht="58" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -4711,17 +4711,17 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>外观检查机</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
@@ -4739,29 +4739,91 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr"/>
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="3" t="inlineStr">
         <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23T10:31:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="58" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>检测设备</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
           <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-421062373</t>
         </is>
       </c>
-      <c r="P68" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-22T10:32:05</t>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23T10:31:58</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P68"/>
+  <autoFilter ref="A1:P69"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -4830,10 +4892,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O69" r:id="rId68"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId68"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId69"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4866,7 +4929,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-22T10:35:43</t>
+          <t>2026-07-23T10:35:18</t>
         </is>
       </c>
     </row>
@@ -4877,7 +4940,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
@@ -4899,7 +4962,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8">

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P69" headerRowCount="1">
-  <autoFilter ref="A1:P69"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P71" headerRowCount="1">
+  <autoFilter ref="A1:P71"/>
   <tableColumns count="16">
     <tableColumn id="1" name="项目名称"/>
     <tableColumn id="2" name="判断类别"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P69"/>
+  <dimension ref="A1:P71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -593,7 +593,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026第三季度 检测 仪器生产物料采购及成品备货专项 芯片</t>
+          <t>硅片 光学 检测 定位模块-申购单号：NCBPMLABS2026000251</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -603,24 +603,24 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>光学检测/量测设备</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>项目：2026第三季度 检测 仪器生产物料采购及成品备货专项 芯片；可见摘要：收藏 招标公告 浙江 14分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：硅片 光学 检测 定位模块-申购单号：NCBPMLABS2026000251；可见摘要：收藏 中标结果 陕西 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -631,7 +631,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -643,19 +643,19 @@
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-432133611</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%A1%85%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-432274027</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）开标信息</t>
+          <t>NCBPMLABS2026000251SGKY20260700053- 硅片 光学 检测 定位模块</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -665,24 +665,24 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>光学检测/量测设备</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）开标信息；可见摘要：收藏 中标结果 安徽 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：NCBPMLABS2026000251SGKY20260700053- 硅片 光学 检测 定位模块；可见摘要：收藏 采购信息 陕西 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -693,7 +693,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>采购信息</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -705,19 +705,19 @@
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431784773</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%A1%85%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-432282142</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="4" ht="58" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）开标信息</t>
+          <t>AOI 晶圆 缺陷 检测台中标结果公告(1)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -727,24 +727,24 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）开标信息；可见摘要：收藏 中标结果 安徽 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：AOI 晶圆 缺陷 检测台中标结果公告(1)；可见摘要：收藏 中标结果 上海 2026-07-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -760,26 +760,26 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431784789</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-432346453</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>合肥丰创光罩有限公司光 掩模 缺陷 检测 仪报废处置项目招标公告</t>
+          <t>2026第三季度 检测 仪器生产物料采购及成品备货专项 芯片</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -789,24 +789,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>掩模缺陷检测仪</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>掩模缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥丰创光罩有限公司光 掩模 缺陷 检测 仪报废处置项目招标公告；可见摘要：收藏 招标公告 安徽 15小时前；详情状态：受限，需人工核验</t>
+          <t>项目：2026第三季度 检测 仪器生产物料采购及成品备货专项 芯片；可见摘要：收藏 招标公告 浙江 14分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -829,57 +829,57 @@
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E6%A3%80%E6%B5%8B#bidcenter-431811305</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-432133611</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购项目单一来源采购邀请书</t>
+          <t>超光滑碳化硅光学元件无损清洗系统-公开招标公告</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>晶圆/衬底光学缺陷检测</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>超光滑碳化硅光学元件无损清洗系统</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购项目单一来源采购邀请书；可见摘要：收藏 招标公告 河北 16小时前；详情状态：受限，需人工核验</t>
+          <t>采购内容：超光滑碳化硅光学元件无损清洗系统；数量：1套；公告类型：公开招标公告；发布时间：2026-07-23</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>公开招标公告</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -891,19 +891,19 @@
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-431794027</t>
+          <t>https://www.365trade.com.cn/zhwzb/848661.jhtml</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:34:55</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目GDMS检测设备采购项目国际招标公告(1)-2435-264JT2026002</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）开标信息</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -913,24 +913,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目GDMS检测设备采购项目国际招标公告(1)-2435-264JT2026002；可见摘要：收藏 招标公告 河南 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）开标信息；可见摘要：收藏 中标结果 安徽 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -941,7 +941,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -953,19 +953,19 @@
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-431545561</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431784773</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目-2026-07-16</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）开标信息</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -975,24 +975,24 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>项目：陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目-2026-07-16；可见摘要：附件 收藏 招标公告 陕西 11小时前；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）开标信息；可见摘要：收藏 中标结果 安徽 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1015,19 +1015,19 @@
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%9B%86%E6%88%90%E7%94%B5%E8%B7%AF%20%E6%A3%80%E6%B5%8B#bidcenter-431023609</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431784789</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目</t>
+          <t>合肥丰创光罩有限公司光 掩模 缺陷 检测 仪报废处置项目招标公告</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1037,24 +1037,24 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>掩模缺陷检测仪</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>掩模缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>项目：陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目；可见摘要：附件 收藏 招标公告 陕西 12小时前；详情状态：受限，需人工核验</t>
+          <t>项目：合肥丰创光罩有限公司光 掩模 缺陷 检测 仪报废处置项目招标公告；可见摘要：收藏 招标公告 安徽 15小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -1077,19 +1077,19 @@
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%9B%86%E6%88%90%E7%94%B5%E8%B7%AF%20%E6%A3%80%E6%B5%8B#bidcenter-431017188</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E6%A3%80%E6%B5%8B#bidcenter-431811305</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第4包中标结果公告</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购项目单一来源采购邀请书</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1099,24 +1099,24 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第4包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购项目单一来源采购邀请书；可见摘要：收藏 招标公告 河北 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -1127,31 +1127,31 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361360</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-431794027</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第3包中标结果公告</t>
+          <t>麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目GDMS检测设备采购项目国际招标公告(1)-2435-264JT2026002</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第3包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目GDMS检测设备采购项目国际招标公告(1)-2435-264JT2026002；可见摘要：收藏 招标公告 河南 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1189,31 +1189,31 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361355</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-431545561</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第2包中标结果公告</t>
+          <t>陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目-2026-07-16</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1223,17 +1223,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第2包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
+          <t>项目：陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目-2026-07-16；可见摘要：附件 收藏 招标公告 陕西 11小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
@@ -1251,31 +1251,31 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361358</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%9B%86%E6%88%90%E7%94%B5%E8%B7%AF%20%E6%A3%80%E6%B5%8B#bidcenter-431023609</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第1包中标结果公告</t>
+          <t>陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第1包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
+          <t>项目：陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目；可见摘要：附件 收藏 招标公告 陕西 12小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
@@ -1313,31 +1313,31 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361353</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%9B%86%E6%88%90%E7%94%B5%E8%B7%AF%20%E6%A3%80%E6%B5%8B#bidcenter-431017188</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备重新招标澄清或变更公告</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第4包中标结果公告</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1347,17 +1347,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>缺陷检测</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备重新招标澄清或变更公告；可见摘要：收藏 招标变更 上海 22小时前；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第4包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
@@ -1375,31 +1375,31 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430852656</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361360</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备重新招标澄清或变更公告(1)-0613-264025123686</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第3包中标结果公告</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1409,24 +1409,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>缺陷检测</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备重新招标澄清或变更公告(1)-0613-264025123686；可见摘要：收藏 招标变更 上海 32分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第3包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1437,31 +1437,31 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430820283</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361355</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）评标结果公示公告(1)-0821-264MSKZZ2202</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第2包中标结果公告</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1471,24 +1471,24 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>缺陷检测</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）评标结果公示公告(1)-0821-264MSKZZ2202；可见摘要：收藏 中标结果 河南 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第2包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1511,81 +1511,81 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430471714</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361358</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>超光滑碳化硅光学元件无损清洗系统-公开招标公告</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第1包中标结果公告</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>晶圆/衬底光学缺陷检测</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>超光滑碳化硅光学元件无损清洗系统</t>
+          <t>缺陷检测</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>采购内容：超光滑碳化硅光学元件无损清洗系统；数量：1套；公告类型：公开招标公告；发布时间：2026-07-15</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第1包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>公开招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/845555.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361353</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T10:35:32</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>北京大学2026年9月政府采购意向- 晶圆 检测 仪详细情况150.000000万元(人民币)</t>
+          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备重新招标澄清或变更公告</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1595,24 +1595,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>项目：北京大学2026年9月政府采购意向- 晶圆 检测 仪详细情况150.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-07-14；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备重新招标澄清或变更公告；可见摘要：收藏 招标变更 上海 22小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1623,31 +1623,31 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-430314307</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430852656</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告</t>
+          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备重新招标澄清或变更公告(1)-0613-264025123686</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1657,24 +1657,24 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告；可见摘要：收藏 招标变更 广东 23小时前；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备重新招标澄清或变更公告(1)-0613-264025123686；可见摘要：收藏 招标变更 上海 32分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1690,26 +1690,26 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430062786</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430820283</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）评标结果公示公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1719,24 +1719,24 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>项目：关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告；可见摘要：收藏 招标变更 广东 9分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）评标结果公示公告(1)-0821-264MSKZZ2202；可见摘要：收藏 中标结果 河南 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1747,31 +1747,31 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430039810</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430471714</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告</t>
+          <t>北京大学2026年9月政府采购意向- 晶圆 检测 仪详细情况150.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1781,24 +1781,24 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>项目：陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告；可见摘要：收藏 招标公告 陕西 2026-07-10；详情状态：受限，需人工核验</t>
+          <t>项目：北京大学2026年9月政府采购意向- 晶圆 检测 仪详细情况150.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-07-14；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -1821,19 +1821,19 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429867103</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-430314307</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09</t>
+          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1843,24 +1843,24 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>项目：西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09；可见摘要：附件 收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告；可见摘要：收藏 招标变更 广东 23小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -1883,19 +1883,19 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429704334</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430062786</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)</t>
+          <t>关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1905,24 +1905,24 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)；可见摘要：收藏 招标预告 上海 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告；可见摘要：收藏 招标变更 广东 9分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -1945,19 +1945,19 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-429701886</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430039810</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告</t>
+          <t>陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1967,17 +1967,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>项目：【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告；可见摘要：收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告；可见摘要：收藏 招标公告 陕西 2026-07-10；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
@@ -2007,39 +2007,39 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429701915</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429867103</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="25" ht="58" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>晶圆有机清洗机-招标公告</t>
+          <t>西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>晶圆/衬底光学缺陷检测</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>晶圆有机清洗机</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>采购内容：晶圆有机清洗机；数量：1台；公告类型：招标公告；发布时间：2026-07-10</t>
+          <t>项目：西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09；可见摘要：附件 收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
@@ -2052,7 +2052,7 @@
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2069,47 +2069,43 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/843900.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429704334</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:31:20</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="26" ht="58" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>中数创和设备采购项目014结果公告</t>
+          <t>中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>晶圆/衬底光学缺陷检测</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>中数创和设备采购项目014</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>检测系统，且公告明确晶圆/硅片/SiC/衬底场景</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>采购内容：中数创和设备采购项目014；成交/中标方：黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2；成交/中标金额：000.00元；公告类型：结果公告；发布时间：2026-07-10</t>
+          <t>项目：中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)；可见摘要：收藏 招标预告 上海 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2</t>
-        </is>
-      </c>
+      <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
@@ -2118,40 +2114,36 @@
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>结果公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>000.00元</t>
-        </is>
-      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/jhwzb/843422.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-429701886</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:31:20</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686</t>
+          <t>【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -2161,24 +2153,24 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告；可见摘要：收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -2201,52 +2193,52 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429404126</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429701915</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="28" ht="58" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)</t>
+          <t>晶圆有机清洗机-招标公告</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>晶圆/衬底光学缺陷检测</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>晶圆有机清洗机</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)；可见摘要：收藏 招标公告 上海 2026-07-08；详情状态：受限，需人工核验</t>
+          <t>采购内容：晶圆有机清洗机；数量：1台；公告类型：招标公告；发布时间：2026-07-10</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2263,81 +2255,89 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429489269</t>
+          <t>https://www.365trade.com.cn/zhwzb/843900.jhtml</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-14T09:31:20</t>
         </is>
       </c>
     </row>
     <row r="29" ht="58" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告</t>
+          <t>中数创和设备采购项目014结果公告</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>晶圆/衬底光学缺陷检测</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>中数创和设备采购项目014</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统，且公告明确晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告；可见摘要：收藏 招标变更 河北 2026-07-05；详情状态：受限，需人工核验</t>
+          <t>采购内容：中数创和设备采购项目014；成交/中标方：黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2；成交/中标金额：000.00元；公告类型：结果公告；发布时间：2026-07-10</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2</t>
+        </is>
+      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>结果公告</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>终止/流标</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>000.00元</t>
+        </is>
+      </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428711615</t>
+          <t>https://www.365trade.com.cn/jhwzb/843422.jhtml</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-14T09:31:20</t>
         </is>
       </c>
     </row>
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告</t>
+          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2347,24 +2347,24 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>项目：纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告；可见摘要：收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -2387,46 +2387,46 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428537526</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429404126</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="31" ht="58" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397</t>
+          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)；可见摘要：收藏 招标公告 上海 2026-07-08；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -2437,58 +2437,58 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419989</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429489269</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告；可见摘要：收藏 招标变更 河北 2026-07-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2504,26 +2504,26 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>终止/流标</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419915</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428711615</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="33" ht="58" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告</t>
+          <t>纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告；可见摘要：附件 收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告；可见摘要：收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
@@ -2573,46 +2573,46 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428541747</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428537526</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="34" ht="58" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告</t>
+          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2623,58 +2623,58 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434578</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419989</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="35" ht="58" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告</t>
+          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2685,31 +2685,31 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434575</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419915</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="36" ht="58" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告</t>
+          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2719,24 +2719,24 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告；可见摘要：收藏 招标公告 河北 22分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告；可见摘要：附件 收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2759,19 +2759,19 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427329545</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428541747</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="37" ht="58" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2781,24 +2781,24 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告；可见摘要：附件 收藏 招标变更 河北 2026-06-27；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2809,31 +2809,31 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>终止/流标</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427255950</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434578</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="38" ht="58" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2843,24 +2843,24 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)；可见摘要：收藏 招标预告 上海 2026-06-27；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -2883,19 +2883,19 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427280358</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434575</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="39" ht="58" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2905,24 +2905,24 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>项目：生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告；可见摘要：收藏 招标公告 江苏 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告；可见摘要：收藏 招标公告 河北 22分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2945,19 +2945,19 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427124669</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427329545</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="40" ht="58" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2967,24 +2967,24 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告；可见摘要：附件 收藏 招标公告 安徽 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告；可见摘要：附件 收藏 招标变更 河北 2026-06-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2995,31 +2995,31 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>终止/流标</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427174343</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427255950</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="41" ht="58" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告</t>
+          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -3039,14 +3039,14 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告；可见摘要：标书 收藏 中标结果 北京 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)；可见摘要：收藏 招标预告 上海 2026-06-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -3057,51 +3057,51 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-427191692</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427280358</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="42" ht="58" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397</t>
+          <t>生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告；可见摘要：收藏 招标公告 江苏 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
@@ -3131,39 +3131,39 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426951671</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427124669</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="43" ht="58" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>缺陷检测</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396；可见摘要：收藏 招标公告 上海 12小时前；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告；可见摘要：附件 收藏 招标公告 安徽 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
@@ -3193,19 +3193,19 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426983145</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427174343</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="44" ht="58" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器；可见摘要：收藏 招标预告 上海 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告；可见摘要：标书 收藏 中标结果 北京 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
@@ -3243,51 +3243,51 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427096376</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-427191692</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="45" ht="58" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14</t>
+          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>项目：2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14；可见摘要：收藏 招标公告 浙江 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
@@ -3317,61 +3317,57 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427057182</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426951671</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="46" ht="58" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>谈判采购公告</t>
+          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>CIM系统</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>RMS，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>采购内容：CIM系统；数量：一家；范围：CIM系统设备采购及有关技术服务、培训等，具体要求详见第五章采购需求；采购方：成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采；公告类型：采购公告；发布时间：2026-06-25</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采</t>
-        </is>
-      </c>
+          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396；可见摘要：收藏 招标公告 上海 12小时前；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>采购公告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -3383,19 +3379,19 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/837713.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426983145</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:51:21</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="47" ht="58" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告</t>
+          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -3415,14 +3411,14 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告；可见摘要：附件 收藏 中标结果 上海 2026-06-24；详情状态：受限，需人工核验</t>
+          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器；可见摘要：收藏 招标预告 上海 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -3433,31 +3429,31 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426498852</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427096376</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="48" ht="58" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762</t>
+          <t>2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3477,14 +3473,14 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
+          <t>项目：2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14；可见摘要：收藏 招标公告 浙江 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -3495,93 +3491,97 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426408417</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427057182</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="49" ht="58" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218</t>
+          <t>谈判采购公告</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测</t>
+          <t>CIM系统</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>RMS，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr"/>
+          <t>采购内容：CIM系统；数量：一家；范围：CIM系统设备采购及有关技术服务、培训等，具体要求详见第五章采购需求；采购方：成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采；公告类型：采购公告；发布时间：2026-06-25</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采</t>
+        </is>
+      </c>
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>采购公告</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426280043</t>
+          <t>https://www.365trade.com.cn/zhwzb/837713.jhtml</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-06-26T10:51:21</t>
         </is>
       </c>
     </row>
     <row r="50" ht="58" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3591,24 +3591,24 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告；可见摘要：附件 收藏 中标结果 上海 2026-06-24；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -3619,31 +3619,31 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426498852</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="51" ht="58" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -3653,24 +3653,24 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -3681,31 +3681,31 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426408417</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="52" ht="58" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
+          <t>上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3715,24 +3715,24 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -3748,26 +3748,26 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426280043</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="53" ht="58" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3777,24 +3777,24 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3805,31 +3805,31 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="54" ht="58" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3839,24 +3839,24 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3867,31 +3867,31 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="55" ht="58" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
+          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3901,24 +3901,24 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -3934,53 +3934,53 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="56" ht="58" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
+          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -3991,31 +3991,31 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="57" ht="58" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>AOI 晶圆缺陷检测台评标结果公示公告</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -4025,24 +4025,24 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>项目：AOI 晶圆缺陷检测台评标结果公示公告；可见摘要：收藏 中标结果 广东 2026-06-11；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
@@ -4053,31 +4053,31 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=AOI#bidcenter-424516652</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="58" ht="58" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -4087,24 +4087,24 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>外观检查机</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -4127,46 +4127,46 @@
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="59" ht="58" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
+          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>膜厚仪</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -4189,19 +4189,19 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="60" ht="58" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
+          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -4211,24 +4211,24 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -4251,19 +4251,19 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="61" ht="58" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -4273,24 +4273,24 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
@@ -4301,97 +4301,93 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="62" ht="58" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪【重新招标】-公开招标公告</t>
+          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>自动光学检查机</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测，且公告具有半导体产业链语境</t>
+          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>无锡中微掩模电子有限公司</t>
-        </is>
-      </c>
+          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>公开招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10T14:16:35</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="63" ht="58" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
+          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -4401,24 +4397,24 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>晶圆表面缺陷检测</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
+          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
@@ -4429,93 +4425,97 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="64" ht="58" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
+          <t>缺陷检测仪【重新招标】-公开招标公告</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr"/>
+          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>无锡中微掩模电子有限公司</t>
+        </is>
+      </c>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>公开招标公告</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr"/>
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
+          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-06-10T14:16:35</t>
         </is>
       </c>
     </row>
     <row r="65" ht="58" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -4525,24 +4525,24 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>外观检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
@@ -4553,58 +4553,58 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr"/>
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="66" ht="58" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
+          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统</t>
+          <t>CD-SEM</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -4627,19 +4627,19 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="67" ht="58" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -4649,24 +4649,24 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>外观检测</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
@@ -4677,31 +4677,31 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr"/>
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="68" ht="58" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -4711,24 +4711,24 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>颗粒检测系统</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
@@ -4739,31 +4739,31 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr"/>
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T10:31:58</t>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="69" ht="58" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -4773,24 +4773,24 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
@@ -4801,29 +4801,153 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr"/>
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="3" t="inlineStr">
         <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24T10:31:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="58" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>招标变更</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>变更/澄清</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24T10:31:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="58" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>检测设备</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="3" t="inlineStr">
+        <is>
           <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-421062373</t>
         </is>
       </c>
-      <c r="P69" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-23T10:31:58</t>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24T10:31:56</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P69"/>
+  <autoFilter ref="A1:P71"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -4893,10 +5017,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O68" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O71" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId69"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId71"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4929,7 +5055,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-23T10:35:18</t>
+          <t>2026-07-24T10:34:56</t>
         </is>
       </c>
     </row>
@@ -4940,7 +5066,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
@@ -4962,7 +5088,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8">

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$72</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P71" headerRowCount="1">
-  <autoFilter ref="A1:P71"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P72" headerRowCount="1">
+  <autoFilter ref="A1:P72"/>
   <tableColumns count="16">
     <tableColumn id="1" name="项目名称"/>
     <tableColumn id="2" name="判断类别"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P71"/>
+  <dimension ref="A1:P72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -593,7 +593,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>硅片 光学 检测 定位模块-申购单号：NCBPMLABS2026000251</t>
+          <t>重庆芯联微电子有限公司无图案 晶圆 缺陷 检测设备国际招标公告(1)-0613-264025124060</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -603,17 +603,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>项目：硅片 光学 检测 定位模块-申购单号：NCBPMLABS2026000251；可见摘要：收藏 中标结果 陕西 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：重庆芯联微电子有限公司无图案 晶圆 缺陷 检测设备国际招标公告(1)-0613-264025124060；可见摘要：收藏 招标公告 重庆 2026-07-24；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
@@ -631,7 +631,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -643,19 +643,19 @@
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%A1%85%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-432274027</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-432526385</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>NCBPMLABS2026000251SGKY20260700053- 硅片 光学 检测 定位模块</t>
+          <t>硅片 光学 检测 定位模块-申购单号：NCBPMLABS2026000251</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>项目：NCBPMLABS2026000251SGKY20260700053- 硅片 光学 检测 定位模块；可见摘要：收藏 采购信息 陕西 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：硅片 光学 检测 定位模块-申购单号：NCBPMLABS2026000251；可见摘要：收藏 中标结果 陕西 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
@@ -693,7 +693,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>采购信息</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -705,19 +705,19 @@
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%A1%85%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-432282142</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%A1%85%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-432274027</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="4" ht="58" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AOI 晶圆 缺陷 检测台中标结果公告(1)</t>
+          <t>NCBPMLABS2026000251SGKY20260700053- 硅片 光学 检测 定位模块</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -727,24 +727,24 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>光学检测/量测设备</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>项目：AOI 晶圆 缺陷 检测台中标结果公告(1)；可见摘要：收藏 中标结果 上海 2026-07-23；详情状态：受限，需人工核验</t>
+          <t>项目：NCBPMLABS2026000251SGKY20260700053- 硅片 光学 检测 定位模块；可见摘要：收藏 采购信息 陕西 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -755,31 +755,31 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>采购信息</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-432346453</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%A1%85%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-432282142</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026第三季度 检测 仪器生产物料采购及成品备货专项 芯片</t>
+          <t>AOI 晶圆 缺陷 检测台中标结果公告(1)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -789,17 +789,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>项目：2026第三季度 检测 仪器生产物料采购及成品备货专项 芯片；可见摘要：收藏 招标公告 浙江 14分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：AOI 晶圆 缺陷 检测台中标结果公告(1)；可见摘要：收藏 中标结果 上海 2026-07-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
@@ -817,51 +817,51 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-432133611</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-432346453</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>超光滑碳化硅光学元件无损清洗系统-公开招标公告</t>
+          <t>2026第三季度 检测 仪器生产物料采购及成品备货专项 芯片</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>晶圆/衬底光学缺陷检测</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>超光滑碳化硅光学元件无损清洗系统</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>采购内容：超光滑碳化硅光学元件无损清洗系统；数量：1套；公告类型：公开招标公告；发布时间：2026-07-23</t>
+          <t>项目：2026第三季度 检测 仪器生产物料采购及成品备货专项 芯片；可见摘要：收藏 招标公告 浙江 14分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
@@ -874,12 +874,12 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>公开招标公告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -891,57 +891,57 @@
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/848661.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-432133611</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:34:55</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）开标信息</t>
+          <t>超光滑碳化硅光学元件无损清洗系统-公开招标公告</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>晶圆/衬底光学缺陷检测</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>超光滑碳化硅光学元件无损清洗系统</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）开标信息；可见摘要：收藏 中标结果 安徽 16小时前；详情状态：受限，需人工核验</t>
+          <t>采购内容：超光滑碳化硅光学元件无损清洗系统；数量：1套；公告类型：公开招标公告；发布时间：2026-07-23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>公开招标公告</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -953,19 +953,19 @@
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431784773</t>
+          <t>https://www.365trade.com.cn/zhwzb/848661.jhtml</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-24T10:34:55</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）开标信息</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）开标信息</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）开标信息；可见摘要：收藏 中标结果 安徽 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）开标信息；可见摘要：收藏 中标结果 安徽 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
@@ -1015,19 +1015,19 @@
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431784789</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431784773</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>合肥丰创光罩有限公司光 掩模 缺陷 检测 仪报废处置项目招标公告</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）开标信息</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1037,17 +1037,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>掩模缺陷检测仪</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>掩模缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥丰创光罩有限公司光 掩模 缺陷 检测 仪报废处置项目招标公告；可见摘要：收藏 招标公告 安徽 15小时前；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）开标信息；可见摘要：收藏 中标结果 安徽 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1077,19 +1077,19 @@
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E6%A3%80%E6%B5%8B#bidcenter-431811305</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431784789</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购项目单一来源采购邀请书</t>
+          <t>合肥丰创光罩有限公司光 掩模 缺陷 检测 仪报废处置项目招标公告</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>掩模缺陷检测仪</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>掩模缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购项目单一来源采购邀请书；可见摘要：收藏 招标公告 河北 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：合肥丰创光罩有限公司光 掩模 缺陷 检测 仪报废处置项目招标公告；可见摘要：收藏 招标公告 安徽 15小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
@@ -1139,19 +1139,19 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-431794027</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E6%A3%80%E6%B5%8B#bidcenter-431811305</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目GDMS检测设备采购项目国际招标公告(1)-2435-264JT2026002</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购项目单一来源采购邀请书</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目GDMS检测设备采购项目国际招标公告(1)-2435-264JT2026002；可见摘要：收藏 招标公告 河南 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购项目单一来源采购邀请书；可见摘要：收藏 招标公告 河北 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1201,19 +1201,19 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-431545561</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-431794027</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目-2026-07-16</t>
+          <t>麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目GDMS检测设备采购项目国际招标公告(1)-2435-264JT2026002</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1223,24 +1223,24 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>项目：陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目-2026-07-16；可见摘要：附件 收藏 招标公告 陕西 11小时前；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目GDMS检测设备采购项目国际招标公告(1)-2435-264JT2026002；可见摘要：收藏 招标公告 河南 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1263,19 +1263,19 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%9B%86%E6%88%90%E7%94%B5%E8%B7%AF%20%E6%A3%80%E6%B5%8B#bidcenter-431023609</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-431545561</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目</t>
+          <t>陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目-2026-07-16</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>项目：陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目；可见摘要：附件 收藏 招标公告 陕西 12小时前；详情状态：受限，需人工核验</t>
+          <t>项目：陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目-2026-07-16；可见摘要：附件 收藏 招标公告 陕西 11小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
@@ -1325,19 +1325,19 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%9B%86%E6%88%90%E7%94%B5%E8%B7%AF%20%E6%A3%80%E6%B5%8B#bidcenter-431017188</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%9B%86%E6%88%90%E7%94%B5%E8%B7%AF%20%E6%A3%80%E6%B5%8B#bidcenter-431023609</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第4包中标结果公告</t>
+          <t>陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1347,17 +1347,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第4包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
+          <t>项目：陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目；可见摘要：附件 收藏 招标公告 陕西 12小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
@@ -1375,31 +1375,31 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361360</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%9B%86%E6%88%90%E7%94%B5%E8%B7%AF%20%E6%A3%80%E6%B5%8B#bidcenter-431017188</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第3包中标结果公告</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第4包中标结果公告</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第3包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第4包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
@@ -1449,19 +1449,19 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361355</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361360</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第2包中标结果公告</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第3包中标结果公告</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第2包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第3包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
@@ -1511,19 +1511,19 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361358</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361355</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第1包中标结果公告</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第2包中标结果公告</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第1包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第2包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
@@ -1573,19 +1573,19 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361353</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361358</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备重新招标澄清或变更公告</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第1包中标结果公告</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>缺陷检测</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备重新招标澄清或变更公告；可见摘要：收藏 招标变更 上海 22小时前；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第1包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
@@ -1623,31 +1623,31 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430852656</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361353</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备重新招标澄清或变更公告(1)-0613-264025123686</t>
+          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备重新招标澄清或变更公告</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1667,14 +1667,14 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备重新招标澄清或变更公告(1)-0613-264025123686；可见摘要：收藏 招标变更 上海 32分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备重新招标澄清或变更公告；可见摘要：收藏 招标变更 上海 22小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1697,19 +1697,19 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430820283</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430852656</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）评标结果公示公告(1)-0821-264MSKZZ2202</t>
+          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备重新招标澄清或变更公告(1)-0613-264025123686</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1719,24 +1719,24 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）评标结果公示公告(1)-0821-264MSKZZ2202；可见摘要：收藏 中标结果 河南 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备重新招标澄清或变更公告(1)-0613-264025123686；可见摘要：收藏 招标变更 上海 32分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1747,31 +1747,31 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430471714</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430820283</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>北京大学2026年9月政府采购意向- 晶圆 检测 仪详细情况150.000000万元(人民币)</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）评标结果公示公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1781,24 +1781,24 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>项目：北京大学2026年9月政府采购意向- 晶圆 检测 仪详细情况150.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-07-14；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目（二次）评标结果公示公告(1)-0821-264MSKZZ2202；可见摘要：收藏 中标结果 河南 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1809,31 +1809,31 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-430314307</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-430471714</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告</t>
+          <t>北京大学2026年9月政府采购意向- 晶圆 检测 仪详细情况150.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告；可见摘要：收藏 招标变更 广东 23小时前；详情状态：受限，需人工核验</t>
+          <t>项目：北京大学2026年9月政府采购意向- 晶圆 检测 仪详细情况150.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-07-14；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -1883,19 +1883,19 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430062786</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-430314307</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告</t>
+          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1915,14 +1915,14 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>项目：关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告；可见摘要：收藏 招标变更 广东 9分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购延期公告；可见摘要：收藏 招标变更 广东 23小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1945,19 +1945,19 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430039810</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430062786</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告</t>
+          <t>关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1967,24 +1967,24 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>项目：陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告；可见摘要：收藏 招标公告 陕西 2026-07-10；详情状态：受限，需人工核验</t>
+          <t>项目：关于纳米孔基因测序仪和微阵列 芯片 检测 仪采购的更正公告；可见摘要：收藏 招标变更 广东 9分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2007,19 +2007,19 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429867103</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-430039810</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="25" ht="58" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09</t>
+          <t>陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -2029,17 +2029,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>项目：西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09；可见摘要：附件 收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：陕西电子芯业时代科技有限公司8英寸高性能特色工艺半导体 芯片 生产线项目颗粒 检测 设备采购撤项公告；可见摘要：收藏 招标公告 陕西 2026-07-10；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
@@ -2069,19 +2069,19 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429704334</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429867103</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="26" ht="58" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)</t>
+          <t>西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -2091,17 +2091,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)；可见摘要：收藏 招标预告 上海 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：西安理工大学新型光电功率集成 芯片 检测 系统招标公告-2026-07-09；可见摘要：附件 收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2131,19 +2131,19 @@
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-429701886</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429704334</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告</t>
+          <t>中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -2153,17 +2153,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>项目：【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告；可见摘要：收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院上海微系统与信息技术研究所2026年8月政府采购意向-无图型 晶圆 缺陷 检测设备详细情况300.000000万元(人民币)；可见摘要：收藏 招标预告 上海 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -2193,39 +2193,39 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429701915</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-429701886</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="28" ht="58" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>晶圆有机清洗机-招标公告</t>
+          <t>【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>晶圆/衬底光学缺陷检测</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>晶圆有机清洗机</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>采购内容：晶圆有机清洗机；数量：1台；公告类型：招标公告；发布时间：2026-07-10</t>
+          <t>项目：【限额上采购】西安理工大学新型光电功率集成 芯片 检测 系统招标公告；可见摘要：收藏 招标公告 陕西 17小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
@@ -2238,7 +2238,7 @@
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2255,19 +2255,19 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/843900.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-429701915</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14T09:31:20</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="29" ht="58" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>中数创和设备采购项目014结果公告</t>
+          <t>晶圆有机清洗机-招标公告</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -2277,25 +2277,21 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>中数创和设备采购项目014</t>
+          <t>晶圆有机清洗机</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>检测系统，且公告明确晶圆/硅片/SiC/衬底场景</t>
+          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>采购内容：中数创和设备采购项目014；成交/中标方：黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2；成交/中标金额：000.00元；公告类型：结果公告；发布时间：2026-07-10</t>
+          <t>采购内容：晶圆有机清洗机；数量：1台；公告类型：招标公告；发布时间：2026-07-10</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2</t>
-        </is>
-      </c>
+      <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
           <t>2026-07-10</t>
@@ -2309,23 +2305,19 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>结果公告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>000.00元</t>
-        </is>
-      </c>
+      <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/jhwzb/843422.jhtml</t>
+          <t>https://www.365trade.com.cn/zhwzb/843900.jhtml</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -2337,69 +2329,77 @@
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686</t>
+          <t>中数创和设备采购项目014结果公告</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>晶圆/衬底光学缺陷检测</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>中数创和设备采购项目014</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统，且公告明确晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
+          <t>采购内容：中数创和设备采购项目014；成交/中标方：黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2；成交/中标金额：000.00元；公告类型：结果公告；发布时间：2026-07-10</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>黄石邦柯科技股份有限公司供应商地址：湖北省黄石市下陆区杭州西路194号成交金额：¥4,800,000.00元四、主要标的信息序号货物名称型号及规格数量及单位品牌含税单价/元含税总价/元交付时间1双立柱堆垛机货物尺寸:1200*1000mm2</t>
+        </is>
+      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>结果公告</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>000.00元</t>
+        </is>
+      </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429404126</t>
+          <t>https://www.365trade.com.cn/jhwzb/843422.jhtml</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-14T09:31:20</t>
         </is>
       </c>
     </row>
     <row r="31" ht="58" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)</t>
+          <t>上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2419,14 +2419,14 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)；可见摘要：收藏 招标公告 上海 2026-07-08；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOI+SWIR检测设备国际招标公告(1)-0613-264025123686；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -2449,19 +2449,19 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429489269</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429404126</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告</t>
+          <t>上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2471,24 +2471,24 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告；可见摘要：收藏 招标变更 河北 2026-07-05；详情状态：受限，需人工核验</t>
+          <t>项目：上海易卜 半导体 有限公司FC3DAOISWIR检测设备-国际招标公告(1)；可见摘要：收藏 招标公告 上海 2026-07-08；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2499,31 +2499,31 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>终止/流标</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428711615</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-429489269</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="33" ht="58" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2533,24 +2533,24 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>项目：纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告；可见摘要：收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次流标公告；可见摘要：收藏 招标变更 河北 2026-07-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2561,51 +2561,51 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>终止/流标</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428537526</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428711615</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="34" ht="58" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397</t>
+          <t>纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：纳米孔基因测序仪和微阵列 芯片 检测 仪采购的采购公告；可见摘要：收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
@@ -2623,31 +2623,31 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419989</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428537526</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="35" ht="58" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396</t>
+          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备重新招标澄清或变更公告(1)-0613-264025123397；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
@@ -2697,39 +2697,39 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419915</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419989</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="36" ht="58" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告</t>
+          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告；可见摘要：附件 收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备重新招标澄清或变更公告(1)-0613-264025123396；可见摘要：收藏 招标变更 上海 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
@@ -2747,31 +2747,31 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428541747</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-428419915</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="37" ht="58" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告</t>
+          <t>ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2781,24 +2781,24 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
+          <t>项目：ZBKJ61(2026)155-0618纳米孔基因测序仪和微阵列 芯片 检测 仪采购招标公告；可见摘要：附件 收藏 招标公告 广东 2026-07-03；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2821,19 +2821,19 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434578</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-428541747</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="38" ht="58" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
@@ -2883,19 +2883,19 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434575</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434578</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="39" ht="58" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2905,24 +2905,24 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告；可见摘要：收藏 招标公告 河北 22分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）招标公告；可见摘要：收藏 招标公告 安徽 18小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2945,19 +2945,19 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427329545</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427434575</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="40" ht="58" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2977,14 +2977,14 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告；可见摘要：附件 收藏 招标变更 河北 2026-06-27；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购二次招标公告；可见摘要：收藏 招标公告 河北 22分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2995,31 +2995,31 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>终止/流标</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427255950</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427329545</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="41" ht="58" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -3029,17 +3029,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)；可见摘要：收藏 招标预告 上海 2026-06-27；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购一次流标公告；可见摘要：附件 收藏 招标变更 河北 2026-06-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
@@ -3057,31 +3057,31 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>终止/流标</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427280358</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427255950</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="42" ht="58" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告</t>
+          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -3091,24 +3091,24 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>项目：生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告；可见摘要：收藏 招标公告 江苏 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器详细情况169.000000万元(人民币)；可见摘要：收藏 招标预告 上海 2026-06-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -3131,19 +3131,19 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427124669</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427280358</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="43" ht="58" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告</t>
+          <t>生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -3153,17 +3153,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告；可见摘要：附件 收藏 招标公告 安徽 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：生医学院器官 芯片 智能分析 检测 系统采购（SEU-ZB-260343）采购公告；可见摘要：收藏 招标公告 江苏 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
@@ -3193,19 +3193,19 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427174343</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427124669</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="44" ht="58" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -3215,17 +3215,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>缺陷检测</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告；可见摘要：标书 收藏 中标结果 北京 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目招标公告；可见摘要：附件 收藏 招标公告 安徽 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
@@ -3243,51 +3243,51 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-427191692</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-427174343</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="45" ht="58" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>量测设备</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测 仪采购项目中标公告；可见摘要：标书 收藏 中标结果 北京 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
@@ -3305,31 +3305,31 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426951671</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-427191692</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="46" ht="58" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396</t>
+          <t>上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396；可见摘要：收藏 招标公告 上海 12小时前；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动12寸 晶圆 缺陷检测设备及全自动CD 量测 设备国际招标公告(1)-0613-264025123397；可见摘要：收藏 招标公告 上海 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
@@ -3379,39 +3379,39 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426983145</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426951671</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="47" ht="58" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器</t>
+          <t>上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>量测设备</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>量测设备 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器；可见摘要：收藏 招标预告 上海 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程半导体有限公司全自动 晶圆 阻值漏电流 量测 设备国际招标公告(1)-0613-264025123396；可见摘要：收藏 招标公告 上海 12小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -3441,19 +3441,19 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427096376</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E9%87%8F%E6%B5%8B#bidcenter-426983145</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="48" ht="58" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14</t>
+          <t>上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>项目：2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14；可见摘要：收藏 招标公告 浙江 2026-06-26；详情状态：受限，需人工核验</t>
+          <t>项目：上海大学2026年07月政府采购意向-多通道 芯片 极低温 检测 仪器；可见摘要：收藏 招标预告 上海 2026-06-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -3503,61 +3503,57 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427057182</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427096376</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="49" ht="58" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>谈判采购公告</t>
+          <t>2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>CIM系统</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>RMS，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>采购内容：CIM系统；数量：一家；范围：CIM系统设备采购及有关技术服务、培训等，具体要求详见第五章采购需求；采购方：成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采；公告类型：采购公告；发布时间：2026-06-25</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采</t>
-        </is>
-      </c>
+          <t>项目：2026第二季度 检测 仪器生产物料采购及成品备货专项 芯片 ICL7650SCPDZDIP14；可见摘要：收藏 招标公告 浙江 2026-06-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>采购公告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -3569,81 +3565,85 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/837713.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-427057182</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T10:51:21</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="50" ht="58" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告</t>
+          <t>谈判采购公告</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>CIM系统</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>RMS，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告；可见摘要：附件 收藏 中标结果 上海 2026-06-24；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr"/>
+          <t>采购内容：CIM系统；数量：一家；范围：CIM系统设备采购及有关技术服务、培训等，具体要求详见第五章采购需求；采购方：成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采；公告类型：采购公告；发布时间：2026-06-25</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>成都华微电子科技股份有限公司。1.3采购代理机构:中科信工程咨询（北京）有限责任公司。1.4采购项目资金落实情况:资金已经到位或资金来源已经确定。1.5采购项目概况:CIM系统采购。1.6成交供应商数量:一家。2.采购范围及相关要求2.1采</t>
+        </is>
+      </c>
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>采购公告</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426498852</t>
+          <t>https://www.365trade.com.cn/zhwzb/837713.jhtml</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-06-26T10:51:21</t>
         </is>
       </c>
     </row>
     <row r="51" ht="58" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -3663,14 +3663,14 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目国际公开招标中标公告；可见摘要：附件 收藏 中标结果 上海 2026-06-24；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -3693,19 +3693,19 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426408417</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426498852</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="52" ht="58" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218</t>
+          <t>华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3715,17 +3715,17 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
+          <t>项目：华东理工大学 半导体 薄膜分析检测仪采购项目中标结果公告(1)-1069-264Z20261762；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
@@ -3755,19 +3755,19 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426280043</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426408417</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="53" ht="58" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
+          <t>上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3777,24 +3777,24 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>颗粒检测</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司颗粒检测设备中标结果公告(1)-0613-264025122218；可见摘要：收藏 中标结果 上海 2026-06-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3805,31 +3805,31 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-426280043</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="54" ht="58" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3839,24 +3839,24 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购招标公告；可见摘要：收藏 招标公告 河北 2026-06-22；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3867,31 +3867,31 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-425959054</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="55" ht="58" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3901,17 +3901,17 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目重新招标澄清或变更公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标变更 河南 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
@@ -3929,31 +3929,31 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425781085</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="56" ht="58" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
+          <t>新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
+          <t>项目：新能源汽车可靠性开发协同创新平台-车载 半导体 功率器件综合检测仪合同公告-GXZC2026-G1-001098-GXTZ；可见摘要：附件 收藏 中标结果 广西 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
@@ -3996,26 +3996,26 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-425848783</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="57" ht="58" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
+          <t>半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -4025,24 +4025,24 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测 仪和 晶圆 光学参数 检测 仪评标结果公示公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 中标结果 江苏 2026-06-18；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
@@ -4053,31 +4053,31 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-425762071</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="58" ht="58" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -4087,24 +4087,24 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目标前公示；可见摘要：收藏 招标公告 安徽 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -4115,51 +4115,51 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-425246132</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="59" ht="58" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪</t>
+          <t>外观检查机</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】评标结果公示公告(1)-0730-264010SZ0036/04；可见摘要：收藏 中标结果 广东 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
@@ -4177,58 +4177,58 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>招标预告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr"/>
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-424767797</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="60" ht="58" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
+          <t>中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>膜厚仪</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>膜厚仪 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院微电子研究所2026年7至11月政府采购意向-12吋光学 膜厚仪 详细情况1200.000000万元(人民币)；可见摘要：收藏 招标预告 北京 2026-06-12；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -4239,31 +4239,31 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标预告</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%86%9C%E5%8E%9A%E4%BB%AA#bidcenter-424521867</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="61" ht="58" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
+          <t>SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -4283,14 +4283,14 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
+          <t>项目：SiC衬底 晶圆 位错缺陷光学无损 检测设备 中标结果公告(1)-0664-2640SUMECA96/01；可见摘要：收藏 中标结果 浙江 22小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
@@ -4301,31 +4301,31 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423847224</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="62" ht="58" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
+          <t>麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -4335,17 +4335,17 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料(郑州)有限公司年产360万片8英寸 半导体 特色硅抛光片项目SPV检测设备采购项目国际招标公告(1)-0821-264MSKZZ2202；可见摘要：收藏 招标公告 河南 2026-06-09；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr"/>
@@ -4363,31 +4363,31 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B%E8%AE%BE%E5%A4%87#bidcenter-423735716</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="63" ht="58" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
+          <t>广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -4397,24 +4397,24 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测</t>
+          <t>自动光学检查机</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>自动光学检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 自动光学检查 机【重新招标】中标结果公告(1)；可见摘要：收藏 中标结果 广东 10分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
@@ -4437,46 +4437,42 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%87%AA%E5%8A%A8%E5%85%89%E5%AD%A6%E6%A3%80%E6%9F%A5#bidcenter-423897036</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="64" ht="58" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪【重新招标】-公开招标公告</t>
+          <t>晶圆表面缺陷检测 设备采购项目中标（成交）结果公告</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>半导体检测/量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>晶圆表面缺陷检测</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测，且公告具有半导体产业链语境</t>
+          <t>晶圆表面缺陷检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>无锡中微掩模电子有限公司</t>
-        </is>
-      </c>
+          <t>项目：晶圆表面缺陷检测 设备采购项目中标（成交）结果公告；可见摘要：收藏 中标结果 湖北 2026-06-08；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -4486,74 +4482,78 @@
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>公开招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr"/>
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%E8%A1%A8%E9%9D%A2%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-423553467</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10T14:16:35</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="65" ht="58" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
+          <t>缺陷检测仪【重新招标】-公开招标公告</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>半导体检测/量测设备</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr"/>
+          <t>采购内容：缺陷检测仪；数量：1套；用途：掩模缺陷检测仪是在表面缺陷和污染检测仪基础上发展起来的综合性自动化掩模缺陷检测仪器；采购方：无锡中微掩模电子有限公司；公告类型：公开招标公告；发布时间：2026-06-08</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>无锡中微掩模电子有限公司</t>
+        </is>
+      </c>
       <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>公开招标公告</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
@@ -4565,46 +4565,46 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
+          <t>https://www.365trade.com.cn/zhwzb/830925.jhtml</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-06-10T14:16:35</t>
         </is>
       </c>
     </row>
     <row r="66" ht="58" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
+          <t>中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>光学量测设备</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
+          <t>项目：中国科学院半导体研究所 晶圆 平整度 检测仪 采购项目；可见摘要：收藏 招标公告 北京 2026-06-05；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -4615,58 +4615,58 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-423147557</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="67" ht="58" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
+          <t>无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>光学量测设备</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>外观检测</t>
+          <t>CD-SEM</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>CD-SEM 属于光学量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司8A新增CD-SEM 线宽量测 S9系列（或同等及以上品牌）翻新设备中标候选人公示；可见摘要：收藏 中标结果 江苏 2026-06-04；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
@@ -4689,19 +4689,19 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%BA%BF%E5%AE%BD%E9%87%8F%E6%B5%8B#bidcenter-423083473</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="68" ht="58" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
+          <t>上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -4711,24 +4711,24 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统</t>
+          <t>外观检测</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检测 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：上海易启芯程 半导体 有限公司 外观检测 机中标结果公告(1)-0613-264025121838；可见摘要：收藏 中标结果 上海 2026-06-02；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
@@ -4751,19 +4751,19 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E5%A4%96%E8%A7%82%E6%A3%80%E6%B5%8B#bidcenter-422490029</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="69" ht="58" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
+          <t>无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -4773,17 +4773,17 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>颗粒检测系统</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
+          <t>项目：无锡华润上华科技有限公司上华一厂在线 颗粒检测 系统采购单源直接采购结果公告；可见摘要：收藏 中标结果 江苏 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
@@ -4801,31 +4801,31 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>招标变更</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>变更/澄清</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr"/>
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%A2%97%E7%B2%92%E6%A3%80%E6%B5%8B#bidcenter-421444008</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="70" ht="58" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
+          <t>半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -4835,24 +4835,24 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>外观检查机</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：半自动表面平整度 检测仪 和 晶圆 光学参数 检测仪 重新招标澄清或变更公告(1)-0664-2640SUMECA96/09；可见摘要：收藏 招标变更 北京 2026-05-27；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
@@ -4875,19 +4875,19 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B%E4%BB%AA#bidcenter-421422332</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:31:56</t>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
     <row r="71" ht="58" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+          <t>广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -4897,17 +4897,17 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>外观检查机</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观检查机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+          <t>项目：广州广芯封装基板有限公司项目- 外观检查机 【重新招标】国际招标澄清或变更公告(11)-0730-264010SZ0036/04；可见摘要：收藏 招标变更 广东 2026-05-26；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
@@ -4925,29 +4925,91 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>变更/澄清</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="3" t="inlineStr">
         <is>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%A4%96%E8%A7%82%E6%A3%80%E6%9F%A5%E6%9C%BA#bidcenter-421253286</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27T10:31:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="58" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>光学检测设备</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>检测设备</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>项目：光 掩模 中低端 缺陷检测 设备中标结果公告(1)-0705-264021603171；可见摘要：收藏 中标结果 广东 2026-05-26；详情状态：受限，需人工核验</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>采招网</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>中标结果</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>已出结果</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="3" t="inlineStr">
+        <is>
           <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E7%BC%BA%E9%99%B7%E6%A3%80%E6%B5%8B#bidcenter-421062373</t>
         </is>
       </c>
-      <c r="P71" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-24T10:31:56</t>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27T10:31:56</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P71"/>
+  <autoFilter ref="A1:P72"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -5019,10 +5081,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O69" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O70" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O72" r:id="rId71"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId71"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId72"/>
   </tableParts>
 </worksheet>
 </file>
@@ -5055,7 +5118,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-24T10:34:56</t>
+          <t>2026-07-27T10:34:25</t>
         </is>
       </c>
     </row>
@@ -5066,7 +5129,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6">
@@ -5088,7 +5151,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8">

--- a/downloads/招标信息总表.xlsx
+++ b/downloads/招标信息总表.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总表'!$A$1:$P$73</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -174,8 +174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P72" headerRowCount="1">
-  <autoFilter ref="A1:P72"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BidInfoTotalTable" displayName="BidInfoTotalTable" ref="A1:P73" headerRowCount="1">
+  <autoFilter ref="A1:P73"/>
   <tableColumns count="16">
     <tableColumn id="1" name="项目名称"/>
     <tableColumn id="2" name="判断类别"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P72"/>
+  <dimension ref="A1:P73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -593,7 +593,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>重庆芯联微电子有限公司无图案 晶圆 缺陷 检测设备国际招标公告(1)-0613-264025124060</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测 仪等设备采购项目（一包）终止公告</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -603,24 +603,24 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>项目：重庆芯联微电子有限公司无图案 晶圆 缺陷 检测设备国际招标公告(1)-0613-264025124060；可见摘要：收藏 招标公告 重庆 2026-07-24；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测 仪等设备采购项目（一包）终止公告；可见摘要：收藏 招标变更 安徽 37分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -631,31 +631,31 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>招标变更</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>终止/流标</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-432526385</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E6%A3%80%E6%B5%8B#bidcenter-432934704</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27T10:31:56</t>
+          <t>2026-07-28T10:31:59</t>
         </is>
       </c>
     </row>
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>硅片 光学 检测 定位模块-申购单号：NCBPMLABS2026000251</t>
+          <t>重庆芯联微电子有限公司无图案 晶圆 缺陷 检测设备国际招标公告(1)-0613-264025124060</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -665,17 +665,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>项目：硅片 光学 检测 定位模块-申购单号：NCBPMLABS2026000251；可见摘要：收藏 中标结果 陕西 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：重庆芯联微电子有限公司无图案 晶圆 缺陷 检测设备国际招标公告(1)-0613-264025124060；可见摘要：收藏 招标公告 重庆 2026-07-24；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
@@ -693,7 +693,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -705,19 +705,19 @@
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%A1%85%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-432274027</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-432526385</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27T10:31:56</t>
+          <t>2026-07-28T10:31:59</t>
         </is>
       </c>
     </row>
     <row r="4" ht="58" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>NCBPMLABS2026000251SGKY20260700053- 硅片 光学 检测 定位模块</t>
+          <t>硅片 光学 检测 定位模块-申购单号：NCBPMLABS2026000251</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>项目：NCBPMLABS2026000251SGKY20260700053- 硅片 光学 检测 定位模块；可见摘要：收藏 采购信息 陕西 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：硅片 光学 检测 定位模块-申购单号：NCBPMLABS2026000251；可见摘要：收藏 中标结果 陕西 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>采购信息</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -767,19 +767,19 @@
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%A1%85%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-432282142</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%A1%85%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-432274027</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27T10:31:56</t>
+          <t>2026-07-28T10:31:59</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AOI 晶圆 缺陷 检测台中标结果公告(1)</t>
+          <t>NCBPMLABS2026000251SGKY20260700053- 硅片 光学 检测 定位模块</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -789,24 +789,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>AOI</t>
+          <t>光学检测/量测设备</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>项目：AOI 晶圆 缺陷 检测台中标结果公告(1)；可见摘要：收藏 中标结果 上海 2026-07-23；详情状态：受限，需人工核验</t>
+          <t>项目：NCBPMLABS2026000251SGKY20260700053- 硅片 光学 检测 定位模块；可见摘要：收藏 采购信息 陕西 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -817,31 +817,31 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>采购信息</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-432346453</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E7%A1%85%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-432282142</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27T10:31:56</t>
+          <t>2026-07-28T10:31:59</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026第三季度 检测 仪器生产物料采购及成品备货专项 芯片</t>
+          <t>AOI 晶圆 缺陷 检测台中标结果公告(1)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -851,17 +851,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>检测仪</t>
+          <t>AOI</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>AOI 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>项目：2026第三季度 检测 仪器生产物料采购及成品备货专项 芯片；可见摘要：收藏 招标公告 浙江 14分钟前；详情状态：受限，需人工核验</t>
+          <t>项目：AOI 晶圆 缺陷 检测台中标结果公告(1)；可见摘要：收藏 中标结果 上海 2026-07-23；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
@@ -879,51 +879,51 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>进行中/未知</t>
+          <t>已出结果</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-432133611</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-432346453</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27T10:31:56</t>
+          <t>2026-07-28T10:31:59</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>超光滑碳化硅光学元件无损清洗系统-公开招标公告</t>
+          <t>2026第三季度 检测 仪器生产物料采购及成品备货专项 芯片</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>晶圆/衬底光学缺陷检测</t>
+          <t>光学检测设备</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>超光滑碳化硅光学元件无损清洗系统</t>
+          <t>检测仪</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
+          <t>检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>采购内容：超光滑碳化硅光学元件无损清洗系统；数量：1套；公告类型：公开招标公告；发布时间：2026-07-23</t>
+          <t>项目：2026第三季度 检测 仪器生产物料采购及成品备货专项 芯片；可见摘要：收藏 招标公告 浙江 14分钟前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
@@ -936,12 +936,12 @@
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>中招联合</t>
+          <t>采招网</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>公开招标公告</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -953,57 +953,57 @@
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>https://www.365trade.com.cn/zhwzb/848661.jhtml</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-432133611</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24T10:34:55</t>
+          <t>2026-07-28T10:31:59</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）开标信息</t>
+          <t>超光滑碳化硅光学元件无损清洗系统-公开招标公告</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>光学检测设备</t>
+          <t>晶圆/衬底光学缺陷检测</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪</t>
+          <t>超光滑碳化硅光学元件无损清洗系统</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>颗粒，且公告明确晶圆/硅片/SiC/衬底场景</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）开标信息；可见摘要：收藏 中标结果 安徽 16小时前；详情状态：受限，需人工核验</t>
+          <t>采购内容：超光滑碳化硅光学元件无损清洗系统；数量：1套；公告类型：公开招标公告；发布时间：2026-07-23</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>采招网</t>
+          <t>中招联合</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>公开招标公告</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1015,19 +1015,19 @@
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431784773</t>
+          <t>https://www.365trade.com.cn/zhwzb/848661.jhtml</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27T10:31:56</t>
+          <t>2026-07-24T10:34:55</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）开标信息</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）开标信息</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）开标信息；可见摘要：收藏 中标结果 安徽 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（二包）开标信息；可见摘要：收藏 中标结果 安徽 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
@@ -1077,19 +1077,19 @@
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431784789</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431784773</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27T10:31:56</t>
+          <t>2026-07-28T10:31:59</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>合肥丰创光罩有限公司光 掩模 缺陷 检测 仪报废处置项目招标公告</t>
+          <t>芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）开标信息</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>掩模缺陷检测仪</t>
+          <t>缺陷检测仪</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>掩模缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥丰创光罩有限公司光 掩模 缺陷 检测 仪报废处置项目招标公告；可见摘要：收藏 招标公告 安徽 15小时前；详情状态：受限，需人工核验</t>
+          <t>项目：芜湖智能传感器研究院有限公司 晶圆 缺陷 检测仪等设备采购项目（一包）开标信息；可见摘要：收藏 中标结果 安徽 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>招标公告</t>
+          <t>中标结果</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1139,19 +1139,19 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E6%A3%80%E6%B5%8B#bidcenter-431811305</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431784789</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27T10:31:56</t>
+          <t>2026-07-28T10:31:59</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购项目单一来源采购邀请书</t>
+          <t>合肥丰创光罩有限公司光 掩模 缺陷 检测 仪报废处置项目招标公告</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1161,17 +1161,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机</t>
+          <t>掩模缺陷检测仪</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>掩模缺陷检测仪 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购项目单一来源采购邀请书；可见摘要：收藏 招标公告 河北 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：合肥丰创光罩有限公司光 掩模 缺陷 检测 仪报废处置项目招标公告；可见摘要：收藏 招标公告 安徽 15小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
@@ -1201,19 +1201,19 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-431794027</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%8E%A9%E6%A8%A1%20%E6%A3%80%E6%B5%8B#bidcenter-431811305</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27T10:31:56</t>
+          <t>2026-07-28T10:31:59</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目GDMS检测设备采购项目国际招标公告(1)-2435-264JT2026002</t>
+          <t>中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购项目单一来源采购邀请书</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1223,24 +1223,24 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>检测设备</t>
+          <t>外观自动检测机</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>外观自动检测机 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>项目：麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目GDMS检测设备采购项目国际招标公告(1)-2435-264JT2026002；可见摘要：收藏 招标公告 河南 16小时前；详情状态：受限，需人工核验</t>
+          <t>项目：中国电子科技集团公司第十三研究所 芯片 外观自动 检测 机采购项目单一来源采购邀请书；可见摘要：收藏 招标公告 河北 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1263,19 +1263,19 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-431545561</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E8%8A%AF%E7%89%87%20%E6%A3%80%E6%B5%8B#bidcenter-431794027</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27T10:31:56</t>
+          <t>2026-07-28T10:31:59</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目-2026-07-16</t>
+          <t>麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目GDMS检测设备采购项目国际招标公告(1)-2435-264JT2026002</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1285,24 +1285,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>检测系统</t>
+          <t>检测设备</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
+          <t>检测设备 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>项目：陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目-2026-07-16；可见摘要：附件 收藏 招标公告 陕西 11小时前；详情状态：受限，需人工核验</t>
+          <t>项目：麦斯克电子材料（郑州）有限公司年产360万片8英寸 半导体 特色硅抛光片项目GDMS检测设备采购项目国际招标公告(1)-2435-264JT2026002；可见摘要：收藏 招标公告 河南 16小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1325,19 +1325,19 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%9B%86%E6%88%90%E7%94%B5%E8%B7%AF%20%E6%A3%80%E6%B5%8B#bidcenter-431023609</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E5%8D%8A%E5%AF%BC%E4%BD%93%20%E9%87%8F%E6%B5%8B#bidcenter-431545561</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27T10:31:56</t>
+          <t>2026-07-28T10:31:59</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目</t>
+          <t>陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目-2026-07-16</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>项目：陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目；可见摘要：附件 收藏 招标公告 陕西 12小时前；详情状态：受限，需人工核验</t>
+          <t>项目：陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目-2026-07-16；可见摘要：附件 收藏 招标公告 陕西 11小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
@@ -1387,19 +1387,19 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%9B%86%E6%88%90%E7%94%B5%E8%B7%AF%20%E6%A3%80%E6%B5%8B#bidcenter-431017188</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%9B%86%E6%88%90%E7%94%B5%E8%B7%AF%20%E6%A3%80%E6%B5%8B#bidcenter-431023609</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27T10:31:56</t>
+          <t>2026-07-28T10:31:59</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第4包中标结果公告</t>
+          <t>陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1409,17 +1409,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>缺陷检测</t>
+          <t>检测系统</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>光学检测/量测设备，且公告具有半导体产业链语境</t>
+          <t>检测系统 属于光学检测设备，且公告具有半导体产业链语境</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第4包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
+          <t>项目：陕西职业技术学院产教融合实训基地项目-智能硬件与 集成电路 创新中心-工业 检测 系统实训平台采购项目；可见摘要：附件 收藏 招标公告 陕西 12小时前；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
@@ -1437,31 +1437,31 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>中标结果</t>
+          <t>招标公告</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>已出结果</t>
+          <t>进行中/未知</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361360</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E9%9B%86%E6%88%90%E7%94%B5%E8%B7%AF%20%E6%A3%80%E6%B5%8B#bidcenter-431017188</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27T10:31:56</t>
+          <t>2026-07-28T10:31:59</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第3包中标结果公告</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第4包中标结果公告</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第3包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第4包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
@@ -1511,19 +1511,19 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361355</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361360</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27T10:31:56</t>
+          <t>2026-07-28T10:31:59</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第2包中标结果公告</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第3包中标结果公告</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第2包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
+          <t>项目：合肥工业大学 晶圆 缺陷 检测装备研制项目第3包中标结果公告；可见摘要：收藏 中标结果 安徽 2026-07-17；详情状态：受限，需人工核验</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
@@ -1573,19 +1573,19 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361358</t>
+          <t>https://www.bidcenter.com.cn/search.html?keywords=%E6%99%B6%E5%9C%86%20%E7%BC%BA%E9%99%B7#bidcenter-431361355</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27T10:31:56</t>
+          <t>2026-07-28T10:31:59</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第1包中标结果公告</t>
+          <t>合肥工业大学 晶圆 缺陷 检测装备研制项目第2